--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -28,7 +28,7 @@
     <sheet name="Cambios vs. original" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$368</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$370</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5314,7 +5314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I368"/>
+  <dimension ref="A1:I370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17920,10 +17920,14 @@
       </c>
       <c r="H328" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I328" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I328" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="14" t="inlineStr">
@@ -17955,10 +17959,14 @@
       </c>
       <c r="H329" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I329" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I329" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="16" t="inlineStr">
@@ -17990,10 +17998,14 @@
       </c>
       <c r="H330" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I330" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I330" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="14" t="inlineStr">
@@ -18025,10 +18037,14 @@
       </c>
       <c r="H331" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I331" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I331" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="16" t="inlineStr">
@@ -18060,10 +18076,14 @@
       </c>
       <c r="H332" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I332" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I332" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="14" t="inlineStr">
@@ -18095,10 +18115,14 @@
       </c>
       <c r="H333" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I333" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I333" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="334" ht="26" customHeight="1">
       <c r="A334" s="12" t="inlineStr">
@@ -18138,10 +18162,14 @@
       </c>
       <c r="H334" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I334" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I334" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="14" t="inlineStr">
@@ -18173,10 +18201,14 @@
       </c>
       <c r="H335" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I335" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I335" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="16" t="inlineStr">
@@ -18192,7 +18224,7 @@
       <c r="C336" s="16" t="inlineStr"/>
       <c r="D336" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Aplicarlo a las rutas de cada módulo</t>
+          <t xml:space="preserve">    Aplicarlo a las rutas de movimientos y categorías</t>
         </is>
       </c>
       <c r="E336" s="17" t="inlineStr"/>
@@ -18208,10 +18240,14 @@
       </c>
       <c r="H336" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I336" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I336" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="14" t="inlineStr">
@@ -18227,7 +18263,7 @@
       <c r="C337" s="14" t="inlineStr"/>
       <c r="D337" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Probar el acceso con el módulo apagado</t>
+          <t xml:space="preserve">    Mostrar en pantalla un aviso claro cuando el módulo está apagado</t>
         </is>
       </c>
       <c r="E337" s="15" t="inlineStr"/>
@@ -18243,58 +18279,58 @@
       </c>
       <c r="H337" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I337" s="14" t="inlineStr"/>
-    </row>
-    <row r="338" ht="26" customHeight="1">
-      <c r="A338" s="12" t="inlineStr">
-        <is>
-          <t>HU-36</t>
-        </is>
-      </c>
-      <c r="B338" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C338" s="12" t="inlineStr">
-        <is>
-          <t>Configuración de Módulos</t>
-        </is>
-      </c>
-      <c r="D338" s="12" t="inlineStr">
-        <is>
-          <t>Como empresa nueva quiero empezar con una configuración razonable para no tener que definir todo antes de usar el sistema.</t>
-        </is>
-      </c>
-      <c r="E338" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F338" s="13" t="inlineStr">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I337" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="16" t="inlineStr">
+        <is>
+          <t>T-35.4</t>
+        </is>
+      </c>
+      <c r="B338" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C338" s="16" t="inlineStr"/>
+      <c r="D338" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Distinguir el aviso de módulo apagado del de falta de permiso</t>
+        </is>
+      </c>
+      <c r="E338" s="17" t="inlineStr"/>
+      <c r="F338" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G338" s="13" t="inlineStr">
+      <c r="G338" s="17" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H338" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I338" s="12" t="inlineStr"/>
+      <c r="H338" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I338" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="14" t="inlineStr">
         <is>
-          <t>T-36.1</t>
+          <t>T-35.5</t>
         </is>
       </c>
       <c r="B339" s="14" t="inlineStr">
@@ -18305,7 +18341,7 @@
       <c r="C339" s="14" t="inlineStr"/>
       <c r="D339" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el conjunto de módulos y categorías iniciales</t>
+          <t xml:space="preserve">    Probar el acceso con el módulo apagado</t>
         </is>
       </c>
       <c r="E339" s="15" t="inlineStr"/>
@@ -18321,50 +18357,62 @@
       </c>
       <c r="H339" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I339" s="14" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" s="16" t="inlineStr">
-        <is>
-          <t>T-36.2</t>
-        </is>
-      </c>
-      <c r="B340" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C340" s="16" t="inlineStr"/>
-      <c r="D340" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar la carga automática al aprobar la empresa</t>
-        </is>
-      </c>
-      <c r="E340" s="17" t="inlineStr"/>
-      <c r="F340" s="17" t="inlineStr">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I339" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="26" customHeight="1">
+      <c r="A340" s="12" t="inlineStr">
+        <is>
+          <t>HU-36</t>
+        </is>
+      </c>
+      <c r="B340" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C340" s="12" t="inlineStr">
+        <is>
+          <t>Configuración de Módulos</t>
+        </is>
+      </c>
+      <c r="D340" s="12" t="inlineStr">
+        <is>
+          <t>Como empresa nueva quiero empezar con una configuración razonable para no tener que definir todo antes de usar el sistema.</t>
+        </is>
+      </c>
+      <c r="E340" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F340" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G340" s="17" t="inlineStr">
+      <c r="G340" s="13" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H340" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I340" s="16" t="inlineStr"/>
+      <c r="H340" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I340" s="12" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="14" t="inlineStr">
         <is>
-          <t>T-36.3</t>
+          <t>T-36.1</t>
         </is>
       </c>
       <c r="B341" s="14" t="inlineStr">
@@ -18375,7 +18423,7 @@
       <c r="C341" s="14" t="inlineStr"/>
       <c r="D341" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Probar el alta de una empresa nueva de punta a punta</t>
+          <t xml:space="preserve">    Definir el conjunto de módulos y categorías iniciales</t>
         </is>
       </c>
       <c r="E341" s="15" t="inlineStr"/>
@@ -18396,154 +18444,154 @@
       </c>
       <c r="I341" s="14" t="inlineStr"/>
     </row>
-    <row r="342" ht="20" customHeight="1">
-      <c r="A342" s="9" t="inlineStr">
+    <row r="342">
+      <c r="A342" s="16" t="inlineStr">
+        <is>
+          <t>T-36.2</t>
+        </is>
+      </c>
+      <c r="B342" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C342" s="16" t="inlineStr"/>
+      <c r="D342" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar la carga automática al aprobar la empresa</t>
+        </is>
+      </c>
+      <c r="E342" s="17" t="inlineStr"/>
+      <c r="F342" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G342" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H342" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I342" s="16" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="14" t="inlineStr">
+        <is>
+          <t>T-36.3</t>
+        </is>
+      </c>
+      <c r="B343" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C343" s="14" t="inlineStr"/>
+      <c r="D343" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Probar el alta de una empresa nueva de punta a punta</t>
+        </is>
+      </c>
+      <c r="E343" s="15" t="inlineStr"/>
+      <c r="F343" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G343" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H343" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I343" s="14" t="inlineStr"/>
+    </row>
+    <row r="344" ht="20" customHeight="1">
+      <c r="A344" s="9" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B342" s="9" t="inlineStr">
+      <c r="B344" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C342" s="9" t="inlineStr">
+      <c r="C344" s="9" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D342" s="9" t="inlineStr">
+      <c r="D344" s="9" t="inlineStr">
         <is>
           <t>Catálogo de servicios que generan ingreso o egreso</t>
         </is>
       </c>
-      <c r="E342" s="10" t="inlineStr">
+      <c r="E344" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F342" s="11" t="n"/>
-      <c r="G342" s="11" t="n"/>
-      <c r="H342" s="11" t="n"/>
-      <c r="I342" s="11" t="n"/>
-    </row>
-    <row r="343" ht="26" customHeight="1">
-      <c r="A343" s="12" t="inlineStr">
+      <c r="F344" s="11" t="n"/>
+      <c r="G344" s="11" t="n"/>
+      <c r="H344" s="11" t="n"/>
+      <c r="I344" s="11" t="n"/>
+    </row>
+    <row r="345" ht="26" customHeight="1">
+      <c r="A345" s="12" t="inlineStr">
         <is>
           <t>HU-47</t>
         </is>
       </c>
-      <c r="B343" s="12" t="inlineStr">
+      <c r="B345" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C343" s="12" t="inlineStr">
+      <c r="C345" s="12" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D343" s="12" t="inlineStr">
+      <c r="D345" s="12" t="inlineStr">
         <is>
           <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
         </is>
       </c>
-      <c r="E343" s="13" t="inlineStr">
+      <c r="E345" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F343" s="13" t="inlineStr">
+      <c r="F345" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G343" s="13" t="inlineStr">
+      <c r="G345" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H343" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I343" s="12" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" s="14" t="inlineStr">
-        <is>
-          <t>T-47.1</t>
-        </is>
-      </c>
-      <c r="B344" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C344" s="14" t="inlineStr"/>
-      <c r="D344" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Reutilizar el modelo de productos agregando la distinción de servicio</t>
-        </is>
-      </c>
-      <c r="E344" s="15" t="inlineStr"/>
-      <c r="F344" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G344" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H344" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I344" s="14" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" s="16" t="inlineStr">
-        <is>
-          <t>T-47.2</t>
-        </is>
-      </c>
-      <c r="B345" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C345" s="16" t="inlineStr"/>
-      <c r="D345" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el alta, la edición y la baja lógica</t>
-        </is>
-      </c>
-      <c r="E345" s="17" t="inlineStr"/>
-      <c r="F345" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G345" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H345" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I345" s="16" t="inlineStr"/>
+      <c r="H345" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I345" s="12" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="14" t="inlineStr">
         <is>
-          <t>T-47.3</t>
+          <t>T-47.1</t>
         </is>
       </c>
       <c r="B346" s="14" t="inlineStr">
@@ -18554,7 +18602,7 @@
       <c r="C346" s="14" t="inlineStr"/>
       <c r="D346" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar la pantalla de servicios</t>
+          <t xml:space="preserve">    Reutilizar el modelo de productos agregando la distinción de servicio</t>
         </is>
       </c>
       <c r="E346" s="15" t="inlineStr"/>
@@ -18578,7 +18626,7 @@
     <row r="347">
       <c r="A347" s="16" t="inlineStr">
         <is>
-          <t>T-47.4</t>
+          <t>T-47.2</t>
         </is>
       </c>
       <c r="B347" s="16" t="inlineStr">
@@ -18589,7 +18637,7 @@
       <c r="C347" s="16" t="inlineStr"/>
       <c r="D347" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Verificar que los servicios no lleven existencias</t>
+          <t xml:space="preserve">    Programar el alta, la edición y la baja lógica</t>
         </is>
       </c>
       <c r="E347" s="17" t="inlineStr"/>
@@ -18610,123 +18658,123 @@
       </c>
       <c r="I347" s="16" t="inlineStr"/>
     </row>
-    <row r="348" ht="26" customHeight="1">
-      <c r="A348" s="12" t="inlineStr">
+    <row r="348">
+      <c r="A348" s="14" t="inlineStr">
+        <is>
+          <t>T-47.3</t>
+        </is>
+      </c>
+      <c r="B348" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C348" s="14" t="inlineStr"/>
+      <c r="D348" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar la pantalla de servicios</t>
+        </is>
+      </c>
+      <c r="E348" s="15" t="inlineStr"/>
+      <c r="F348" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G348" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H348" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I348" s="14" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="16" t="inlineStr">
+        <is>
+          <t>T-47.4</t>
+        </is>
+      </c>
+      <c r="B349" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C349" s="16" t="inlineStr"/>
+      <c r="D349" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Verificar que los servicios no lleven existencias</t>
+        </is>
+      </c>
+      <c r="E349" s="17" t="inlineStr"/>
+      <c r="F349" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G349" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H349" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I349" s="16" t="inlineStr"/>
+    </row>
+    <row r="350" ht="26" customHeight="1">
+      <c r="A350" s="12" t="inlineStr">
         <is>
           <t>HU-48</t>
         </is>
       </c>
-      <c r="B348" s="12" t="inlineStr">
+      <c r="B350" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C348" s="12" t="inlineStr">
+      <c r="C350" s="12" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D348" s="12" t="inlineStr">
+      <c r="D350" s="12" t="inlineStr">
         <is>
           <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
         </is>
       </c>
-      <c r="E348" s="13" t="inlineStr">
+      <c r="E350" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F348" s="13" t="inlineStr">
+      <c r="F350" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G348" s="13" t="inlineStr">
+      <c r="G350" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H348" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I348" s="12" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" s="14" t="inlineStr">
-        <is>
-          <t>T-48.1</t>
-        </is>
-      </c>
-      <c r="B349" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C349" s="14" t="inlineStr"/>
-      <c r="D349" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Vincular el movimiento económico con el servicio</t>
-        </is>
-      </c>
-      <c r="E349" s="15" t="inlineStr"/>
-      <c r="F349" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G349" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H349" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I349" s="14" t="inlineStr"/>
-    </row>
-    <row r="350">
-      <c r="A350" s="16" t="inlineStr">
-        <is>
-          <t>T-48.2</t>
-        </is>
-      </c>
-      <c r="B350" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C350" s="16" t="inlineStr"/>
-      <c r="D350" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agregar el servicio al formulario de movimiento</t>
-        </is>
-      </c>
-      <c r="E350" s="17" t="inlineStr"/>
-      <c r="F350" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G350" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H350" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I350" s="16" t="inlineStr"/>
+      <c r="H350" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I350" s="12" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="14" t="inlineStr">
         <is>
-          <t>T-48.3</t>
+          <t>T-48.1</t>
         </is>
       </c>
       <c r="B351" s="14" t="inlineStr">
@@ -18737,7 +18785,7 @@
       <c r="C351" s="14" t="inlineStr"/>
       <c r="D351" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Agregar el filtro por servicio en el listado</t>
+          <t xml:space="preserve">    Vincular el movimiento económico con el servicio</t>
         </is>
       </c>
       <c r="E351" s="15" t="inlineStr"/>
@@ -18758,53 +18806,45 @@
       </c>
       <c r="I351" s="14" t="inlineStr"/>
     </row>
-    <row r="352" ht="16" customHeight="1">
-      <c r="A352" s="12" t="inlineStr">
-        <is>
-          <t>HU-49</t>
-        </is>
-      </c>
-      <c r="B352" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C352" s="12" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D352" s="12" t="inlineStr">
-        <is>
-          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
-        </is>
-      </c>
-      <c r="E352" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F352" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G352" s="13" t="inlineStr">
+    <row r="352">
+      <c r="A352" s="16" t="inlineStr">
+        <is>
+          <t>T-48.2</t>
+        </is>
+      </c>
+      <c r="B352" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C352" s="16" t="inlineStr"/>
+      <c r="D352" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agregar el servicio al formulario de movimiento</t>
+        </is>
+      </c>
+      <c r="E352" s="17" t="inlineStr"/>
+      <c r="F352" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G352" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H352" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I352" s="12" t="inlineStr"/>
+      <c r="H352" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I352" s="16" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="14" t="inlineStr">
         <is>
-          <t>T-49.1</t>
+          <t>T-48.3</t>
         </is>
       </c>
       <c r="B353" s="14" t="inlineStr">
@@ -18815,210 +18855,218 @@
       <c r="C353" s="14" t="inlineStr"/>
       <c r="D353" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar la consulta agrupada por servicio</t>
+          <t xml:space="preserve">    Agregar el filtro por servicio en el listado</t>
         </is>
       </c>
       <c r="E353" s="15" t="inlineStr"/>
       <c r="F353" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G353" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H353" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I353" s="14" t="inlineStr"/>
+    </row>
+    <row r="354" ht="16" customHeight="1">
+      <c r="A354" s="12" t="inlineStr">
+        <is>
+          <t>HU-49</t>
+        </is>
+      </c>
+      <c r="B354" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C354" s="12" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D354" s="12" t="inlineStr">
+        <is>
+          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
+        </is>
+      </c>
+      <c r="E354" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F354" s="13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G353" s="15" t="inlineStr">
+      <c r="G354" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H353" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I353" s="14" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" s="16" t="inlineStr">
+      <c r="H354" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I354" s="12" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="14" t="inlineStr">
+        <is>
+          <t>T-49.1</t>
+        </is>
+      </c>
+      <c r="B355" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C355" s="14" t="inlineStr"/>
+      <c r="D355" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar la consulta agrupada por servicio</t>
+        </is>
+      </c>
+      <c r="E355" s="15" t="inlineStr"/>
+      <c r="F355" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G355" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H355" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I355" s="14" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="16" t="inlineStr">
         <is>
           <t>T-49.2</t>
         </is>
       </c>
-      <c r="B354" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C354" s="16" t="inlineStr"/>
-      <c r="D354" s="16" t="inlineStr">
+      <c r="B356" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C356" s="16" t="inlineStr"/>
+      <c r="D356" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar la visualización del resumen</t>
         </is>
       </c>
-      <c r="E354" s="17" t="inlineStr"/>
-      <c r="F354" s="17" t="inlineStr">
+      <c r="E356" s="17" t="inlineStr"/>
+      <c r="F356" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G354" s="17" t="inlineStr">
+      <c r="G356" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H354" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I354" s="16" t="inlineStr"/>
-    </row>
-    <row r="355" ht="20" customHeight="1">
-      <c r="A355" s="9" t="inlineStr">
+      <c r="H356" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I356" s="16" t="inlineStr"/>
+    </row>
+    <row r="357" ht="20" customHeight="1">
+      <c r="A357" s="9" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B355" s="9" t="inlineStr">
+      <c r="B357" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C355" s="9" t="inlineStr">
+      <c r="C357" s="9" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D355" s="9" t="inlineStr">
+      <c r="D357" s="9" t="inlineStr">
         <is>
           <t>Vacaciones, licencias y documentación del personal (backlog futuro)</t>
         </is>
       </c>
-      <c r="E355" s="10" t="inlineStr">
+      <c r="E357" s="10" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F355" s="11" t="n"/>
-      <c r="G355" s="11" t="n"/>
-      <c r="H355" s="11" t="n"/>
-      <c r="I355" s="11" t="n"/>
-    </row>
-    <row r="356" ht="16" customHeight="1">
-      <c r="A356" s="12" t="inlineStr">
+      <c r="F357" s="11" t="n"/>
+      <c r="G357" s="11" t="n"/>
+      <c r="H357" s="11" t="n"/>
+      <c r="I357" s="11" t="n"/>
+    </row>
+    <row r="358" ht="16" customHeight="1">
+      <c r="A358" s="12" t="inlineStr">
         <is>
           <t>HU-68</t>
         </is>
       </c>
-      <c r="B356" s="12" t="inlineStr">
+      <c r="B358" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C356" s="12" t="inlineStr">
+      <c r="C358" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D356" s="12" t="inlineStr">
+      <c r="D358" s="12" t="inlineStr">
         <is>
           <t>Como empleado quiero solicitar días de vacaciones para gestionarlos sin papeles.</t>
         </is>
       </c>
-      <c r="E356" s="13" t="inlineStr">
+      <c r="E358" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F356" s="13" t="inlineStr">
+      <c r="F358" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G356" s="13" t="inlineStr">
+      <c r="G358" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H356" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I356" s="12" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" s="14" t="inlineStr">
-        <is>
-          <t>T-68.1</t>
-        </is>
-      </c>
-      <c r="B357" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C357" s="14" t="inlineStr"/>
-      <c r="D357" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Diseñar el modelo de licencias y saldo de días</t>
-        </is>
-      </c>
-      <c r="E357" s="15" t="inlineStr"/>
-      <c r="F357" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G357" s="15" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H357" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I357" s="14" t="inlineStr"/>
-    </row>
-    <row r="358">
-      <c r="A358" s="16" t="inlineStr">
-        <is>
-          <t>T-68.2</t>
-        </is>
-      </c>
-      <c r="B358" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C358" s="16" t="inlineStr"/>
-      <c r="D358" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el circuito de solicitud y aprobación</t>
-        </is>
-      </c>
-      <c r="E358" s="17" t="inlineStr"/>
-      <c r="F358" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G358" s="17" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H358" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I358" s="16" t="inlineStr"/>
+      <c r="H358" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I358" s="12" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="14" t="inlineStr">
         <is>
-          <t>T-68.3</t>
+          <t>T-68.1</t>
         </is>
       </c>
       <c r="B359" s="14" t="inlineStr">
@@ -19029,7 +19077,7 @@
       <c r="C359" s="14" t="inlineStr"/>
       <c r="D359" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar las pantallas de solicitud y de bandeja del responsable</t>
+          <t xml:space="preserve">    Diseñar el modelo de licencias y saldo de días</t>
         </is>
       </c>
       <c r="E359" s="15" t="inlineStr"/>
@@ -19053,7 +19101,7 @@
     <row r="360">
       <c r="A360" s="16" t="inlineStr">
         <is>
-          <t>T-68.4</t>
+          <t>T-68.2</t>
         </is>
       </c>
       <c r="B360" s="16" t="inlineStr">
@@ -19064,7 +19112,7 @@
       <c r="C360" s="16" t="inlineStr"/>
       <c r="D360" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar el cálculo del saldo de días</t>
+          <t xml:space="preserve">    Programar el circuito de solicitud y aprobación</t>
         </is>
       </c>
       <c r="E360" s="17" t="inlineStr"/>
@@ -19085,123 +19133,123 @@
       </c>
       <c r="I360" s="16" t="inlineStr"/>
     </row>
-    <row r="361" ht="16" customHeight="1">
-      <c r="A361" s="12" t="inlineStr">
+    <row r="361">
+      <c r="A361" s="14" t="inlineStr">
+        <is>
+          <t>T-68.3</t>
+        </is>
+      </c>
+      <c r="B361" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C361" s="14" t="inlineStr"/>
+      <c r="D361" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar las pantallas de solicitud y de bandeja del responsable</t>
+        </is>
+      </c>
+      <c r="E361" s="15" t="inlineStr"/>
+      <c r="F361" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G361" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H361" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I361" s="14" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="16" t="inlineStr">
+        <is>
+          <t>T-68.4</t>
+        </is>
+      </c>
+      <c r="B362" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C362" s="16" t="inlineStr"/>
+      <c r="D362" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar el cálculo del saldo de días</t>
+        </is>
+      </c>
+      <c r="E362" s="17" t="inlineStr"/>
+      <c r="F362" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G362" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H362" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I362" s="16" t="inlineStr"/>
+    </row>
+    <row r="363" ht="16" customHeight="1">
+      <c r="A363" s="12" t="inlineStr">
         <is>
           <t>HU-69</t>
         </is>
       </c>
-      <c r="B361" s="12" t="inlineStr">
+      <c r="B363" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C361" s="12" t="inlineStr">
+      <c r="C363" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D361" s="12" t="inlineStr">
+      <c r="D363" s="12" t="inlineStr">
         <is>
           <t>Como empleado quiero subir mi orden médica para justificar una ausencia.</t>
         </is>
       </c>
-      <c r="E361" s="13" t="inlineStr">
+      <c r="E363" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F361" s="13" t="inlineStr">
+      <c r="F363" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G361" s="13" t="inlineStr">
+      <c r="G363" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H361" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I361" s="12" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" s="14" t="inlineStr">
-        <is>
-          <t>T-69.1</t>
-        </is>
-      </c>
-      <c r="B362" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C362" s="14" t="inlineStr"/>
-      <c r="D362" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Definir el almacenamiento local de archivos adjuntos</t>
-        </is>
-      </c>
-      <c r="E362" s="15" t="inlineStr"/>
-      <c r="F362" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G362" s="15" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H362" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I362" s="14" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" s="16" t="inlineStr">
-        <is>
-          <t>T-69.2</t>
-        </is>
-      </c>
-      <c r="B363" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C363" s="16" t="inlineStr"/>
-      <c r="D363" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar la subida con validación de tipo y tamaño</t>
-        </is>
-      </c>
-      <c r="E363" s="17" t="inlineStr"/>
-      <c r="F363" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G363" s="17" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H363" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I363" s="16" t="inlineStr"/>
+      <c r="H363" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I363" s="12" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="14" t="inlineStr">
         <is>
-          <t>T-69.3</t>
+          <t>T-69.1</t>
         </is>
       </c>
       <c r="B364" s="14" t="inlineStr">
@@ -19212,7 +19260,7 @@
       <c r="C364" s="14" t="inlineStr"/>
       <c r="D364" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Restringir la visibilidad del archivo</t>
+          <t xml:space="preserve">    Definir el almacenamiento local de archivos adjuntos</t>
         </is>
       </c>
       <c r="E364" s="15" t="inlineStr"/>
@@ -19236,7 +19284,7 @@
     <row r="365">
       <c r="A365" s="16" t="inlineStr">
         <is>
-          <t>T-69.4</t>
+          <t>T-69.2</t>
         </is>
       </c>
       <c r="B365" s="16" t="inlineStr">
@@ -19247,7 +19295,7 @@
       <c r="C365" s="16" t="inlineStr"/>
       <c r="D365" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el tratamiento de los datos de salud</t>
+          <t xml:space="preserve">    Programar la subida con validación de tipo y tamaño</t>
         </is>
       </c>
       <c r="E365" s="17" t="inlineStr"/>
@@ -19268,126 +19316,196 @@
       </c>
       <c r="I365" s="16" t="inlineStr"/>
     </row>
-    <row r="366" ht="16" customHeight="1">
-      <c r="A366" s="12" t="inlineStr">
+    <row r="366">
+      <c r="A366" s="14" t="inlineStr">
+        <is>
+          <t>T-69.3</t>
+        </is>
+      </c>
+      <c r="B366" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C366" s="14" t="inlineStr"/>
+      <c r="D366" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Restringir la visibilidad del archivo</t>
+        </is>
+      </c>
+      <c r="E366" s="15" t="inlineStr"/>
+      <c r="F366" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G366" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H366" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I366" s="14" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="16" t="inlineStr">
+        <is>
+          <t>T-69.4</t>
+        </is>
+      </c>
+      <c r="B367" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C367" s="16" t="inlineStr"/>
+      <c r="D367" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Definir el tratamiento de los datos de salud</t>
+        </is>
+      </c>
+      <c r="E367" s="17" t="inlineStr"/>
+      <c r="F367" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G367" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H367" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I367" s="16" t="inlineStr"/>
+    </row>
+    <row r="368" ht="16" customHeight="1">
+      <c r="A368" s="12" t="inlineStr">
         <is>
           <t>HU-70</t>
         </is>
       </c>
-      <c r="B366" s="12" t="inlineStr">
+      <c r="B368" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C366" s="12" t="inlineStr">
+      <c r="C368" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D366" s="12" t="inlineStr">
+      <c r="D368" s="12" t="inlineStr">
         <is>
           <t>Como área de personal quiero ver el calendario de ausencias para organizar la cobertura.</t>
         </is>
       </c>
-      <c r="E366" s="13" t="inlineStr">
+      <c r="E368" s="13" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F366" s="13" t="inlineStr">
+      <c r="F368" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G366" s="13" t="inlineStr">
+      <c r="G368" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H366" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I366" s="12" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" s="14" t="inlineStr">
+      <c r="H368" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I368" s="12" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="14" t="inlineStr">
         <is>
           <t>T-70.1</t>
         </is>
       </c>
-      <c r="B367" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C367" s="14" t="inlineStr"/>
-      <c r="D367" s="14" t="inlineStr">
+      <c r="B369" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C369" s="14" t="inlineStr"/>
+      <c r="D369" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar el calendario de ausencias</t>
         </is>
       </c>
-      <c r="E367" s="15" t="inlineStr"/>
-      <c r="F367" s="15" t="inlineStr">
+      <c r="E369" s="15" t="inlineStr"/>
+      <c r="F369" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G367" s="15" t="inlineStr">
+      <c r="G369" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H367" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I367" s="14" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" s="16" t="inlineStr">
+      <c r="H369" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I369" s="14" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="16" t="inlineStr">
         <is>
           <t>T-70.2</t>
         </is>
       </c>
-      <c r="B368" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C368" s="16" t="inlineStr"/>
-      <c r="D368" s="16" t="inlineStr">
+      <c r="B370" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C370" s="16" t="inlineStr"/>
+      <c r="D370" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar la consulta por período</t>
         </is>
       </c>
-      <c r="E368" s="17" t="inlineStr"/>
-      <c r="F368" s="17" t="inlineStr">
+      <c r="E370" s="17" t="inlineStr"/>
+      <c r="F370" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G368" s="17" t="inlineStr">
+      <c r="G370" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H368" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I368" s="16" t="inlineStr"/>
+      <c r="H370" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I370" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I368"/>
+  <autoFilter ref="A4:I370"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H368">
+  <conditionalFormatting sqref="H5:H370">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -19402,13 +19520,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H5:H368" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H370" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E368" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E370" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I368" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I370" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19710,11 +19828,11 @@
         <v>6</v>
       </c>
       <c r="E10" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 06'!A6:A36,2)="T-")*1)</f>
+        <f>SUMPRODUCT((LEFT('Sprint 06'!A6:A38,2)="T-")*1)</f>
         <v/>
       </c>
       <c r="F10" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 06'!A6:A36,2)="T-")*('Sprint 06'!E6:E36="Hecho"))</f>
+        <f>SUMPRODUCT((LEFT('Sprint 06'!A6:A38,2)="T-")*('Sprint 06'!E6:E38="Hecho"))</f>
         <v/>
       </c>
       <c r="G10" s="18">
@@ -24147,7 +24265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24632,10 +24750,14 @@
           <t>Configuración de Módulos</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr"/>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -24651,10 +24773,14 @@
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -24670,10 +24796,14 @@
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr"/>
-      <c r="D25" s="16" t="inlineStr"/>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -24689,10 +24819,14 @@
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -24708,10 +24842,14 @@
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr"/>
-      <c r="D27" s="16" t="inlineStr"/>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E27" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -24727,10 +24865,14 @@
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr"/>
-      <c r="D28" s="14" t="inlineStr"/>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -24750,10 +24892,14 @@
           <t>Configuración de Módulos</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr"/>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -24769,10 +24915,14 @@
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr"/>
-      <c r="D30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -24784,14 +24934,18 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Aplicarlo a las rutas de cada módulo</t>
+          <t xml:space="preserve">     Aplicarlo a las rutas de movimientos y categorías</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr"/>
-      <c r="D31" s="16" t="inlineStr"/>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -24803,73 +24957,85 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Probar el acceso con el módulo apagado</t>
+          <t xml:space="preserve">     Mostrar en pantalla un aviso claro cuando el módulo está apagado</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr"/>
-      <c r="D32" s="14" t="inlineStr"/>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>HU-36</t>
-        </is>
-      </c>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>Como empresa nueva quiero empezar con una configuración razonable para no tener que definir todo antes de usar el sistema.</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>Configuración de Módulos</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr"/>
-      <c r="E33" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>T-35.4</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Distinguir el aviso de módulo apagado del de falta de permiso</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr"/>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>T-36.1</t>
+          <t>T-35.5</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Definir el conjunto de módulos y categorías iniciales</t>
+          <t xml:space="preserve">     Probar el acceso con el módulo apagado</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr"/>
-      <c r="D34" s="14" t="inlineStr"/>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>T-36.2</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Programar la carga automática al aprobar la empresa</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr"/>
-      <c r="D35" s="16" t="inlineStr"/>
-      <c r="E35" s="17" t="inlineStr">
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>HU-36</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Como empresa nueva quiero empezar con una configuración razonable para no tener que definir todo antes de usar el sistema.</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Configuración de Módulos</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr"/>
+      <c r="E35" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -24878,12 +25044,12 @@
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>T-36.3</t>
+          <t>T-36.1</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Probar el alta de una empresa nueva de punta a punta</t>
+          <t xml:space="preserve">     Definir el conjunto de módulos y categorías iniciales</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr"/>
@@ -24894,15 +25060,53 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>T-36.2</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Programar la carga automática al aprobar la empresa</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr"/>
+      <c r="D37" s="16" t="inlineStr"/>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
     <row r="38">
-      <c r="C38" s="19" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>T-36.3</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Probar el alta de una empresa nueva de punta a punta</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr"/>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>AVANCE DEL SPRINT (tareas terminadas)</t>
         </is>
       </c>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="20">
-        <f>TEXT(SUMPRODUCT((LEFT(A6:A36,2)="T-")*(E6:E36="Hecho"))/SUMPRODUCT((LEFT(A6:A36,2)="T-")*1),"0%")</f>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20">
+        <f>TEXT(SUMPRODUCT((LEFT(A6:A38,2)="T-")*(E6:E38="Hecho"))/SUMPRODUCT((LEFT(A6:A38,2)="T-")*1),"0%")</f>
         <v/>
       </c>
     </row>
@@ -24912,7 +25116,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E36">
+  <conditionalFormatting sqref="E6:E38">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -24927,10 +25131,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E6:E36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:D36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -28,7 +28,7 @@
     <sheet name="Cambios vs. original" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$370</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$372</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5314,7 +5314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I370"/>
+  <dimension ref="A1:I372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18404,10 +18404,14 @@
       </c>
       <c r="H340" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I340" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I340" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="14" t="inlineStr">
@@ -18439,10 +18443,14 @@
       </c>
       <c r="H341" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I341" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I341" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="16" t="inlineStr">
@@ -18474,10 +18482,14 @@
       </c>
       <c r="H342" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I342" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I342" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="14" t="inlineStr">
@@ -18493,7 +18505,7 @@
       <c r="C343" s="14" t="inlineStr"/>
       <c r="D343" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Probar el alta de una empresa nueva de punta a punta</t>
+          <t xml:space="preserve">    Dejar la configuración escrita en la base, no deducida del catálogo</t>
         </is>
       </c>
       <c r="E343" s="15" t="inlineStr"/>
@@ -18509,159 +18521,171 @@
       </c>
       <c r="H343" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I343" s="14" t="inlineStr"/>
-    </row>
-    <row r="344" ht="20" customHeight="1">
-      <c r="A344" s="9" t="inlineStr">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I343" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="16" t="inlineStr">
+        <is>
+          <t>T-36.4</t>
+        </is>
+      </c>
+      <c r="B344" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C344" s="16" t="inlineStr"/>
+      <c r="D344" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Evitar que una segunda aprobación duplique o pise lo ya configurado</t>
+        </is>
+      </c>
+      <c r="E344" s="17" t="inlineStr"/>
+      <c r="F344" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G344" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H344" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I344" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="14" t="inlineStr">
+        <is>
+          <t>T-36.5</t>
+        </is>
+      </c>
+      <c r="B345" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C345" s="14" t="inlineStr"/>
+      <c r="D345" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Probar el alta de una empresa nueva de punta a punta</t>
+        </is>
+      </c>
+      <c r="E345" s="15" t="inlineStr"/>
+      <c r="F345" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G345" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H345" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I345" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="20" customHeight="1">
+      <c r="A346" s="9" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B344" s="9" t="inlineStr">
+      <c r="B346" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C344" s="9" t="inlineStr">
+      <c r="C346" s="9" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D344" s="9" t="inlineStr">
+      <c r="D346" s="9" t="inlineStr">
         <is>
           <t>Catálogo de servicios que generan ingreso o egreso</t>
         </is>
       </c>
-      <c r="E344" s="10" t="inlineStr">
+      <c r="E346" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F344" s="11" t="n"/>
-      <c r="G344" s="11" t="n"/>
-      <c r="H344" s="11" t="n"/>
-      <c r="I344" s="11" t="n"/>
-    </row>
-    <row r="345" ht="26" customHeight="1">
-      <c r="A345" s="12" t="inlineStr">
+      <c r="F346" s="11" t="n"/>
+      <c r="G346" s="11" t="n"/>
+      <c r="H346" s="11" t="n"/>
+      <c r="I346" s="11" t="n"/>
+    </row>
+    <row r="347" ht="26" customHeight="1">
+      <c r="A347" s="12" t="inlineStr">
         <is>
           <t>HU-47</t>
         </is>
       </c>
-      <c r="B345" s="12" t="inlineStr">
+      <c r="B347" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C345" s="12" t="inlineStr">
+      <c r="C347" s="12" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D345" s="12" t="inlineStr">
+      <c r="D347" s="12" t="inlineStr">
         <is>
           <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
         </is>
       </c>
-      <c r="E345" s="13" t="inlineStr">
+      <c r="E347" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F345" s="13" t="inlineStr">
+      <c r="F347" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G345" s="13" t="inlineStr">
+      <c r="G347" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H345" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I345" s="12" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" s="14" t="inlineStr">
-        <is>
-          <t>T-47.1</t>
-        </is>
-      </c>
-      <c r="B346" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C346" s="14" t="inlineStr"/>
-      <c r="D346" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Reutilizar el modelo de productos agregando la distinción de servicio</t>
-        </is>
-      </c>
-      <c r="E346" s="15" t="inlineStr"/>
-      <c r="F346" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G346" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H346" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I346" s="14" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" s="16" t="inlineStr">
-        <is>
-          <t>T-47.2</t>
-        </is>
-      </c>
-      <c r="B347" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C347" s="16" t="inlineStr"/>
-      <c r="D347" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el alta, la edición y la baja lógica</t>
-        </is>
-      </c>
-      <c r="E347" s="17" t="inlineStr"/>
-      <c r="F347" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G347" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H347" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I347" s="16" t="inlineStr"/>
+      <c r="H347" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I347" s="12" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="14" t="inlineStr">
         <is>
-          <t>T-47.3</t>
+          <t>T-47.1</t>
         </is>
       </c>
       <c r="B348" s="14" t="inlineStr">
@@ -18672,7 +18696,7 @@
       <c r="C348" s="14" t="inlineStr"/>
       <c r="D348" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar la pantalla de servicios</t>
+          <t xml:space="preserve">    Reutilizar el modelo de productos agregando la distinción de servicio</t>
         </is>
       </c>
       <c r="E348" s="15" t="inlineStr"/>
@@ -18696,7 +18720,7 @@
     <row r="349">
       <c r="A349" s="16" t="inlineStr">
         <is>
-          <t>T-47.4</t>
+          <t>T-47.2</t>
         </is>
       </c>
       <c r="B349" s="16" t="inlineStr">
@@ -18707,7 +18731,7 @@
       <c r="C349" s="16" t="inlineStr"/>
       <c r="D349" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Verificar que los servicios no lleven existencias</t>
+          <t xml:space="preserve">    Programar el alta, la edición y la baja lógica</t>
         </is>
       </c>
       <c r="E349" s="17" t="inlineStr"/>
@@ -18728,123 +18752,123 @@
       </c>
       <c r="I349" s="16" t="inlineStr"/>
     </row>
-    <row r="350" ht="26" customHeight="1">
-      <c r="A350" s="12" t="inlineStr">
+    <row r="350">
+      <c r="A350" s="14" t="inlineStr">
+        <is>
+          <t>T-47.3</t>
+        </is>
+      </c>
+      <c r="B350" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C350" s="14" t="inlineStr"/>
+      <c r="D350" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar la pantalla de servicios</t>
+        </is>
+      </c>
+      <c r="E350" s="15" t="inlineStr"/>
+      <c r="F350" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G350" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H350" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I350" s="14" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="16" t="inlineStr">
+        <is>
+          <t>T-47.4</t>
+        </is>
+      </c>
+      <c r="B351" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C351" s="16" t="inlineStr"/>
+      <c r="D351" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Verificar que los servicios no lleven existencias</t>
+        </is>
+      </c>
+      <c r="E351" s="17" t="inlineStr"/>
+      <c r="F351" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G351" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H351" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I351" s="16" t="inlineStr"/>
+    </row>
+    <row r="352" ht="26" customHeight="1">
+      <c r="A352" s="12" t="inlineStr">
         <is>
           <t>HU-48</t>
         </is>
       </c>
-      <c r="B350" s="12" t="inlineStr">
+      <c r="B352" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C350" s="12" t="inlineStr">
+      <c r="C352" s="12" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D350" s="12" t="inlineStr">
+      <c r="D352" s="12" t="inlineStr">
         <is>
           <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
         </is>
       </c>
-      <c r="E350" s="13" t="inlineStr">
+      <c r="E352" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F350" s="13" t="inlineStr">
+      <c r="F352" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G350" s="13" t="inlineStr">
+      <c r="G352" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H350" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I350" s="12" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" s="14" t="inlineStr">
-        <is>
-          <t>T-48.1</t>
-        </is>
-      </c>
-      <c r="B351" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C351" s="14" t="inlineStr"/>
-      <c r="D351" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Vincular el movimiento económico con el servicio</t>
-        </is>
-      </c>
-      <c r="E351" s="15" t="inlineStr"/>
-      <c r="F351" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G351" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H351" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I351" s="14" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="16" t="inlineStr">
-        <is>
-          <t>T-48.2</t>
-        </is>
-      </c>
-      <c r="B352" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C352" s="16" t="inlineStr"/>
-      <c r="D352" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agregar el servicio al formulario de movimiento</t>
-        </is>
-      </c>
-      <c r="E352" s="17" t="inlineStr"/>
-      <c r="F352" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G352" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H352" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I352" s="16" t="inlineStr"/>
+      <c r="H352" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I352" s="12" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="14" t="inlineStr">
         <is>
-          <t>T-48.3</t>
+          <t>T-48.1</t>
         </is>
       </c>
       <c r="B353" s="14" t="inlineStr">
@@ -18855,7 +18879,7 @@
       <c r="C353" s="14" t="inlineStr"/>
       <c r="D353" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Agregar el filtro por servicio en el listado</t>
+          <t xml:space="preserve">    Vincular el movimiento económico con el servicio</t>
         </is>
       </c>
       <c r="E353" s="15" t="inlineStr"/>
@@ -18876,53 +18900,45 @@
       </c>
       <c r="I353" s="14" t="inlineStr"/>
     </row>
-    <row r="354" ht="16" customHeight="1">
-      <c r="A354" s="12" t="inlineStr">
-        <is>
-          <t>HU-49</t>
-        </is>
-      </c>
-      <c r="B354" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C354" s="12" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D354" s="12" t="inlineStr">
-        <is>
-          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
-        </is>
-      </c>
-      <c r="E354" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F354" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G354" s="13" t="inlineStr">
+    <row r="354">
+      <c r="A354" s="16" t="inlineStr">
+        <is>
+          <t>T-48.2</t>
+        </is>
+      </c>
+      <c r="B354" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C354" s="16" t="inlineStr"/>
+      <c r="D354" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agregar el servicio al formulario de movimiento</t>
+        </is>
+      </c>
+      <c r="E354" s="17" t="inlineStr"/>
+      <c r="F354" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G354" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H354" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I354" s="12" t="inlineStr"/>
+      <c r="H354" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I354" s="16" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="14" t="inlineStr">
         <is>
-          <t>T-49.1</t>
+          <t>T-48.3</t>
         </is>
       </c>
       <c r="B355" s="14" t="inlineStr">
@@ -18933,210 +18949,218 @@
       <c r="C355" s="14" t="inlineStr"/>
       <c r="D355" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar la consulta agrupada por servicio</t>
+          <t xml:space="preserve">    Agregar el filtro por servicio en el listado</t>
         </is>
       </c>
       <c r="E355" s="15" t="inlineStr"/>
       <c r="F355" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G355" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H355" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I355" s="14" t="inlineStr"/>
+    </row>
+    <row r="356" ht="16" customHeight="1">
+      <c r="A356" s="12" t="inlineStr">
+        <is>
+          <t>HU-49</t>
+        </is>
+      </c>
+      <c r="B356" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C356" s="12" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D356" s="12" t="inlineStr">
+        <is>
+          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
+        </is>
+      </c>
+      <c r="E356" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F356" s="13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G355" s="15" t="inlineStr">
+      <c r="G356" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H355" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I355" s="14" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" s="16" t="inlineStr">
+      <c r="H356" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I356" s="12" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="14" t="inlineStr">
+        <is>
+          <t>T-49.1</t>
+        </is>
+      </c>
+      <c r="B357" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C357" s="14" t="inlineStr"/>
+      <c r="D357" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar la consulta agrupada por servicio</t>
+        </is>
+      </c>
+      <c r="E357" s="15" t="inlineStr"/>
+      <c r="F357" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G357" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H357" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I357" s="14" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="16" t="inlineStr">
         <is>
           <t>T-49.2</t>
         </is>
       </c>
-      <c r="B356" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C356" s="16" t="inlineStr"/>
-      <c r="D356" s="16" t="inlineStr">
+      <c r="B358" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C358" s="16" t="inlineStr"/>
+      <c r="D358" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar la visualización del resumen</t>
         </is>
       </c>
-      <c r="E356" s="17" t="inlineStr"/>
-      <c r="F356" s="17" t="inlineStr">
+      <c r="E358" s="17" t="inlineStr"/>
+      <c r="F358" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G356" s="17" t="inlineStr">
+      <c r="G358" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H356" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I356" s="16" t="inlineStr"/>
-    </row>
-    <row r="357" ht="20" customHeight="1">
-      <c r="A357" s="9" t="inlineStr">
+      <c r="H358" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I358" s="16" t="inlineStr"/>
+    </row>
+    <row r="359" ht="20" customHeight="1">
+      <c r="A359" s="9" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B357" s="9" t="inlineStr">
+      <c r="B359" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C357" s="9" t="inlineStr">
+      <c r="C359" s="9" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D357" s="9" t="inlineStr">
+      <c r="D359" s="9" t="inlineStr">
         <is>
           <t>Vacaciones, licencias y documentación del personal (backlog futuro)</t>
         </is>
       </c>
-      <c r="E357" s="10" t="inlineStr">
+      <c r="E359" s="10" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F357" s="11" t="n"/>
-      <c r="G357" s="11" t="n"/>
-      <c r="H357" s="11" t="n"/>
-      <c r="I357" s="11" t="n"/>
-    </row>
-    <row r="358" ht="16" customHeight="1">
-      <c r="A358" s="12" t="inlineStr">
+      <c r="F359" s="11" t="n"/>
+      <c r="G359" s="11" t="n"/>
+      <c r="H359" s="11" t="n"/>
+      <c r="I359" s="11" t="n"/>
+    </row>
+    <row r="360" ht="16" customHeight="1">
+      <c r="A360" s="12" t="inlineStr">
         <is>
           <t>HU-68</t>
         </is>
       </c>
-      <c r="B358" s="12" t="inlineStr">
+      <c r="B360" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C358" s="12" t="inlineStr">
+      <c r="C360" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D358" s="12" t="inlineStr">
+      <c r="D360" s="12" t="inlineStr">
         <is>
           <t>Como empleado quiero solicitar días de vacaciones para gestionarlos sin papeles.</t>
         </is>
       </c>
-      <c r="E358" s="13" t="inlineStr">
+      <c r="E360" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F358" s="13" t="inlineStr">
+      <c r="F360" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G358" s="13" t="inlineStr">
+      <c r="G360" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H358" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I358" s="12" t="inlineStr"/>
-    </row>
-    <row r="359">
-      <c r="A359" s="14" t="inlineStr">
-        <is>
-          <t>T-68.1</t>
-        </is>
-      </c>
-      <c r="B359" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C359" s="14" t="inlineStr"/>
-      <c r="D359" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Diseñar el modelo de licencias y saldo de días</t>
-        </is>
-      </c>
-      <c r="E359" s="15" t="inlineStr"/>
-      <c r="F359" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G359" s="15" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H359" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I359" s="14" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" s="16" t="inlineStr">
-        <is>
-          <t>T-68.2</t>
-        </is>
-      </c>
-      <c r="B360" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C360" s="16" t="inlineStr"/>
-      <c r="D360" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el circuito de solicitud y aprobación</t>
-        </is>
-      </c>
-      <c r="E360" s="17" t="inlineStr"/>
-      <c r="F360" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G360" s="17" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H360" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I360" s="16" t="inlineStr"/>
+      <c r="H360" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I360" s="12" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="14" t="inlineStr">
         <is>
-          <t>T-68.3</t>
+          <t>T-68.1</t>
         </is>
       </c>
       <c r="B361" s="14" t="inlineStr">
@@ -19147,7 +19171,7 @@
       <c r="C361" s="14" t="inlineStr"/>
       <c r="D361" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar las pantallas de solicitud y de bandeja del responsable</t>
+          <t xml:space="preserve">    Diseñar el modelo de licencias y saldo de días</t>
         </is>
       </c>
       <c r="E361" s="15" t="inlineStr"/>
@@ -19171,7 +19195,7 @@
     <row r="362">
       <c r="A362" s="16" t="inlineStr">
         <is>
-          <t>T-68.4</t>
+          <t>T-68.2</t>
         </is>
       </c>
       <c r="B362" s="16" t="inlineStr">
@@ -19182,7 +19206,7 @@
       <c r="C362" s="16" t="inlineStr"/>
       <c r="D362" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar el cálculo del saldo de días</t>
+          <t xml:space="preserve">    Programar el circuito de solicitud y aprobación</t>
         </is>
       </c>
       <c r="E362" s="17" t="inlineStr"/>
@@ -19203,123 +19227,123 @@
       </c>
       <c r="I362" s="16" t="inlineStr"/>
     </row>
-    <row r="363" ht="16" customHeight="1">
-      <c r="A363" s="12" t="inlineStr">
+    <row r="363">
+      <c r="A363" s="14" t="inlineStr">
+        <is>
+          <t>T-68.3</t>
+        </is>
+      </c>
+      <c r="B363" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C363" s="14" t="inlineStr"/>
+      <c r="D363" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar las pantallas de solicitud y de bandeja del responsable</t>
+        </is>
+      </c>
+      <c r="E363" s="15" t="inlineStr"/>
+      <c r="F363" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G363" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H363" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I363" s="14" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="16" t="inlineStr">
+        <is>
+          <t>T-68.4</t>
+        </is>
+      </c>
+      <c r="B364" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C364" s="16" t="inlineStr"/>
+      <c r="D364" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar el cálculo del saldo de días</t>
+        </is>
+      </c>
+      <c r="E364" s="17" t="inlineStr"/>
+      <c r="F364" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G364" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H364" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I364" s="16" t="inlineStr"/>
+    </row>
+    <row r="365" ht="16" customHeight="1">
+      <c r="A365" s="12" t="inlineStr">
         <is>
           <t>HU-69</t>
         </is>
       </c>
-      <c r="B363" s="12" t="inlineStr">
+      <c r="B365" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C363" s="12" t="inlineStr">
+      <c r="C365" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D363" s="12" t="inlineStr">
+      <c r="D365" s="12" t="inlineStr">
         <is>
           <t>Como empleado quiero subir mi orden médica para justificar una ausencia.</t>
         </is>
       </c>
-      <c r="E363" s="13" t="inlineStr">
+      <c r="E365" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F363" s="13" t="inlineStr">
+      <c r="F365" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G363" s="13" t="inlineStr">
+      <c r="G365" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H363" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I363" s="12" t="inlineStr"/>
-    </row>
-    <row r="364">
-      <c r="A364" s="14" t="inlineStr">
-        <is>
-          <t>T-69.1</t>
-        </is>
-      </c>
-      <c r="B364" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C364" s="14" t="inlineStr"/>
-      <c r="D364" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Definir el almacenamiento local de archivos adjuntos</t>
-        </is>
-      </c>
-      <c r="E364" s="15" t="inlineStr"/>
-      <c r="F364" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G364" s="15" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H364" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I364" s="14" t="inlineStr"/>
-    </row>
-    <row r="365">
-      <c r="A365" s="16" t="inlineStr">
-        <is>
-          <t>T-69.2</t>
-        </is>
-      </c>
-      <c r="B365" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C365" s="16" t="inlineStr"/>
-      <c r="D365" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar la subida con validación de tipo y tamaño</t>
-        </is>
-      </c>
-      <c r="E365" s="17" t="inlineStr"/>
-      <c r="F365" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G365" s="17" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H365" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I365" s="16" t="inlineStr"/>
+      <c r="H365" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I365" s="12" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="14" t="inlineStr">
         <is>
-          <t>T-69.3</t>
+          <t>T-69.1</t>
         </is>
       </c>
       <c r="B366" s="14" t="inlineStr">
@@ -19330,7 +19354,7 @@
       <c r="C366" s="14" t="inlineStr"/>
       <c r="D366" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Restringir la visibilidad del archivo</t>
+          <t xml:space="preserve">    Definir el almacenamiento local de archivos adjuntos</t>
         </is>
       </c>
       <c r="E366" s="15" t="inlineStr"/>
@@ -19354,7 +19378,7 @@
     <row r="367">
       <c r="A367" s="16" t="inlineStr">
         <is>
-          <t>T-69.4</t>
+          <t>T-69.2</t>
         </is>
       </c>
       <c r="B367" s="16" t="inlineStr">
@@ -19365,7 +19389,7 @@
       <c r="C367" s="16" t="inlineStr"/>
       <c r="D367" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el tratamiento de los datos de salud</t>
+          <t xml:space="preserve">    Programar la subida con validación de tipo y tamaño</t>
         </is>
       </c>
       <c r="E367" s="17" t="inlineStr"/>
@@ -19386,126 +19410,196 @@
       </c>
       <c r="I367" s="16" t="inlineStr"/>
     </row>
-    <row r="368" ht="16" customHeight="1">
-      <c r="A368" s="12" t="inlineStr">
+    <row r="368">
+      <c r="A368" s="14" t="inlineStr">
+        <is>
+          <t>T-69.3</t>
+        </is>
+      </c>
+      <c r="B368" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C368" s="14" t="inlineStr"/>
+      <c r="D368" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Restringir la visibilidad del archivo</t>
+        </is>
+      </c>
+      <c r="E368" s="15" t="inlineStr"/>
+      <c r="F368" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G368" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H368" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I368" s="14" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="16" t="inlineStr">
+        <is>
+          <t>T-69.4</t>
+        </is>
+      </c>
+      <c r="B369" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C369" s="16" t="inlineStr"/>
+      <c r="D369" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Definir el tratamiento de los datos de salud</t>
+        </is>
+      </c>
+      <c r="E369" s="17" t="inlineStr"/>
+      <c r="F369" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G369" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H369" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I369" s="16" t="inlineStr"/>
+    </row>
+    <row r="370" ht="16" customHeight="1">
+      <c r="A370" s="12" t="inlineStr">
         <is>
           <t>HU-70</t>
         </is>
       </c>
-      <c r="B368" s="12" t="inlineStr">
+      <c r="B370" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C368" s="12" t="inlineStr">
+      <c r="C370" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D368" s="12" t="inlineStr">
+      <c r="D370" s="12" t="inlineStr">
         <is>
           <t>Como área de personal quiero ver el calendario de ausencias para organizar la cobertura.</t>
         </is>
       </c>
-      <c r="E368" s="13" t="inlineStr">
+      <c r="E370" s="13" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F368" s="13" t="inlineStr">
+      <c r="F370" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G368" s="13" t="inlineStr">
+      <c r="G370" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H368" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I368" s="12" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" s="14" t="inlineStr">
+      <c r="H370" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I370" s="12" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="14" t="inlineStr">
         <is>
           <t>T-70.1</t>
         </is>
       </c>
-      <c r="B369" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C369" s="14" t="inlineStr"/>
-      <c r="D369" s="14" t="inlineStr">
+      <c r="B371" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C371" s="14" t="inlineStr"/>
+      <c r="D371" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar el calendario de ausencias</t>
         </is>
       </c>
-      <c r="E369" s="15" t="inlineStr"/>
-      <c r="F369" s="15" t="inlineStr">
+      <c r="E371" s="15" t="inlineStr"/>
+      <c r="F371" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G369" s="15" t="inlineStr">
+      <c r="G371" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H369" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I369" s="14" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" s="16" t="inlineStr">
+      <c r="H371" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I371" s="14" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="16" t="inlineStr">
         <is>
           <t>T-70.2</t>
         </is>
       </c>
-      <c r="B370" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C370" s="16" t="inlineStr"/>
-      <c r="D370" s="16" t="inlineStr">
+      <c r="B372" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C372" s="16" t="inlineStr"/>
+      <c r="D372" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar la consulta por período</t>
         </is>
       </c>
-      <c r="E370" s="17" t="inlineStr"/>
-      <c r="F370" s="17" t="inlineStr">
+      <c r="E372" s="17" t="inlineStr"/>
+      <c r="F372" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G370" s="17" t="inlineStr">
+      <c r="G372" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H370" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I370" s="16" t="inlineStr"/>
+      <c r="H372" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I372" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I370"/>
+  <autoFilter ref="A4:I372"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H370">
+  <conditionalFormatting sqref="H5:H372">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -19520,13 +19614,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H5:H370" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H372" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E370" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E372" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I370" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I372" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19828,11 +19922,11 @@
         <v>6</v>
       </c>
       <c r="E10" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 06'!A6:A38,2)="T-")*1)</f>
+        <f>SUMPRODUCT((LEFT('Sprint 06'!A6:A40,2)="T-")*1)</f>
         <v/>
       </c>
       <c r="F10" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 06'!A6:A38,2)="T-")*('Sprint 06'!E6:E38="Hecho"))</f>
+        <f>SUMPRODUCT((LEFT('Sprint 06'!A6:A40,2)="T-")*('Sprint 06'!E6:E40="Hecho"))</f>
         <v/>
       </c>
       <c r="G10" s="18">
@@ -24265,7 +24359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25034,10 +25128,14 @@
           <t>Configuración de Módulos</t>
         </is>
       </c>
-      <c r="D35" s="23" t="inlineStr"/>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -25053,10 +25151,14 @@
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr"/>
-      <c r="D36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -25072,10 +25174,14 @@
         </is>
       </c>
       <c r="C37" s="16" t="inlineStr"/>
-      <c r="D37" s="16" t="inlineStr"/>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -25087,26 +25193,76 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">     Dejar la configuración escrita en la base, no deducida del catálogo</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>T-36.4</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Evitar que una segunda aprobación duplique o pise lo ya configurado</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr"/>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>T-36.5</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">     Probar el alta de una empresa nueva de punta a punta</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr"/>
-      <c r="D38" s="14" t="inlineStr"/>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" s="19" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr"/>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>AVANCE DEL SPRINT (tareas terminadas)</t>
         </is>
       </c>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="20">
-        <f>TEXT(SUMPRODUCT((LEFT(A6:A38,2)="T-")*(E6:E38="Hecho"))/SUMPRODUCT((LEFT(A6:A38,2)="T-")*1),"0%")</f>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20">
+        <f>TEXT(SUMPRODUCT((LEFT(A6:A40,2)="T-")*(E6:E40="Hecho"))/SUMPRODUCT((LEFT(A6:A40,2)="T-")*1),"0%")</f>
         <v/>
       </c>
     </row>
@@ -25116,7 +25272,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E38">
+  <conditionalFormatting sqref="E6:E40">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -25131,10 +25287,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E6:E38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:D38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -928,7 +928,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Período: 21/09 al 27/09    |    Estado: Planificado</t>
+          <t>Período: 21/09 al 27/09    |    Estado: En curso</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -986,10 +986,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr"/>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1005,10 +1009,14 @@
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr"/>
-      <c r="D7" s="14" t="inlineStr"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1024,10 +1032,14 @@
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1043,10 +1055,14 @@
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="14" t="inlineStr"/>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1062,10 +1078,14 @@
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1085,10 +1105,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr"/>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1104,10 +1128,14 @@
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1123,10 +1151,14 @@
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr"/>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1142,10 +1174,14 @@
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1161,10 +1197,14 @@
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1184,10 +1224,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr"/>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1203,10 +1247,14 @@
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr"/>
-      <c r="D17" s="14" t="inlineStr"/>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1222,10 +1270,14 @@
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr"/>
-      <c r="D18" s="16" t="inlineStr"/>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1245,10 +1297,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr"/>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1264,10 +1320,14 @@
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1283,10 +1343,14 @@
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="16" t="inlineStr"/>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1302,10 +1366,14 @@
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5296,6 +5364,46 @@
       <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Todas las HU</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>La subcategoría del producto quedó opcional</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Exigirla obligaba a inventar una subcategoría de relleno ("General") en cada categoría que la empresa no quiere subdividir, sólo para poder cargar el primer producto. Es fricción justo para el tipo de usuario del proyecto. La categoría sí es obligatoria: es lo que ordena el catálogo.</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>HU-38 · Sprint 07</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="39" customHeight="1">
+      <c r="A23" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>La unidad de medida es una lista cerrada, no un texto libre</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Con texto libre conviven "kg", "Kg", "kilo" y "kilos" en el mismo catálogo, y después no hay forma de sumar el stock ni de agrupar un reporte. La lista vive en un archivo de configuración, así que ampliarla es una línea.</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>HU-38 · Sprint 07</t>
         </is>
       </c>
     </row>
@@ -11666,10 +11774,14 @@
       </c>
       <c r="H162" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I162" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I162" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="14" t="inlineStr">
@@ -11701,10 +11813,14 @@
       </c>
       <c r="H163" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I163" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I163" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="16" t="inlineStr">
@@ -11736,10 +11852,14 @@
       </c>
       <c r="H164" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I164" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I164" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="14" t="inlineStr">
@@ -11771,10 +11891,14 @@
       </c>
       <c r="H165" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I165" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I165" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="16" t="inlineStr">
@@ -11806,10 +11930,14 @@
       </c>
       <c r="H166" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I166" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="16" customHeight="1">
       <c r="A167" s="12" t="inlineStr">
@@ -11849,10 +11977,14 @@
       </c>
       <c r="H167" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I167" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I167" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
@@ -11884,10 +12016,14 @@
       </c>
       <c r="H168" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I168" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I168" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="16" t="inlineStr">
@@ -11919,10 +12055,14 @@
       </c>
       <c r="H169" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I169" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
@@ -11954,10 +12094,14 @@
       </c>
       <c r="H170" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I170" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I170" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="16" t="inlineStr">
@@ -11989,10 +12133,14 @@
       </c>
       <c r="H171" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I171" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="16" customHeight="1">
       <c r="A172" s="12" t="inlineStr">
@@ -12032,10 +12180,14 @@
       </c>
       <c r="H172" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I172" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I172" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="14" t="inlineStr">
@@ -12067,10 +12219,14 @@
       </c>
       <c r="H173" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I173" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I173" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="16" t="inlineStr">
@@ -12102,10 +12258,14 @@
       </c>
       <c r="H174" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I174" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="16" customHeight="1">
       <c r="A175" s="12" t="inlineStr">
@@ -12145,10 +12305,14 @@
       </c>
       <c r="H175" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I175" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I175" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
@@ -12180,10 +12344,14 @@
       </c>
       <c r="H176" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I176" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I176" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="16" t="inlineStr">
@@ -12215,10 +12383,14 @@
       </c>
       <c r="H177" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I177" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
@@ -12250,10 +12422,14 @@
       </c>
       <c r="H178" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I178" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I178" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="26" customHeight="1">
       <c r="A179" s="12" t="inlineStr">
@@ -20416,7 +20592,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>Planificado</t>
+          <t>En curso</t>
         </is>
       </c>
     </row>

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -1451,7 +1451,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Período: 28/09 al 04/10    |    Estado: Planificado</t>
+          <t>Período: 28/09 al 04/10    |    Estado: En curso</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1509,10 +1509,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr"/>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1528,10 +1532,14 @@
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr"/>
-      <c r="D7" s="14" t="inlineStr"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1547,10 +1555,14 @@
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1566,10 +1578,14 @@
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="14" t="inlineStr"/>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1585,10 +1601,14 @@
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1608,10 +1628,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr"/>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1627,10 +1651,14 @@
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1646,10 +1674,14 @@
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr"/>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1665,10 +1697,14 @@
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1684,10 +1720,14 @@
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1707,10 +1747,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr"/>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1726,10 +1770,14 @@
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr"/>
-      <c r="D17" s="14" t="inlineStr"/>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1745,10 +1793,14 @@
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr"/>
-      <c r="D18" s="16" t="inlineStr"/>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1764,10 +1816,14 @@
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="14" t="inlineStr"/>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1787,10 +1843,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr"/>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1806,10 +1866,14 @@
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="14" t="inlineStr"/>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1825,10 +1889,14 @@
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr"/>
-      <c r="D22" s="16" t="inlineStr"/>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1844,10 +1912,14 @@
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr"/>
-      <c r="D23" s="14" t="inlineStr"/>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1867,10 +1939,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr"/>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1886,10 +1962,14 @@
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr"/>
-      <c r="D25" s="14" t="inlineStr"/>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1905,10 +1985,14 @@
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr"/>
-      <c r="D26" s="16" t="inlineStr"/>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1924,10 +2008,14 @@
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr"/>
-      <c r="D27" s="14" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1943,10 +2031,14 @@
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr"/>
-      <c r="D28" s="16" t="inlineStr"/>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1966,10 +2058,14 @@
           <t>Productos y Stock</t>
         </is>
       </c>
-      <c r="D29" s="23" t="inlineStr"/>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -1985,10 +2081,14 @@
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr"/>
-      <c r="D30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -2004,10 +2104,14 @@
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr"/>
-      <c r="D31" s="16" t="inlineStr"/>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E31" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -4976,7 +5080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5387,21 +5491,101 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="39" customHeight="1">
+    <row r="23" ht="65" customHeight="1">
       <c r="A23" s="15" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
+          <t>La existencia no se guarda en una columna: se calcula</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Un campo "stock actual" hay que mantenerlo sincronizado a mano en cada alta, cada anulación y cada corrección, y el día que una se olvida el número queda mal para siempre sin que nadie se entere. Calculándolo a partir de los movimientos, la anulación corrige el stock sola y el historial siempre explica el número que se ve en pantalla.</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>HU-42, HU-46 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>El efecto de un motivo de stock no se puede cambiar una vez usado</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>El stock se calcula recorriendo los movimientos y subiendo al motivo para saber si suman o restan. Dar vuelta "Venta" de salida a entrada reinterpretaría todo el historial y las existencias cambiarían solas. El nombre sí se puede corregir siempre.</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>HU-41 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="39" customHeight="1">
+      <c r="A25" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>El ajuste de stock quedó partido en dos motivos</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>El backlog pedía un motivo "ajuste" a secas, pero un mismo motivo no puede a veces sumar y a veces restar: si el efecto no es fijo, el historial es imposible de interpretar. Se cargan "Ajuste positivo" y "Ajuste negativo".</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>HU-41 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="65" customHeight="1">
+      <c r="A26" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>El movimiento de dinero se ofrece, no se crea solo</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>El sistema no conoce los precios, así que no puede calcular el monto; y una venta puede haberse cobrado de otra manera. El sistema propone el movimiento con la fecha y el detalle ya armados, y la persona decide. Si dice que no, el movimiento de stock queda marcado como "falta el dinero" en el historial, que es lo que después descuadra.</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>HU-45 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39" customHeight="1">
+      <c r="A27" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
           <t>La unidad de medida es una lista cerrada, no un texto libre</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Con texto libre conviven "kg", "Kg", "kilo" y "kilos" en el mismo catálogo, y después no hay forma de sumar el stock ni de agrupar un reporte. La lista vive en un archivo de configuración, así que ampliarla es una línea.</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>HU-38 · Sprint 07</t>
         </is>
@@ -12469,10 +12653,14 @@
       </c>
       <c r="H179" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I179" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I179" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
@@ -12504,10 +12692,14 @@
       </c>
       <c r="H180" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I180" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I180" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="16" t="inlineStr">
@@ -12539,10 +12731,14 @@
       </c>
       <c r="H181" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I181" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I181" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
@@ -12574,10 +12770,14 @@
       </c>
       <c r="H182" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I182" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I182" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="16" t="inlineStr">
@@ -12609,10 +12809,14 @@
       </c>
       <c r="H183" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I183" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="26" customHeight="1">
       <c r="A184" s="12" t="inlineStr">
@@ -12652,10 +12856,14 @@
       </c>
       <c r="H184" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I184" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I184" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="14" t="inlineStr">
@@ -12687,10 +12895,14 @@
       </c>
       <c r="H185" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I185" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I185" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="16" t="inlineStr">
@@ -12722,10 +12934,14 @@
       </c>
       <c r="H186" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I186" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I186" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="14" t="inlineStr">
@@ -12757,10 +12973,14 @@
       </c>
       <c r="H187" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I187" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I187" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="16" t="inlineStr">
@@ -12792,10 +13012,14 @@
       </c>
       <c r="H188" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I188" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I188" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="26" customHeight="1">
       <c r="A189" s="12" t="inlineStr">
@@ -12835,10 +13059,14 @@
       </c>
       <c r="H189" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I189" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I189" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
@@ -12870,10 +13098,14 @@
       </c>
       <c r="H190" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I190" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I190" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="16" t="inlineStr">
@@ -12905,10 +13137,14 @@
       </c>
       <c r="H191" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I191" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I191" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
@@ -12940,10 +13176,14 @@
       </c>
       <c r="H192" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I192" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I192" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="26" customHeight="1">
       <c r="A193" s="12" t="inlineStr">
@@ -12983,10 +13223,14 @@
       </c>
       <c r="H193" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I193" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I193" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="14" t="inlineStr">
@@ -13018,10 +13262,14 @@
       </c>
       <c r="H194" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I194" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I194" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="16" t="inlineStr">
@@ -13053,10 +13301,14 @@
       </c>
       <c r="H195" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I195" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I195" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="14" t="inlineStr">
@@ -13088,10 +13340,14 @@
       </c>
       <c r="H196" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I196" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I196" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="26" customHeight="1">
       <c r="A197" s="12" t="inlineStr">
@@ -13131,10 +13387,14 @@
       </c>
       <c r="H197" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I197" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I197" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="14" t="inlineStr">
@@ -13166,10 +13426,14 @@
       </c>
       <c r="H198" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I198" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I198" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="16" t="inlineStr">
@@ -13201,10 +13465,14 @@
       </c>
       <c r="H199" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I199" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I199" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="14" t="inlineStr">
@@ -13236,10 +13504,14 @@
       </c>
       <c r="H200" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I200" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I200" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="16" t="inlineStr">
@@ -13271,10 +13543,14 @@
       </c>
       <c r="H201" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I201" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I201" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="26" customHeight="1">
       <c r="A202" s="12" t="inlineStr">
@@ -13314,10 +13590,14 @@
       </c>
       <c r="H202" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I202" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I202" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="14" t="inlineStr">
@@ -13349,10 +13629,14 @@
       </c>
       <c r="H203" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I203" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I203" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="16" t="inlineStr">
@@ -13384,10 +13668,14 @@
       </c>
       <c r="H204" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I204" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I204" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="9" t="inlineStr">
@@ -20629,7 +20917,7 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Planificado</t>
+          <t>En curso</t>
         </is>
       </c>
     </row>

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -28,7 +28,7 @@
     <sheet name="Cambios vs. original" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$384</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$421</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2165,7 +2165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2200,7 +2200,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
         <is>
-          <t>Objetivo del sprint:  Abrir el módulo de Servicios, que comparte estructura con Productos pero sin control de existencias.</t>
+          <t>Objetivo del sprint:  Emparejar la base ANTES de duplicarla, y recién entonces abrir Servicios. El orden importa: Servicios copia las pantallas de Productos, así que cada nombre, cada tabla que no entra en el celular y cada pantalla de configuración mal ubicada que quede sin arreglar se copia a un lugar más. Primero el vocabulario, el celular y la configuración; después el módulo nuevo, que es un producto sin stock.</t>
         </is>
       </c>
     </row>
@@ -2234,332 +2234,963 @@
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="23" t="inlineStr">
         <is>
-          <t>HU-47</t>
+          <t>HU-83</t>
         </is>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
+          <t>Como empresa nueva quiero poder registrarme y entrar sin trabarme para empezar a usar el sistema.</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr"/>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>T-47.1</t>
+          <t>T-83.1</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Reutilizar el modelo de productos agregando la distinción de servicio</t>
+          <t xml:space="preserve">     Sacar la matrícula del registro, del perfil y de la base</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr"/>
-      <c r="D7" s="14" t="inlineStr"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>T-47.2</t>
+          <t>T-83.2</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Programar el alta, la edición y la baja lógica</t>
+          <t xml:space="preserve">     Que el formulario de registro no se cierre ni se borre cuando hay un error</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>T-47.3</t>
+          <t>T-83.3</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Diseñar la pantalla de servicios</t>
+          <t xml:space="preserve">     Marcar los campos obligatorios y nombrar el que falta</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="14" t="inlineStr"/>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>T-47.4</t>
+          <t>T-83.4</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Verificar que los servicios no lleven existencias</t>
+          <t xml:space="preserve">     Mandar al administrador de la plataforma a su panel al iniciar sesión</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>HU-48</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr"/>
-      <c r="E11" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>T-83.5</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Llevar los módulos sin pantalla a un aviso de 'en construcción'</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr"/>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>T-48.1</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Vincular el movimiento económico con el servicio</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>T-48.2</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Agregar el servicio al formulario de movimiento</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>T-83.6</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Explicarle al operador qué hacer si falta la categoría del producto</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr"/>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>HU-89</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Como empresa quiero que dos personas puedan trabajar al mismo tiempo sin que los números queden mal.</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>T-48.3</t>
+          <t>T-89.1</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Agregar el filtro por servicio en el listado</t>
+          <t xml:space="preserve">     Trabar la fila del producto antes de contar la existencia</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>HU-49</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr"/>
-      <c r="E15" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>T-89.2</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Hacer el control y el alta del movimiento de stock en una sola transacción</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr"/>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>T-49.1</t>
+          <t>T-89.3</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Programar la consulta agrupada por servicio</t>
+          <t xml:space="preserve">     Hacer lo mismo con el movimiento de dinero de una venta</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr"/>
-      <c r="D16" s="14" t="inlineStr"/>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
         <is>
+          <t>T-89.4</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Corregir la marca del cobro para que mire si el movimiento sigue vigente</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr"/>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>T-89.5</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     No revivir en cascada lo que el administrador dio de baja a propósito</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr"/>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>T-89.6</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Validar el largo de los textos y pedir modo estricto a la base</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr"/>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>T-89.7</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Devolver JSON en vez del stack trace cuando el pedido viene mal</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>HU-84</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Como usuario quiero que cada cosa se llame siempre igual para aprender una vez y no tener que adivinar.</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr"/>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>T-84.1</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Decidir los nombres en grupo (naturaleza, categorías, anular/dar de baja)</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>T-84.2</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Reemplazar 'naturaleza' por una pregunta en castellano llano</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr"/>
+      <c r="D23" s="16" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>T-84.3</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Ponerle apellido a las dos pantallas de categorías (dinero y productos)</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>T-84.4</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Unificar anular / dar de baja / desactivar en dos palabras y dos íconos</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr"/>
+      <c r="D25" s="16" t="inlineStr"/>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>T-84.5</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Renombrar los movimientos de stock como entradas y salidas</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>HU-85</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Como operador quiero ver en el celular la columna que me importa para no tener que arrastrar la tabla de costado.</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr"/>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>T-85.1</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Convertir los tres listados en tarjetas por debajo de 768 px</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr"/>
+      <c r="D28" s="14" t="inlineStr"/>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>T-85.2</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Compactar el encabezado en celular</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr"/>
+      <c r="D29" s="16" t="inlineStr"/>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>T-85.3</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Validar en 375 px que no quede scroll horizontal</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="inlineStr"/>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>HU-86</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Como administrador quiero encontrar la configuración en un solo lugar para no buscarla abajo de mi nombre.</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr"/>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>T-86.1</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Agrupar las cuatro pantallas de configuración en el menú principal</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr"/>
+      <c r="D32" s="14" t="inlineStr"/>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>T-86.2</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Dejar en el menú del usuario sólo lo personal y cerrar sesión</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr"/>
+      <c r="D33" s="16" t="inlineStr"/>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>T-86.3</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Mover el acceso a motivos desde Productos a Stock</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr"/>
+      <c r="D34" s="14" t="inlineStr"/>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>HU-47</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr"/>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>T-47.1</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Reutilizar el modelo de productos agregando la distinción de servicio</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr"/>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>T-47.2</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Programar el alta, la edición y la baja lógica</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr"/>
+      <c r="D37" s="16" t="inlineStr"/>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>T-47.3</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Diseñar la pantalla de servicios</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr"/>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>T-47.4</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Verificar que los servicios no lleven existencias</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr"/>
+      <c r="D39" s="16" t="inlineStr"/>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>HU-48</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr"/>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>T-48.1</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Vincular el movimiento económico con el servicio</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr"/>
+      <c r="D41" s="14" t="inlineStr"/>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>T-48.2</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Agregar el servicio al formulario de movimiento</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr"/>
+      <c r="D42" s="16" t="inlineStr"/>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>T-48.3</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Agregar el filtro por servicio en el listado</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr"/>
+      <c r="D43" s="14" t="inlineStr"/>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>HU-49</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr"/>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>T-49.1</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Programar la consulta agrupada por servicio</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr"/>
+      <c r="D45" s="14" t="inlineStr"/>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
           <t>T-49.2</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B46" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Diseñar la visualización del resumen</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr"/>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr"/>
+      <c r="D46" s="16" t="inlineStr"/>
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t>HU-50</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B47" s="23" t="inlineStr">
         <is>
           <t>Como equipo quiero probar los módulos de productos y servicios para entregarlos sin errores.</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C47" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr"/>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="D47" s="23" t="inlineStr"/>
+      <c r="E47" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>T-50.1</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Escribir y ejecutar los casos de prueba de stock</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="14" t="inlineStr"/>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr"/>
+      <c r="D48" s="14" t="inlineStr"/>
+      <c r="E48" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>T-50.2</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Escribir y ejecutar los casos de prueba de servicios</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr"/>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr"/>
+      <c r="D49" s="16" t="inlineStr"/>
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>T-50.3</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Validar ambas pantallas en celular</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="14" t="inlineStr"/>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr"/>
+      <c r="D50" s="14" t="inlineStr"/>
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="C23" s="19" t="inlineStr">
+    <row r="52">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>AVANCE DEL SPRINT (tareas terminadas)</t>
         </is>
       </c>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20">
-        <f>TEXT(SUMPRODUCT((LEFT(A6:A21,2)="T-")*(E6:E21="Hecho"))/SUMPRODUCT((LEFT(A6:A21,2)="T-")*1),"0%")</f>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="20">
+        <f>TEXT(SUMPRODUCT((LEFT(A6:A50,2)="T-")*(E6:E50="Hecho"))/SUMPRODUCT((LEFT(A6:A50,2)="T-")*1),"0%")</f>
         <v/>
       </c>
     </row>
@@ -2569,7 +3200,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E21">
+  <conditionalFormatting sqref="E6:E50">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -2584,10 +3215,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E6:E21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3814,7 +4445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3849,7 +4480,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="22" t="inlineStr">
         <is>
-          <t>Objetivo del sprint:  Cierre del ciclo: definir la identidad del producto, ajustar la interfaz, probar de punta a punta y documentar para la continuidad del proyecto.</t>
+          <t>Objetivo del sprint:  Cierre del ciclo: definir la identidad del producto, terminar de ajustar la interfaz, probar de punta a punta y documentar para la continuidad del proyecto. Queda más liviano que en la planificación anterior porque el vocabulario, el celular y la configuración se adelantaron al Sprint 09, donde hacían falta.</t>
         </is>
       </c>
     </row>
@@ -4078,15 +4709,15 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="26" customHeight="1">
       <c r="A16" s="23" t="inlineStr">
         <is>
-          <t>HU-65</t>
+          <t>HU-87</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
+          <t>Como tesorero quiero cargar un movimiento en menos pasos para no contestar tres preguntas encadenadas.</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -4104,12 +4735,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>T-65.1</t>
+          <t>T-87.1</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Revisar las pantallas de los módulos nuevos en ancho de celular</t>
+          <t xml:space="preserve">     Reemplazar los tres desplegables encadenados por uno solo</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr"/>
@@ -4123,12 +4754,12 @@
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>T-65.2</t>
+          <t>T-87.2</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Validar en Chrome y en un segundo navegador</t>
+          <t xml:space="preserve">     Ofrecer entró/salió como dos botones en vez de un desplegable</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr"/>
@@ -4142,12 +4773,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>T-65.3</t>
+          <t>T-87.3</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Validar en un celular real</t>
+          <t xml:space="preserve">     Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr"/>
@@ -4158,15 +4789,15 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="26" customHeight="1">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>HU-66</t>
+          <t>HU-88</t>
         </is>
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Como equipo quiero dejar el proyecto documentado para poder continuarlo el año próximo.</t>
+          <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -4184,12 +4815,12 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>T-66.1</t>
+          <t>T-88.1</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Escribir el README con las instrucciones de instalación</t>
+          <t xml:space="preserve">     Separar el listado vacío del listado filtrado en los cuatro listados</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr"/>
@@ -4203,12 +4834,12 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>T-66.2</t>
+          <t>T-88.2</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Escribir el manual de usuario básico</t>
+          <t xml:space="preserve">     Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr"/>
@@ -4222,12 +4853,12 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>T-66.3</t>
+          <t>T-88.3</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Documentar el modelo de datos</t>
+          <t xml:space="preserve">     Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr"/>
@@ -4238,114 +4869,274 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>HU-65</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr"/>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>T-65.1</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Revisar las pantallas de los módulos nuevos en ancho de celular</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr"/>
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>T-65.2</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Validar en Chrome y en un segundo navegador</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr"/>
+      <c r="D26" s="16" t="inlineStr"/>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>T-65.3</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Validar en un celular real</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>HU-66</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Como equipo quiero dejar el proyecto documentado para poder continuarlo el año próximo.</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr"/>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>T-66.1</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Escribir el README con las instrucciones de instalación</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr"/>
+      <c r="D29" s="14" t="inlineStr"/>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>T-66.2</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Escribir el manual de usuario básico</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr"/>
+      <c r="D30" s="16" t="inlineStr"/>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>T-66.3</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Documentar el modelo de datos</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr"/>
+      <c r="D31" s="14" t="inlineStr"/>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>T-66.4</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Documentar el diseño de los módulos que quedaron sin implementar</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr"/>
-      <c r="D24" s="16" t="inlineStr"/>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr"/>
+      <c r="D32" s="16" t="inlineStr"/>
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>HU-67</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>Como equipo quiero probar el sistema completo para entregar una versión estable.</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr"/>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr"/>
+      <c r="E33" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>T-67.1</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Ejecutar la batería de pruebas de punta a punta</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="14" t="inlineStr"/>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr"/>
+      <c r="D34" s="14" t="inlineStr"/>
+      <c r="E34" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>T-67.2</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Corregir los errores detectados</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr"/>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr"/>
+      <c r="D35" s="16" t="inlineStr"/>
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>T-67.3</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Unificar la carga del encabezado en un archivo compartido</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr"/>
-      <c r="D28" s="14" t="inlineStr"/>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr"/>
+      <c r="E36" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="C30" s="19" t="inlineStr">
+    <row r="38">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>AVANCE DEL SPRINT (tareas terminadas)</t>
         </is>
       </c>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20">
-        <f>TEXT(SUMPRODUCT((LEFT(A6:A28,2)="T-")*(E6:E28="Hecho"))/SUMPRODUCT((LEFT(A6:A28,2)="T-")*1),"0%")</f>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20">
+        <f>TEXT(SUMPRODUCT((LEFT(A6:A36,2)="T-")*(E6:E36="Hecho"))/SUMPRODUCT((LEFT(A6:A36,2)="T-")*1),"0%")</f>
         <v/>
       </c>
     </row>
@@ -4355,7 +5146,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E28">
+  <conditionalFormatting sqref="E6:E36">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -4370,10 +5161,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E6:E28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:D28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5080,7 +5871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5131,83 +5922,83 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="65" customHeight="1">
+    <row r="5" ht="91" customHeight="1">
       <c r="A5" s="15" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>El producto pasó de cooperativas a empresas en general</t>
+          <t>El vocabulario, el celular y la configuración se adelantaron del Sprint 13 al 09</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Se decidió ofrecer el sistema a empresas, de PyMEs a grandes, en lugar de limitarlo a cooperativas y fábricas recuperadas. Cambia el público, el vocabulario de todo el sistema y el argumento de venta: ya no alcanza con 'es simple', hay que sostener por qué conviene frente a un ERP. Queda pendiente redefinir el nombre del producto y rehacer la validación de idea.</t>
+          <t>Las dos auditorías (QA y UX) llegaron a la misma conclusión por caminos distintos: Servicios se escribe copiando las pantallas de Productos, así que todo lo que hoy está mal en esas pantallas se va a duplicar. Estaban planificadas para DESPUÉS de lo que tienen que preceder. Adelantarlas cuesta una semana ahora y ahorra corregir el doble de pantallas después. De paso el Sprint 13 baja de 35 a 24 tareas: era el más cargado de los trece, y encima es la semana de la entrega final.</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Todas las épicas · HU-32 ejecutó el renombrado · HU-63 cierra la identidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="52" customHeight="1">
+          <t>HU-84, HU-85 y HU-86 · del Sprint 13 al Sprint 09</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="26" t="inlineStr">
         <is>
-          <t>Se agregó la épica de Configuración de Módulos</t>
+          <t>Se sumaron las correcciones de las dos auditorías como historias propias</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Cada empresa activa sólo lo que usa: una empresa de servicios no necesita stock, y una distribuidora puede no usar articulación. Se hace ahora, con dos módulos, porque incorporarlo con seis ya construidos obliga a rehacer todo el control de acceso.</t>
+          <t>Los hallazgos que se corrigen quedan escritos como historia, no sólo en el informe: así el avance del backlog refleja el trabajo que se hizo de verdad y la trazabilidad no depende de acordarse. HU-83 salió de la auditoría de UX (la puerta de entrada rota, el superadmin en un tablero ajeno, los botones que no reaccionaban) y HU-89 de la de QA (dos pedidos al mismo tiempo dejaban el stock en negativo y cobraban la misma venta seis veces).</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Nueva E12 · Sprint 06</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="39" customHeight="1">
+          <t>HU-83 y HU-89 · Sprint 09 · las dos ya Hechas</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="65" customHeight="1">
       <c r="A7" s="15" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Se agregó la épica de Servicios</t>
+          <t>Articulación conserva sus dos sprints</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Junto con Productos son los dos orígenes de movimientos de dinero del sistema. Un servicio es estructuralmente un producto sin existencias, así que reutiliza el modelo y sale en un sprint.</t>
+          <t>Al reordenar se evaluó comprimirla en uno para descargar el Sprint 09. Se descartó: es el módulo diferencial del producto, el único que no tiene un ERP, y es el que más incógnitas arrastra (los criterios exactos del match todavía no están definidos). Comprimir lo más incierto es el riesgo más caro de los que había sobre la mesa.</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>Nueva E13 · Sprint 09</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="39" customHeight="1">
+          <t>Sprints 11 y 12 · sin cambios</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="65" customHeight="1">
       <c r="A8" s="17" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="26" t="inlineStr">
         <is>
-          <t>Productos y Servicios NO son categorías de movimientos</t>
+          <t>El producto pasó de cooperativas a empresas en general</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>El dinero ya tiene su propia clasificación (categoría y tipo). Productos y Servicios son módulos operativos que generan movimientos. Si se mezclaran, la misma venta quedaría clasificada dos veces y los totales no cerrarían.</t>
+          <t>Se decidió ofrecer el sistema a empresas, de PyMEs a grandes, en lugar de limitarlo a cooperativas y fábricas recuperadas. Cambia el público, el vocabulario de todo el sistema y el argumento de venta: ya no alcanza con 'es simple', hay que sostener por qué conviene frente a un ERP. Queda pendiente redefinir el nombre del producto y rehacer la validación de idea.</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>E3 y E4 frente a E6 y E13</t>
+          <t>Todas las épicas · HU-32 ejecutó el renombrado · HU-63 cierra la identidad</t>
         </is>
       </c>
     </row>
@@ -5217,37 +6008,37 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Los motivos de movimiento de stock llevan su impacto configurado</t>
+          <t>Se agregó la épica de Configuración de Módulos</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Cada motivo dice si suma o resta existencias y si genera ingreso, egreso o nada, así el administrador arma los suyos sin tocar código. Pérdida y robo no generan movimiento de dinero, pero se ven valorizados en un reporte aparte para no ensuciar el balance.</t>
+          <t>Cada empresa activa sólo lo que usa: una empresa de servicios no necesita stock, y una distribuidora puede no usar articulación. Se hace ahora, con dos módulos, porque incorporarlo con seis ya construidos obliga a rehacer todo el control de acceso.</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>HU-41 y HU-53</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
+          <t>Nueva E12 · Sprint 06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="39" customHeight="1">
       <c r="A10" s="17" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>Recursos Humanos quedó en el backlog futuro</t>
+          <t>Se agregó la épica de Servicios</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>Es el módulo más grande de los propuestos (circuito de aprobación, saldo de días, archivos adjuntos con datos de salud) y el único que no toca el flujo de dinero, que es el eje del producto. Con siete sprints por delante no entra sin poner en riesgo el resto. Se deja diseñado y documentado para el ciclo siguiente.</t>
+          <t>Junto con Productos son los dos orígenes de movimientos de dinero del sistema. Un servicio es estructuralmente un producto sin existencias, así que reutiliza el modelo y sale en un sprint.</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>Nueva E14 · HU-68 a HU-70, sin sprint</t>
+          <t>Nueva E13 · Sprint 09</t>
         </is>
       </c>
     </row>
@@ -5257,57 +6048,57 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>La articulación se mantuvo pese al cambio de público</t>
+          <t>Productos y Servicios NO son categorías de movimientos</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Es lo único del producto que no ofrece un sistema de gestión convencional. Se conserva acotada a PyMEs, donde la coincidencia entre necesidades y ofertas tiene sentido real.</t>
+          <t>El dinero ya tiene su propia clasificación (categoría y tipo). Productos y Servicios son módulos operativos que generan movimientos. Si se mezclaran, la misma venta quedaría clasificada dos veces y los totales no cerrarían.</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>E8 · Sprints 11 y 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="39" customHeight="1">
+          <t>E3 y E4 frente a E6 y E13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
       <c r="A12" s="17" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>Los sprints 04 a 06 originales se consolidaron en dos</t>
+          <t>Los motivos de movimiento de stock llevan su impacto configurado</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>El equipo entregó categorías, movimientos, consulta, anulación, resumen y dashboard real en menos tiempo del planificado. El backlog refleja lo entregado, no la planificación anterior.</t>
+          <t>Cada motivo dice si suma o resta existencias y si genera ingreso, egreso o nada, así el administrador arma los suyos sin tocar código. Pérdida y robo no generan movimiento de dinero, pero se ven valorizados en un reporte aparte para no ensuciar el balance.</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Sprint 04 (categorías) y Sprint 05 (movimientos y resumen)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+          <t>HU-41 y HU-53</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="65" customHeight="1">
       <c r="A13" s="15" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Las subcategorías de movimientos pasaron a llamarse tipos</t>
+          <t>Recursos Humanos quedó en el backlog futuro</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Es el nombre que quedó implementado: naturaleza, categoría y tipo. El backlog usa el mismo vocabulario que el sistema para que no haya dos idiomas.</t>
+          <t>Es el módulo más grande de los propuestos (circuito de aprobación, saldo de días, archivos adjuntos con datos de salud) y el único que no toca el flujo de dinero, que es el eje del producto. Con siete sprints por delante no entra sin poner en riesgo el resto. Se deja diseñado y documentado para el ciclo siguiente.</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>E3 · HU-19</t>
+          <t>Nueva E14 · HU-68 a HU-70, sin sprint</t>
         </is>
       </c>
     </row>
@@ -5317,17 +6108,17 @@
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>Se agregó un sprint de corrección de deuda técnica</t>
+          <t>La articulación se mantuvo pese al cambio de público</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>La revisión del módulo de movimientos encontró seis errores, entre ellos textos del usuario que se ejecutaban como código en la pantalla y montos que se guardaban en cero. No estaban representados en ninguna historia.</t>
+          <t>Es lo único del producto que no ofrece un sistema de gestión convencional. Se conserva acotada a PyMEs, donde la coincidencia entre necesidades y ofertas tiene sentido real.</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>HU-31 · Sprint 06</t>
+          <t>E8 · Sprints 11 y 12</t>
         </is>
       </c>
     </row>
@@ -5337,17 +6128,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>El Sprint 1 original se dividió en dos sprints</t>
+          <t>Los sprints 04 a 06 originales se consolidaron en dos</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Concentraba ocho historias y dos módulos distintos (alta de empresas y acceso al sistema). Partido en dos queda un sprint por tema y el seguimiento semanal es realista.</t>
+          <t>El equipo entregó categorías, movimientos, consulta, anulación, resumen y dashboard real en menos tiempo del planificado. El backlog refleja lo entregado, no la planificación anterior.</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Sprint 01 (base y registro) + Sprint 02 (acceso y usuarios)</t>
+          <t>Sprint 04 (categorías) y Sprint 05 (movimientos y resumen)</t>
         </is>
       </c>
     </row>
@@ -5357,17 +6148,17 @@
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>Se quitaron las columnas de horas estimadas y reales</t>
+          <t>Las subcategorías de movimientos pasaron a llamarse tipos</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Las estimaciones eran una suposición sin velocidad real medida del equipo, y una columna que nadie completa con datos confiables ensucia el seguimiento.</t>
+          <t>Es el nombre que quedó implementado: naturaleza, categoría y tipo. El backlog usa el mismo vocabulario que el sistema para que no haya dos idiomas.</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>Product Backlog, hojas de sprint y Seguimiento</t>
+          <t>E3 · HU-19</t>
         </is>
       </c>
     </row>
@@ -5377,77 +6168,77 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>El recupero de contraseña por correo se reemplazó por reseteo por el administrador</t>
+          <t>Se agregó un sprint de corrección de deuda técnica</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>El proyecto corre sólo en local: no hay servidor de correo. El administrador de la plataforma resetea a los administradores de empresa, y cada administrador a los usuarios de su empresa.</t>
+          <t>La revisión del módulo de movimientos encontró seis errores, entre ellos textos del usuario que se ejecutaban como código en la pantalla y montos que se guardaban en cero. No estaban representados en ninguna historia.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>HU-10 y HU-11 · el recupero por correo pasó a HU-71, sin sprint</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
+          <t>HU-31 · Sprint 06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="39" customHeight="1">
       <c r="A18" s="17" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>Se unificaron las épicas Operaciones financieras y Registro de movimientos diarios</t>
+          <t>El Sprint 1 original se dividió en dos sprints</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>En el backlog original describían el mismo módulo con distinto nombre y sus historias se superponían.</t>
+          <t>Concentraba ocho historias y dos módulos distintos (alta de empresas y acceso al sistema). Partido en dos queda un sprint por tema y el seguimiento semanal es realista.</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>E3 y E5 originales → E4 Movimientos Económico-Financieros</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="39" customHeight="1">
+          <t>Sprint 01 (base y registro) + Sprint 02 (acceso y usuarios)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="15" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Se agregó la épica de Calidad, UX y Documentación</t>
+          <t>Se quitaron las columnas de horas estimadas y reales</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>La Definición de Terminado exige validación en celular y en dos navegadores, y el proyecto se continúa el año próximo. Ese trabajo no estaba representado en ninguna historia.</t>
+          <t>Las estimaciones eran una suposición sin velocidad real medida del equipo, y una columna que nadie completa con datos confiables ensucia el seguimiento.</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>E10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
+          <t>Product Backlog, hojas de sprint y Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="39" customHeight="1">
       <c r="A20" s="17" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>El chat pasó al backlog futuro</t>
+          <t>El recupero de contraseña por correo se reemplazó por reseteo por el administrador</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>No forma parte del MVP y compite con funcionalidades críticas.</t>
+          <t>El proyecto corre sólo en local: no hay servidor de correo. El administrador de la plataforma resetea a los administradores de empresa, y cada administrador a los usuarios de su empresa.</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>E11, sin sprint asignado</t>
+          <t>HU-10 y HU-11 · el recupero por correo pasó a HU-71, sin sprint</t>
         </is>
       </c>
     </row>
@@ -5457,97 +6248,97 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Todas las historias se escriben en formato Como… quiero… para…</t>
+          <t>Se unificaron las épicas Operaciones financieras y Registro de movimientos diarios</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>El backlog original mezclaba historias de usuario con nombres de pantalla y tareas técnicas.</t>
+          <t>En el backlog original describían el mismo módulo con distinto nombre y sus historias se superponían.</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Todas las HU</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="52" customHeight="1">
+          <t>E3 y E5 originales → E4 Movimientos Económico-Financieros</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39" customHeight="1">
       <c r="A22" s="17" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>La subcategoría del producto quedó opcional</t>
+          <t>Se agregó la épica de Calidad, UX y Documentación</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>Exigirla obligaba a inventar una subcategoría de relleno ("General") en cada categoría que la empresa no quiere subdividir, sólo para poder cargar el primer producto. Es fricción justo para el tipo de usuario del proyecto. La categoría sí es obligatoria: es lo que ordena el catálogo.</t>
+          <t>La Definición de Terminado exige validación en celular y en dos navegadores, y el proyecto se continúa el año próximo. Ese trabajo no estaba representado en ninguna historia.</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>HU-38 · Sprint 07</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
+          <t>E10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
       <c r="A23" s="15" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>La existencia no se guarda en una columna: se calcula</t>
+          <t>El chat pasó al backlog futuro</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Un campo "stock actual" hay que mantenerlo sincronizado a mano en cada alta, cada anulación y cada corrección, y el día que una se olvida el número queda mal para siempre sin que nadie se entere. Calculándolo a partir de los movimientos, la anulación corrige el stock sola y el historial siempre explica el número que se ve en pantalla.</t>
+          <t>No forma parte del MVP y compite con funcionalidades críticas.</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>HU-42, HU-46 · Sprint 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="52" customHeight="1">
+          <t>E11, sin sprint asignado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="17" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>El efecto de un motivo de stock no se puede cambiar una vez usado</t>
+          <t>Todas las historias se escriben en formato Como… quiero… para…</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>El stock se calcula recorriendo los movimientos y subiendo al motivo para saber si suman o restan. Dar vuelta "Venta" de salida a entrada reinterpretaría todo el historial y las existencias cambiarían solas. El nombre sí se puede corregir siempre.</t>
+          <t>El backlog original mezclaba historias de usuario con nombres de pantalla y tareas técnicas.</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>HU-41 · Sprint 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="39" customHeight="1">
+          <t>Todas las HU</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
       <c r="A25" s="15" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>El ajuste de stock quedó partido en dos motivos</t>
+          <t>La subcategoría del producto quedó opcional</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>El backlog pedía un motivo "ajuste" a secas, pero un mismo motivo no puede a veces sumar y a veces restar: si el efecto no es fijo, el historial es imposible de interpretar. Se cargan "Ajuste positivo" y "Ajuste negativo".</t>
+          <t>Exigirla obligaba a inventar una subcategoría de relleno ("General") en cada categoría que la empresa no quiere subdividir, sólo para poder cargar el primer producto. Es fricción justo para el tipo de usuario del proyecto. La categoría sí es obligatoria: es lo que ordena el catálogo.</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>HU-41 · Sprint 08</t>
+          <t>HU-38 · Sprint 07</t>
         </is>
       </c>
     </row>
@@ -5557,35 +6348,95 @@
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>El movimiento de dinero se ofrece, no se crea solo</t>
+          <t>La existencia no se guarda en una columna: se calcula</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>El sistema no conoce los precios, así que no puede calcular el monto; y una venta puede haberse cobrado de otra manera. El sistema propone el movimiento con la fecha y el detalle ya armados, y la persona decide. Si dice que no, el movimiento de stock queda marcado como "falta el dinero" en el historial, que es lo que después descuadra.</t>
+          <t>Un campo "stock actual" hay que mantenerlo sincronizado a mano en cada alta, cada anulación y cada corrección, y el día que una se olvida el número queda mal para siempre sin que nadie se entere. Calculándolo a partir de los movimientos, la anulación corrige el stock sola y el historial siempre explica el número que se ve en pantalla.</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>HU-45 · Sprint 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="39" customHeight="1">
+          <t>HU-42, HU-46 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
       <c r="A27" s="15" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
+          <t>El efecto de un motivo de stock no se puede cambiar una vez usado</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>El stock se calcula recorriendo los movimientos y subiendo al motivo para saber si suman o restan. Dar vuelta "Venta" de salida a entrada reinterpretaría todo el historial y las existencias cambiarían solas. El nombre sí se puede corregir siempre.</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>HU-41 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="39" customHeight="1">
+      <c r="A28" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>El ajuste de stock quedó partido en dos motivos</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>El backlog pedía un motivo "ajuste" a secas, pero un mismo motivo no puede a veces sumar y a veces restar: si el efecto no es fijo, el historial es imposible de interpretar. Se cargan "Ajuste positivo" y "Ajuste negativo".</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>HU-41 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>El movimiento de dinero se ofrece, no se crea solo</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>El sistema no conoce los precios, así que no puede calcular el monto; y una venta puede haberse cobrado de otra manera. El sistema propone el movimiento con la fecha y el detalle ya armados, y la persona decide. Si dice que no, el movimiento de stock queda marcado como "falta el dinero" en el historial, que es lo que después descuadra.</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>HU-45 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="39" customHeight="1">
+      <c r="A30" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
           <t>La unidad de medida es una lista cerrada, no un texto libre</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>Con texto libre conviven "kg", "Kg", "kilo" y "kilos" en el mismo catálogo, y después no hay forma de sumar el stock ni de agrupar un reporte. La lista vive en un archivo de configuración, así que ampliarla es una línea.</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D30" s="16" t="inlineStr">
         <is>
           <t>HU-38 · Sprint 07</t>
         </is>
@@ -5606,7 +6457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I384"/>
+  <dimension ref="A1:I421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17512,7 +18363,7 @@
     <row r="305" ht="26" customHeight="1">
       <c r="A305" s="12" t="inlineStr">
         <is>
-          <t>HU-50</t>
+          <t>HU-83</t>
         </is>
       </c>
       <c r="B305" s="12" t="inlineStr">
@@ -17527,7 +18378,7 @@
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>Como equipo quiero probar los módulos de productos y servicios para entregarlos sin errores.</t>
+          <t>Como empresa nueva quiero poder registrarme y entrar sin trabarme para empezar a usar el sistema.</t>
         </is>
       </c>
       <c r="E305" s="13" t="inlineStr">
@@ -17547,15 +18398,19 @@
       </c>
       <c r="H305" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I305" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I305" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="14" t="inlineStr">
         <is>
-          <t>T-50.1</t>
+          <t>T-83.1</t>
         </is>
       </c>
       <c r="B306" s="14" t="inlineStr">
@@ -17566,7 +18421,7 @@
       <c r="C306" s="14" t="inlineStr"/>
       <c r="D306" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de stock</t>
+          <t xml:space="preserve">    Sacar la matrícula del registro, del perfil y de la base</t>
         </is>
       </c>
       <c r="E306" s="15" t="inlineStr"/>
@@ -17582,15 +18437,19 @@
       </c>
       <c r="H306" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I306" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I306" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="16" t="inlineStr">
         <is>
-          <t>T-50.2</t>
+          <t>T-83.2</t>
         </is>
       </c>
       <c r="B307" s="16" t="inlineStr">
@@ -17601,7 +18460,7 @@
       <c r="C307" s="16" t="inlineStr"/>
       <c r="D307" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de servicios</t>
+          <t xml:space="preserve">    Que el formulario de registro no se cierre ni se borre cuando hay un error</t>
         </is>
       </c>
       <c r="E307" s="17" t="inlineStr"/>
@@ -17617,15 +18476,19 @@
       </c>
       <c r="H307" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I307" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I307" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="14" t="inlineStr">
         <is>
-          <t>T-50.3</t>
+          <t>T-83.3</t>
         </is>
       </c>
       <c r="B308" s="14" t="inlineStr">
@@ -17636,7 +18499,7 @@
       <c r="C308" s="14" t="inlineStr"/>
       <c r="D308" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Validar ambas pantallas en celular</t>
+          <t xml:space="preserve">    Marcar los campos obligatorios y nombrar el que falta</t>
         </is>
       </c>
       <c r="E308" s="15" t="inlineStr"/>
@@ -17652,58 +18515,58 @@
       </c>
       <c r="H308" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I308" s="14" t="inlineStr"/>
-    </row>
-    <row r="309" ht="16" customHeight="1">
-      <c r="A309" s="12" t="inlineStr">
-        <is>
-          <t>HU-62</t>
-        </is>
-      </c>
-      <c r="B309" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C309" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D309" s="12" t="inlineStr">
-        <is>
-          <t>Como equipo quiero probar el módulo de articulación para entregarlo funcionando.</t>
-        </is>
-      </c>
-      <c r="E309" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F309" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G309" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 12</t>
-        </is>
-      </c>
-      <c r="H309" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I309" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I308" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="16" t="inlineStr">
+        <is>
+          <t>T-83.4</t>
+        </is>
+      </c>
+      <c r="B309" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C309" s="16" t="inlineStr"/>
+      <c r="D309" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Mandar al administrador de la plataforma a su panel al iniciar sesión</t>
+        </is>
+      </c>
+      <c r="E309" s="17" t="inlineStr"/>
+      <c r="F309" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G309" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H309" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I309" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="14" t="inlineStr">
         <is>
-          <t>T-62.1</t>
+          <t>T-83.5</t>
         </is>
       </c>
       <c r="B310" s="14" t="inlineStr">
@@ -17714,257 +18577,277 @@
       <c r="C310" s="14" t="inlineStr"/>
       <c r="D310" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de coincidencia</t>
+          <t xml:space="preserve">    Llevar los módulos sin pantalla a un aviso de 'en construcción'</t>
         </is>
       </c>
       <c r="E310" s="15" t="inlineStr"/>
       <c r="F310" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G310" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H310" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I310" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="16" t="inlineStr">
+        <is>
+          <t>T-83.6</t>
+        </is>
+      </c>
+      <c r="B311" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C311" s="16" t="inlineStr"/>
+      <c r="D311" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Explicarle al operador qué hacer si falta la categoría del producto</t>
+        </is>
+      </c>
+      <c r="E311" s="17" t="inlineStr"/>
+      <c r="F311" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G311" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H311" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I311" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="26" customHeight="1">
+      <c r="A312" s="12" t="inlineStr">
+        <is>
+          <t>HU-89</t>
+        </is>
+      </c>
+      <c r="B312" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C312" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D312" s="12" t="inlineStr">
+        <is>
+          <t>Como empresa quiero que dos personas puedan trabajar al mismo tiempo sin que los números queden mal.</t>
+        </is>
+      </c>
+      <c r="E312" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F312" s="13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G310" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 12</t>
-        </is>
-      </c>
-      <c r="H310" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I310" s="14" t="inlineStr"/>
-    </row>
-    <row r="311" ht="26" customHeight="1">
-      <c r="A311" s="12" t="inlineStr">
-        <is>
-          <t>HU-63</t>
-        </is>
-      </c>
-      <c r="B311" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C311" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D311" s="12" t="inlineStr">
-        <is>
-          <t>Como equipo quiero definir el nombre y la identidad del producto para que acompañen al público al que apunta.</t>
-        </is>
-      </c>
-      <c r="E311" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F311" s="13" t="inlineStr">
+      <c r="G312" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H312" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I312" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="14" t="inlineStr">
+        <is>
+          <t>T-89.1</t>
+        </is>
+      </c>
+      <c r="B313" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C313" s="14" t="inlineStr"/>
+      <c r="D313" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Trabar la fila del producto antes de contar la existencia</t>
+        </is>
+      </c>
+      <c r="E313" s="15" t="inlineStr"/>
+      <c r="F313" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G311" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H311" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I311" s="12" t="inlineStr"/>
-    </row>
-    <row r="312">
-      <c r="A312" s="14" t="inlineStr">
-        <is>
-          <t>T-63.1</t>
-        </is>
-      </c>
-      <c r="B312" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C312" s="14" t="inlineStr"/>
-      <c r="D312" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Definir el nombre del producto con el equipo</t>
-        </is>
-      </c>
-      <c r="E312" s="15" t="inlineStr"/>
-      <c r="F312" s="15" t="inlineStr">
+      <c r="G313" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H313" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I313" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="16" t="inlineStr">
+        <is>
+          <t>T-89.2</t>
+        </is>
+      </c>
+      <c r="B314" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C314" s="16" t="inlineStr"/>
+      <c r="D314" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Hacer el control y el alta del movimiento de stock en una sola transacción</t>
+        </is>
+      </c>
+      <c r="E314" s="17" t="inlineStr"/>
+      <c r="F314" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G312" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H312" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I312" s="14" t="inlineStr"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="16" t="inlineStr">
-        <is>
-          <t>T-63.2</t>
-        </is>
-      </c>
-      <c r="B313" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C313" s="16" t="inlineStr"/>
-      <c r="D313" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Aplicarlo en la interfaz y en los títulos de las pantallas</t>
-        </is>
-      </c>
-      <c r="E313" s="17" t="inlineStr"/>
-      <c r="F313" s="17" t="inlineStr">
+      <c r="G314" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H314" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I314" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="14" t="inlineStr">
+        <is>
+          <t>T-89.3</t>
+        </is>
+      </c>
+      <c r="B315" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C315" s="14" t="inlineStr"/>
+      <c r="D315" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Hacer lo mismo con el movimiento de dinero de una venta</t>
+        </is>
+      </c>
+      <c r="E315" s="15" t="inlineStr"/>
+      <c r="F315" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G313" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H313" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I313" s="16" t="inlineStr"/>
-    </row>
-    <row r="314">
-      <c r="A314" s="14" t="inlineStr">
-        <is>
-          <t>T-63.3</t>
-        </is>
-      </c>
-      <c r="B314" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C314" s="14" t="inlineStr"/>
-      <c r="D314" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Renombrar la base de datos y el repositorio</t>
-        </is>
-      </c>
-      <c r="E314" s="15" t="inlineStr"/>
-      <c r="F314" s="15" t="inlineStr">
+      <c r="G315" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H315" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I315" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="16" t="inlineStr">
+        <is>
+          <t>T-89.4</t>
+        </is>
+      </c>
+      <c r="B316" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C316" s="16" t="inlineStr"/>
+      <c r="D316" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Corregir la marca del cobro para que mire si el movimiento sigue vigente</t>
+        </is>
+      </c>
+      <c r="E316" s="17" t="inlineStr"/>
+      <c r="F316" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G314" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H314" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I314" s="14" t="inlineStr"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="16" t="inlineStr">
-        <is>
-          <t>T-63.4</t>
-        </is>
-      </c>
-      <c r="B315" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C315" s="16" t="inlineStr"/>
-      <c r="D315" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Actualizar la documentación y la validación de idea</t>
-        </is>
-      </c>
-      <c r="E315" s="17" t="inlineStr"/>
-      <c r="F315" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G315" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H315" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I315" s="16" t="inlineStr"/>
-    </row>
-    <row r="316" ht="26" customHeight="1">
-      <c r="A316" s="12" t="inlineStr">
-        <is>
-          <t>HU-64</t>
-        </is>
-      </c>
-      <c r="B316" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C316" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D316" s="12" t="inlineStr">
-        <is>
-          <t>Como usuario con poca experiencia digital quiero una interfaz clara para poder usar el sistema sin ayuda.</t>
-        </is>
-      </c>
-      <c r="E316" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F316" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G316" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H316" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I316" s="12" t="inlineStr"/>
+      <c r="G316" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H316" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I316" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="14" t="inlineStr">
         <is>
-          <t>T-64.1</t>
+          <t>T-89.5</t>
         </is>
       </c>
       <c r="B317" s="14" t="inlineStr">
@@ -17975,7 +18858,7 @@
       <c r="C317" s="14" t="inlineStr"/>
       <c r="D317" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Revisar los textos y rótulos de todas las pantallas</t>
+          <t xml:space="preserve">    No revivir en cascada lo que el administrador dio de baja a propósito</t>
         </is>
       </c>
       <c r="E317" s="15" t="inlineStr"/>
@@ -17986,20 +18869,24 @@
       </c>
       <c r="G317" s="15" t="inlineStr">
         <is>
-          <t>Sprint 13</t>
+          <t>Sprint 09</t>
         </is>
       </c>
       <c r="H317" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I317" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I317" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="16" t="inlineStr">
         <is>
-          <t>T-64.2</t>
+          <t>T-89.6</t>
         </is>
       </c>
       <c r="B318" s="16" t="inlineStr">
@@ -18010,7 +18897,7 @@
       <c r="C318" s="16" t="inlineStr"/>
       <c r="D318" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Agregar ayudas contextuales</t>
+          <t xml:space="preserve">    Validar el largo de los textos y pedir modo estricto a la base</t>
         </is>
       </c>
       <c r="E318" s="17" t="inlineStr"/>
@@ -18021,20 +18908,24 @@
       </c>
       <c r="G318" s="17" t="inlineStr">
         <is>
-          <t>Sprint 13</t>
+          <t>Sprint 09</t>
         </is>
       </c>
       <c r="H318" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I318" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I318" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="14" t="inlineStr">
         <is>
-          <t>T-64.3</t>
+          <t>T-89.7</t>
         </is>
       </c>
       <c r="B319" s="14" t="inlineStr">
@@ -18045,7 +18936,7 @@
       <c r="C319" s="14" t="inlineStr"/>
       <c r="D319" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Revisar el contraste y el tamaño de la tipografía</t>
+          <t xml:space="preserve">    Devolver JSON en vez del stack trace cuando el pedido viene mal</t>
         </is>
       </c>
       <c r="E319" s="15" t="inlineStr"/>
@@ -18056,416 +18947,420 @@
       </c>
       <c r="G319" s="15" t="inlineStr">
         <is>
-          <t>Sprint 13</t>
+          <t>Sprint 09</t>
         </is>
       </c>
       <c r="H319" s="14" t="inlineStr">
         <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I319" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="26" customHeight="1">
+      <c r="A320" s="12" t="inlineStr">
+        <is>
+          <t>HU-84</t>
+        </is>
+      </c>
+      <c r="B320" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C320" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D320" s="12" t="inlineStr">
+        <is>
+          <t>Como usuario quiero que cada cosa se llame siempre igual para aprender una vez y no tener que adivinar.</t>
+        </is>
+      </c>
+      <c r="E320" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F320" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G320" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H320" s="12" t="inlineStr">
+        <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I319" s="14" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" s="16" t="inlineStr">
-        <is>
-          <t>T-64.4</t>
-        </is>
-      </c>
-      <c r="B320" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C320" s="16" t="inlineStr"/>
-      <c r="D320" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Validar la interfaz con un usuario real</t>
-        </is>
-      </c>
-      <c r="E320" s="17" t="inlineStr"/>
-      <c r="F320" s="17" t="inlineStr">
+      <c r="I320" s="12" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="14" t="inlineStr">
+        <is>
+          <t>T-84.1</t>
+        </is>
+      </c>
+      <c r="B321" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C321" s="14" t="inlineStr"/>
+      <c r="D321" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Decidir los nombres en grupo (naturaleza, categorías, anular/dar de baja)</t>
+        </is>
+      </c>
+      <c r="E321" s="15" t="inlineStr"/>
+      <c r="F321" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G320" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H320" s="16" t="inlineStr">
+      <c r="G321" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H321" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I320" s="16" t="inlineStr"/>
-    </row>
-    <row r="321" ht="16" customHeight="1">
-      <c r="A321" s="12" t="inlineStr">
-        <is>
-          <t>HU-65</t>
-        </is>
-      </c>
-      <c r="B321" s="12" t="inlineStr">
+      <c r="I321" s="14" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="16" t="inlineStr">
+        <is>
+          <t>T-84.2</t>
+        </is>
+      </c>
+      <c r="B322" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C322" s="16" t="inlineStr"/>
+      <c r="D322" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Reemplazar 'naturaleza' por una pregunta en castellano llano</t>
+        </is>
+      </c>
+      <c r="E322" s="17" t="inlineStr"/>
+      <c r="F322" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G322" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H322" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I322" s="16" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="14" t="inlineStr">
+        <is>
+          <t>T-84.3</t>
+        </is>
+      </c>
+      <c r="B323" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C323" s="14" t="inlineStr"/>
+      <c r="D323" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ponerle apellido a las dos pantallas de categorías (dinero y productos)</t>
+        </is>
+      </c>
+      <c r="E323" s="15" t="inlineStr"/>
+      <c r="F323" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G323" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H323" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I323" s="14" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="16" t="inlineStr">
+        <is>
+          <t>T-84.4</t>
+        </is>
+      </c>
+      <c r="B324" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C324" s="16" t="inlineStr"/>
+      <c r="D324" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Unificar anular / dar de baja / desactivar en dos palabras y dos íconos</t>
+        </is>
+      </c>
+      <c r="E324" s="17" t="inlineStr"/>
+      <c r="F324" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G324" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H324" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I324" s="16" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="14" t="inlineStr">
+        <is>
+          <t>T-84.5</t>
+        </is>
+      </c>
+      <c r="B325" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C325" s="14" t="inlineStr"/>
+      <c r="D325" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Renombrar los movimientos de stock como entradas y salidas</t>
+        </is>
+      </c>
+      <c r="E325" s="15" t="inlineStr"/>
+      <c r="F325" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G325" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H325" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I325" s="14" t="inlineStr"/>
+    </row>
+    <row r="326" ht="26" customHeight="1">
+      <c r="A326" s="12" t="inlineStr">
+        <is>
+          <t>HU-85</t>
+        </is>
+      </c>
+      <c r="B326" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C321" s="12" t="inlineStr">
+      <c r="C326" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D321" s="12" t="inlineStr">
-        <is>
-          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
-        </is>
-      </c>
-      <c r="E321" s="13" t="inlineStr">
+      <c r="D326" s="12" t="inlineStr">
+        <is>
+          <t>Como operador quiero ver en el celular la columna que me importa para no tener que arrastrar la tabla de costado.</t>
+        </is>
+      </c>
+      <c r="E326" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F321" s="13" t="inlineStr">
+      <c r="F326" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G321" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H321" s="12" t="inlineStr">
+      <c r="G326" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H326" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I321" s="12" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="14" t="inlineStr">
-        <is>
-          <t>T-65.1</t>
-        </is>
-      </c>
-      <c r="B322" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C322" s="14" t="inlineStr"/>
-      <c r="D322" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Revisar las pantallas de los módulos nuevos en ancho de celular</t>
-        </is>
-      </c>
-      <c r="E322" s="15" t="inlineStr"/>
-      <c r="F322" s="15" t="inlineStr">
+      <c r="I326" s="12" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="14" t="inlineStr">
+        <is>
+          <t>T-85.1</t>
+        </is>
+      </c>
+      <c r="B327" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C327" s="14" t="inlineStr"/>
+      <c r="D327" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Convertir los tres listados en tarjetas por debajo de 768 px</t>
+        </is>
+      </c>
+      <c r="E327" s="15" t="inlineStr"/>
+      <c r="F327" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G322" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H322" s="14" t="inlineStr">
+      <c r="G327" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H327" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I322" s="14" t="inlineStr"/>
-    </row>
-    <row r="323">
-      <c r="A323" s="16" t="inlineStr">
-        <is>
-          <t>T-65.2</t>
-        </is>
-      </c>
-      <c r="B323" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C323" s="16" t="inlineStr"/>
-      <c r="D323" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Validar en Chrome y en un segundo navegador</t>
-        </is>
-      </c>
-      <c r="E323" s="17" t="inlineStr"/>
-      <c r="F323" s="17" t="inlineStr">
+      <c r="I327" s="14" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="16" t="inlineStr">
+        <is>
+          <t>T-85.2</t>
+        </is>
+      </c>
+      <c r="B328" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C328" s="16" t="inlineStr"/>
+      <c r="D328" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compactar el encabezado en celular</t>
+        </is>
+      </c>
+      <c r="E328" s="17" t="inlineStr"/>
+      <c r="F328" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G323" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H323" s="16" t="inlineStr">
+      <c r="G328" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H328" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I323" s="16" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="14" t="inlineStr">
-        <is>
-          <t>T-65.3</t>
-        </is>
-      </c>
-      <c r="B324" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C324" s="14" t="inlineStr"/>
-      <c r="D324" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Validar en un celular real</t>
-        </is>
-      </c>
-      <c r="E324" s="15" t="inlineStr"/>
-      <c r="F324" s="15" t="inlineStr">
+      <c r="I328" s="16" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="14" t="inlineStr">
+        <is>
+          <t>T-85.3</t>
+        </is>
+      </c>
+      <c r="B329" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C329" s="14" t="inlineStr"/>
+      <c r="D329" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Validar en 375 px que no quede scroll horizontal</t>
+        </is>
+      </c>
+      <c r="E329" s="15" t="inlineStr"/>
+      <c r="F329" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G324" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H324" s="14" t="inlineStr">
+      <c r="G329" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H329" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I324" s="14" t="inlineStr"/>
-    </row>
-    <row r="325" ht="16" customHeight="1">
-      <c r="A325" s="12" t="inlineStr">
-        <is>
-          <t>HU-66</t>
-        </is>
-      </c>
-      <c r="B325" s="12" t="inlineStr">
+      <c r="I329" s="14" t="inlineStr"/>
+    </row>
+    <row r="330" ht="26" customHeight="1">
+      <c r="A330" s="12" t="inlineStr">
+        <is>
+          <t>HU-86</t>
+        </is>
+      </c>
+      <c r="B330" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C325" s="12" t="inlineStr">
+      <c r="C330" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D325" s="12" t="inlineStr">
-        <is>
-          <t>Como equipo quiero dejar el proyecto documentado para poder continuarlo el año próximo.</t>
-        </is>
-      </c>
-      <c r="E325" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F325" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G325" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H325" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I325" s="12" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" s="14" t="inlineStr">
-        <is>
-          <t>T-66.1</t>
-        </is>
-      </c>
-      <c r="B326" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C326" s="14" t="inlineStr"/>
-      <c r="D326" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Escribir el README con las instrucciones de instalación</t>
-        </is>
-      </c>
-      <c r="E326" s="15" t="inlineStr"/>
-      <c r="F326" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G326" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H326" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I326" s="14" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" s="16" t="inlineStr">
-        <is>
-          <t>T-66.2</t>
-        </is>
-      </c>
-      <c r="B327" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C327" s="16" t="inlineStr"/>
-      <c r="D327" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Escribir el manual de usuario básico</t>
-        </is>
-      </c>
-      <c r="E327" s="17" t="inlineStr"/>
-      <c r="F327" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G327" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H327" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I327" s="16" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" s="14" t="inlineStr">
-        <is>
-          <t>T-66.3</t>
-        </is>
-      </c>
-      <c r="B328" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C328" s="14" t="inlineStr"/>
-      <c r="D328" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Documentar el modelo de datos</t>
-        </is>
-      </c>
-      <c r="E328" s="15" t="inlineStr"/>
-      <c r="F328" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G328" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H328" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I328" s="14" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" s="16" t="inlineStr">
-        <is>
-          <t>T-66.4</t>
-        </is>
-      </c>
-      <c r="B329" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C329" s="16" t="inlineStr"/>
-      <c r="D329" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Documentar el diseño de los módulos que quedaron sin implementar</t>
-        </is>
-      </c>
-      <c r="E329" s="17" t="inlineStr"/>
-      <c r="F329" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G329" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H329" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I329" s="16" t="inlineStr"/>
-    </row>
-    <row r="330" ht="16" customHeight="1">
-      <c r="A330" s="12" t="inlineStr">
-        <is>
-          <t>HU-67</t>
-        </is>
-      </c>
-      <c r="B330" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C330" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
       <c r="D330" s="12" t="inlineStr">
         <is>
-          <t>Como equipo quiero probar el sistema completo para entregar una versión estable.</t>
+          <t>Como administrador quiero encontrar la configuración en un solo lugar para no buscarla abajo de mi nombre.</t>
         </is>
       </c>
       <c r="E330" s="13" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="F330" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G330" s="13" t="inlineStr">
         <is>
-          <t>Sprint 13</t>
+          <t>Sprint 09</t>
         </is>
       </c>
       <c r="H330" s="12" t="inlineStr">
@@ -18478,7 +19373,7 @@
     <row r="331">
       <c r="A331" s="14" t="inlineStr">
         <is>
-          <t>T-67.1</t>
+          <t>T-86.1</t>
         </is>
       </c>
       <c r="B331" s="14" t="inlineStr">
@@ -18489,18 +19384,18 @@
       <c r="C331" s="14" t="inlineStr"/>
       <c r="D331" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Ejecutar la batería de pruebas de punta a punta</t>
+          <t xml:space="preserve">    Agrupar las cuatro pantallas de configuración en el menú principal</t>
         </is>
       </c>
       <c r="E331" s="15" t="inlineStr"/>
       <c r="F331" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G331" s="15" t="inlineStr">
         <is>
-          <t>Sprint 13</t>
+          <t>Sprint 09</t>
         </is>
       </c>
       <c r="H331" s="14" t="inlineStr">
@@ -18513,7 +19408,7 @@
     <row r="332">
       <c r="A332" s="16" t="inlineStr">
         <is>
-          <t>T-67.2</t>
+          <t>T-86.2</t>
         </is>
       </c>
       <c r="B332" s="16" t="inlineStr">
@@ -18524,18 +19419,18 @@
       <c r="C332" s="16" t="inlineStr"/>
       <c r="D332" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Corregir los errores detectados</t>
+          <t xml:space="preserve">    Dejar en el menú del usuario sólo lo personal y cerrar sesión</t>
         </is>
       </c>
       <c r="E332" s="17" t="inlineStr"/>
       <c r="F332" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G332" s="17" t="inlineStr">
         <is>
-          <t>Sprint 13</t>
+          <t>Sprint 09</t>
         </is>
       </c>
       <c r="H332" s="16" t="inlineStr">
@@ -18548,7 +19443,7 @@
     <row r="333">
       <c r="A333" s="14" t="inlineStr">
         <is>
-          <t>T-67.3</t>
+          <t>T-86.3</t>
         </is>
       </c>
       <c r="B333" s="14" t="inlineStr">
@@ -18559,241 +19454,257 @@
       <c r="C333" s="14" t="inlineStr"/>
       <c r="D333" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Unificar la carga del encabezado en un archivo compartido</t>
+          <t xml:space="preserve">    Mover el acceso a motivos desde Productos a Stock</t>
         </is>
       </c>
       <c r="E333" s="15" t="inlineStr"/>
       <c r="F333" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G333" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H333" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I333" s="14" t="inlineStr"/>
+    </row>
+    <row r="334" ht="26" customHeight="1">
+      <c r="A334" s="12" t="inlineStr">
+        <is>
+          <t>HU-50</t>
+        </is>
+      </c>
+      <c r="B334" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C334" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D334" s="12" t="inlineStr">
+        <is>
+          <t>Como equipo quiero probar los módulos de productos y servicios para entregarlos sin errores.</t>
+        </is>
+      </c>
+      <c r="E334" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F334" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G334" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H334" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I334" s="12" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="14" t="inlineStr">
+        <is>
+          <t>T-50.1</t>
+        </is>
+      </c>
+      <c r="B335" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C335" s="14" t="inlineStr"/>
+      <c r="D335" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de stock</t>
+        </is>
+      </c>
+      <c r="E335" s="15" t="inlineStr"/>
+      <c r="F335" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G335" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H335" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I335" s="14" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="16" t="inlineStr">
+        <is>
+          <t>T-50.2</t>
+        </is>
+      </c>
+      <c r="B336" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C336" s="16" t="inlineStr"/>
+      <c r="D336" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de servicios</t>
+        </is>
+      </c>
+      <c r="E336" s="17" t="inlineStr"/>
+      <c r="F336" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G336" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H336" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I336" s="16" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="14" t="inlineStr">
+        <is>
+          <t>T-50.3</t>
+        </is>
+      </c>
+      <c r="B337" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C337" s="14" t="inlineStr"/>
+      <c r="D337" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Validar ambas pantallas en celular</t>
+        </is>
+      </c>
+      <c r="E337" s="15" t="inlineStr"/>
+      <c r="F337" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G337" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H337" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I337" s="14" t="inlineStr"/>
+    </row>
+    <row r="338" ht="16" customHeight="1">
+      <c r="A338" s="12" t="inlineStr">
+        <is>
+          <t>HU-62</t>
+        </is>
+      </c>
+      <c r="B338" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C338" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D338" s="12" t="inlineStr">
+        <is>
+          <t>Como equipo quiero probar el módulo de articulación para entregarlo funcionando.</t>
+        </is>
+      </c>
+      <c r="E338" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F338" s="13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G333" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H333" s="14" t="inlineStr">
+      <c r="G338" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 12</t>
+        </is>
+      </c>
+      <c r="H338" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I333" s="14" t="inlineStr"/>
-    </row>
-    <row r="334" ht="20" customHeight="1">
-      <c r="A334" s="9" t="inlineStr">
-        <is>
-          <t>E11</t>
-        </is>
-      </c>
-      <c r="B334" s="9" t="inlineStr">
-        <is>
-          <t>Épica</t>
-        </is>
-      </c>
-      <c r="C334" s="9" t="inlineStr">
-        <is>
-          <t>Chat y Notificaciones</t>
-        </is>
-      </c>
-      <c r="D334" s="9" t="inlineStr">
-        <is>
-          <t>Mensajería entre empresas (posterior al MVP)</t>
-        </is>
-      </c>
-      <c r="E334" s="10" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F334" s="11" t="n"/>
-      <c r="G334" s="11" t="n"/>
-      <c r="H334" s="11" t="n"/>
-      <c r="I334" s="11" t="n"/>
-    </row>
-    <row r="335" ht="16" customHeight="1">
-      <c r="A335" s="12" t="inlineStr">
-        <is>
-          <t>HU-73</t>
-        </is>
-      </c>
-      <c r="B335" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C335" s="12" t="inlineStr">
-        <is>
-          <t>Chat y Notificaciones</t>
-        </is>
-      </c>
-      <c r="D335" s="12" t="inlineStr">
-        <is>
-          <t>Como empresa quiero chatear con otra empresa para coordinar una articulación.</t>
-        </is>
-      </c>
-      <c r="E335" s="13" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F335" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G335" s="13" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H335" s="12" t="inlineStr">
+      <c r="I338" s="12" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="14" t="inlineStr">
+        <is>
+          <t>T-62.1</t>
+        </is>
+      </c>
+      <c r="B339" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C339" s="14" t="inlineStr"/>
+      <c r="D339" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de coincidencia</t>
+        </is>
+      </c>
+      <c r="E339" s="15" t="inlineStr"/>
+      <c r="F339" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G339" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 12</t>
+        </is>
+      </c>
+      <c r="H339" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I335" s="12" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" s="14" t="inlineStr">
-        <is>
-          <t>T-73.1</t>
-        </is>
-      </c>
-      <c r="B336" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C336" s="14" t="inlineStr"/>
-      <c r="D336" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Diseñar la pantalla de chat</t>
-        </is>
-      </c>
-      <c r="E336" s="15" t="inlineStr"/>
-      <c r="F336" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G336" s="15" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H336" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I336" s="14" t="inlineStr"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="16" t="inlineStr">
-        <is>
-          <t>T-73.2</t>
-        </is>
-      </c>
-      <c r="B337" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C337" s="16" t="inlineStr"/>
-      <c r="D337" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el envío y la recepción de mensajes</t>
-        </is>
-      </c>
-      <c r="E337" s="17" t="inlineStr"/>
-      <c r="F337" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G337" s="17" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H337" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I337" s="16" t="inlineStr"/>
-    </row>
-    <row r="338">
-      <c r="A338" s="14" t="inlineStr">
-        <is>
-          <t>T-73.3</t>
-        </is>
-      </c>
-      <c r="B338" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C338" s="14" t="inlineStr"/>
-      <c r="D338" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agregar notificaciones de mensaje nuevo</t>
-        </is>
-      </c>
-      <c r="E338" s="15" t="inlineStr"/>
-      <c r="F338" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G338" s="15" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H338" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I338" s="14" t="inlineStr"/>
-    </row>
-    <row r="339" ht="20" customHeight="1">
-      <c r="A339" s="9" t="inlineStr">
-        <is>
-          <t>E12</t>
-        </is>
-      </c>
-      <c r="B339" s="9" t="inlineStr">
-        <is>
-          <t>Épica</t>
-        </is>
-      </c>
-      <c r="C339" s="9" t="inlineStr">
-        <is>
-          <t>Configuración de Módulos</t>
-        </is>
-      </c>
-      <c r="D339" s="9" t="inlineStr">
-        <is>
-          <t>Cada empresa activa sólo los módulos que usa</t>
-        </is>
-      </c>
-      <c r="E339" s="10" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F339" s="11" t="n"/>
-      <c r="G339" s="11" t="n"/>
-      <c r="H339" s="11" t="n"/>
-      <c r="I339" s="11" t="n"/>
+      <c r="I339" s="14" t="inlineStr"/>
     </row>
     <row r="340" ht="26" customHeight="1">
       <c r="A340" s="12" t="inlineStr">
         <is>
-          <t>HU-34</t>
+          <t>HU-63</t>
         </is>
       </c>
       <c r="B340" s="12" t="inlineStr">
@@ -18803,12 +19714,12 @@
       </c>
       <c r="C340" s="12" t="inlineStr">
         <is>
-          <t>Configuración de Módulos</t>
+          <t>Calidad, UX y Documentación</t>
         </is>
       </c>
       <c r="D340" s="12" t="inlineStr">
         <is>
-          <t>Como administrador de la empresa quiero activar sólo los módulos que mi empresa usa para no ver funciones que no necesito.</t>
+          <t>Como equipo quiero definir el nombre y la identidad del producto para que acompañen al público al que apunta.</t>
         </is>
       </c>
       <c r="E340" s="13" t="inlineStr">
@@ -18818,29 +19729,25 @@
       </c>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G340" s="13" t="inlineStr">
         <is>
-          <t>Sprint 06</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H340" s="12" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I340" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I340" s="12" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="14" t="inlineStr">
         <is>
-          <t>T-34.1</t>
+          <t>T-63.1</t>
         </is>
       </c>
       <c r="B341" s="14" t="inlineStr">
@@ -18851,35 +19758,31 @@
       <c r="C341" s="14" t="inlineStr"/>
       <c r="D341" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Crear la tabla de módulos activos por empresa</t>
+          <t xml:space="preserve">    Definir el nombre del producto con el equipo</t>
         </is>
       </c>
       <c r="E341" s="15" t="inlineStr"/>
       <c r="F341" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G341" s="15" t="inlineStr">
         <is>
-          <t>Sprint 06</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H341" s="14" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I341" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I341" s="14" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="16" t="inlineStr">
         <is>
-          <t>T-34.2</t>
+          <t>T-63.2</t>
         </is>
       </c>
       <c r="B342" s="16" t="inlineStr">
@@ -18890,35 +19793,31 @@
       <c r="C342" s="16" t="inlineStr"/>
       <c r="D342" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el conjunto de módulos disponibles</t>
+          <t xml:space="preserve">    Aplicarlo en la interfaz y en los títulos de las pantallas</t>
         </is>
       </c>
       <c r="E342" s="17" t="inlineStr"/>
       <c r="F342" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G342" s="17" t="inlineStr">
         <is>
-          <t>Sprint 06</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H342" s="16" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I342" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I342" s="16" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="14" t="inlineStr">
         <is>
-          <t>T-34.3</t>
+          <t>T-63.3</t>
         </is>
       </c>
       <c r="B343" s="14" t="inlineStr">
@@ -18929,35 +19828,31 @@
       <c r="C343" s="14" t="inlineStr"/>
       <c r="D343" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar los endpoints de consulta y actualización</t>
+          <t xml:space="preserve">    Renombrar la base de datos y el repositorio</t>
         </is>
       </c>
       <c r="E343" s="15" t="inlineStr"/>
       <c r="F343" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G343" s="15" t="inlineStr">
         <is>
-          <t>Sprint 06</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H343" s="14" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I343" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I343" s="14" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="16" t="inlineStr">
         <is>
-          <t>T-34.4</t>
+          <t>T-63.4</t>
         </is>
       </c>
       <c r="B344" s="16" t="inlineStr">
@@ -18968,277 +19863,257 @@
       <c r="C344" s="16" t="inlineStr"/>
       <c r="D344" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar la pantalla de configuración de módulos</t>
+          <t xml:space="preserve">    Actualizar la documentación y la validación de idea</t>
         </is>
       </c>
       <c r="E344" s="17" t="inlineStr"/>
       <c r="F344" s="17" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G344" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H344" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I344" s="16" t="inlineStr"/>
+    </row>
+    <row r="345" ht="26" customHeight="1">
+      <c r="A345" s="12" t="inlineStr">
+        <is>
+          <t>HU-64</t>
+        </is>
+      </c>
+      <c r="B345" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C345" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D345" s="12" t="inlineStr">
+        <is>
+          <t>Como usuario con poca experiencia digital quiero una interfaz clara para poder usar el sistema sin ayuda.</t>
+        </is>
+      </c>
+      <c r="E345" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F345" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G345" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H345" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I345" s="12" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="14" t="inlineStr">
+        <is>
+          <t>T-64.1</t>
+        </is>
+      </c>
+      <c r="B346" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C346" s="14" t="inlineStr"/>
+      <c r="D346" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revisar los textos y rótulos de todas las pantallas</t>
+        </is>
+      </c>
+      <c r="E346" s="15" t="inlineStr"/>
+      <c r="F346" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G346" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H346" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I346" s="14" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="16" t="inlineStr">
+        <is>
+          <t>T-64.2</t>
+        </is>
+      </c>
+      <c r="B347" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C347" s="16" t="inlineStr"/>
+      <c r="D347" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agregar ayudas contextuales</t>
+        </is>
+      </c>
+      <c r="E347" s="17" t="inlineStr"/>
+      <c r="F347" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G347" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H347" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I347" s="16" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="14" t="inlineStr">
+        <is>
+          <t>T-64.3</t>
+        </is>
+      </c>
+      <c r="B348" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C348" s="14" t="inlineStr"/>
+      <c r="D348" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revisar el contraste y el tamaño de la tipografía</t>
+        </is>
+      </c>
+      <c r="E348" s="15" t="inlineStr"/>
+      <c r="F348" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G348" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H348" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I348" s="14" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="16" t="inlineStr">
+        <is>
+          <t>T-64.4</t>
+        </is>
+      </c>
+      <c r="B349" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C349" s="16" t="inlineStr"/>
+      <c r="D349" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Validar la interfaz con un usuario real</t>
+        </is>
+      </c>
+      <c r="E349" s="17" t="inlineStr"/>
+      <c r="F349" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G349" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H349" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I349" s="16" t="inlineStr"/>
+    </row>
+    <row r="350" ht="26" customHeight="1">
+      <c r="A350" s="12" t="inlineStr">
+        <is>
+          <t>HU-87</t>
+        </is>
+      </c>
+      <c r="B350" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C350" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D350" s="12" t="inlineStr">
+        <is>
+          <t>Como tesorero quiero cargar un movimiento en menos pasos para no contestar tres preguntas encadenadas.</t>
+        </is>
+      </c>
+      <c r="E350" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F350" s="13" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G344" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H344" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I344" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" s="14" t="inlineStr">
-        <is>
-          <t>T-34.5</t>
-        </is>
-      </c>
-      <c r="B345" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C345" s="14" t="inlineStr"/>
-      <c r="D345" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Mostrar en el menú sólo los módulos activos</t>
-        </is>
-      </c>
-      <c r="E345" s="15" t="inlineStr"/>
-      <c r="F345" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G345" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H345" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I345" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="26" customHeight="1">
-      <c r="A346" s="12" t="inlineStr">
-        <is>
-          <t>HU-35</t>
-        </is>
-      </c>
-      <c r="B346" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C346" s="12" t="inlineStr">
-        <is>
-          <t>Configuración de Módulos</t>
-        </is>
-      </c>
-      <c r="D346" s="12" t="inlineStr">
-        <is>
-          <t>Como sistema quiero rechazar los pedidos a módulos desactivados para que no se pueda entrar por fuera del menú.</t>
-        </is>
-      </c>
-      <c r="E346" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F346" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G346" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H346" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I346" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="14" t="inlineStr">
-        <is>
-          <t>T-35.1</t>
-        </is>
-      </c>
-      <c r="B347" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C347" s="14" t="inlineStr"/>
-      <c r="D347" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el middleware de módulo activo</t>
-        </is>
-      </c>
-      <c r="E347" s="15" t="inlineStr"/>
-      <c r="F347" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G347" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H347" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I347" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="16" t="inlineStr">
-        <is>
-          <t>T-35.2</t>
-        </is>
-      </c>
-      <c r="B348" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C348" s="16" t="inlineStr"/>
-      <c r="D348" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Aplicarlo a las rutas de movimientos y categorías</t>
-        </is>
-      </c>
-      <c r="E348" s="17" t="inlineStr"/>
-      <c r="F348" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G348" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H348" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I348" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="14" t="inlineStr">
-        <is>
-          <t>T-35.3</t>
-        </is>
-      </c>
-      <c r="B349" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C349" s="14" t="inlineStr"/>
-      <c r="D349" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Mostrar en pantalla un aviso claro cuando el módulo está apagado</t>
-        </is>
-      </c>
-      <c r="E349" s="15" t="inlineStr"/>
-      <c r="F349" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G349" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H349" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I349" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="16" t="inlineStr">
-        <is>
-          <t>T-35.4</t>
-        </is>
-      </c>
-      <c r="B350" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C350" s="16" t="inlineStr"/>
-      <c r="D350" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Distinguir el aviso de módulo apagado del de falta de permiso</t>
-        </is>
-      </c>
-      <c r="E350" s="17" t="inlineStr"/>
-      <c r="F350" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G350" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H350" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I350" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
+      <c r="G350" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H350" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I350" s="12" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="14" t="inlineStr">
         <is>
-          <t>T-35.5</t>
+          <t>T-87.1</t>
         </is>
       </c>
       <c r="B351" s="14" t="inlineStr">
@@ -19249,7 +20124,7 @@
       <c r="C351" s="14" t="inlineStr"/>
       <c r="D351" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Probar el acceso con el módulo apagado</t>
+          <t xml:space="preserve">    Reemplazar los tres desplegables encadenados por uno solo</t>
         </is>
       </c>
       <c r="E351" s="15" t="inlineStr"/>
@@ -19260,71 +20135,55 @@
       </c>
       <c r="G351" s="15" t="inlineStr">
         <is>
-          <t>Sprint 06</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H351" s="14" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I351" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="352" ht="26" customHeight="1">
-      <c r="A352" s="12" t="inlineStr">
-        <is>
-          <t>HU-36</t>
-        </is>
-      </c>
-      <c r="B352" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C352" s="12" t="inlineStr">
-        <is>
-          <t>Configuración de Módulos</t>
-        </is>
-      </c>
-      <c r="D352" s="12" t="inlineStr">
-        <is>
-          <t>Como empresa nueva quiero empezar con una configuración razonable para no tener que definir todo antes de usar el sistema.</t>
-        </is>
-      </c>
-      <c r="E352" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F352" s="13" t="inlineStr">
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I351" s="14" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="16" t="inlineStr">
+        <is>
+          <t>T-87.2</t>
+        </is>
+      </c>
+      <c r="B352" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C352" s="16" t="inlineStr"/>
+      <c r="D352" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ofrecer entró/salió como dos botones en vez de un desplegable</t>
+        </is>
+      </c>
+      <c r="E352" s="17" t="inlineStr"/>
+      <c r="F352" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G352" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H352" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I352" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
+      <c r="G352" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H352" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I352" s="16" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="14" t="inlineStr">
         <is>
-          <t>T-36.1</t>
+          <t>T-87.3</t>
         </is>
       </c>
       <c r="B353" s="14" t="inlineStr">
@@ -19335,7 +20194,7 @@
       <c r="C353" s="14" t="inlineStr"/>
       <c r="D353" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el conjunto de módulos y categorías iniciales</t>
+          <t xml:space="preserve">    Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
         </is>
       </c>
       <c r="E353" s="15" t="inlineStr"/>
@@ -19346,63 +20205,63 @@
       </c>
       <c r="G353" s="15" t="inlineStr">
         <is>
-          <t>Sprint 06</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H353" s="14" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I353" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="16" t="inlineStr">
-        <is>
-          <t>T-36.2</t>
-        </is>
-      </c>
-      <c r="B354" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C354" s="16" t="inlineStr"/>
-      <c r="D354" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar la carga automática al aprobar la empresa</t>
-        </is>
-      </c>
-      <c r="E354" s="17" t="inlineStr"/>
-      <c r="F354" s="17" t="inlineStr">
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I353" s="14" t="inlineStr"/>
+    </row>
+    <row r="354" ht="26" customHeight="1">
+      <c r="A354" s="12" t="inlineStr">
+        <is>
+          <t>HU-88</t>
+        </is>
+      </c>
+      <c r="B354" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C354" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D354" s="12" t="inlineStr">
+        <is>
+          <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
+        </is>
+      </c>
+      <c r="E354" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F354" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G354" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H354" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I354" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
+      <c r="G354" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H354" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I354" s="12" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="14" t="inlineStr">
         <is>
-          <t>T-36.3</t>
+          <t>T-88.1</t>
         </is>
       </c>
       <c r="B355" s="14" t="inlineStr">
@@ -19413,7 +20272,7 @@
       <c r="C355" s="14" t="inlineStr"/>
       <c r="D355" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Dejar la configuración escrita en la base, no deducida del catálogo</t>
+          <t xml:space="preserve">    Separar el listado vacío del listado filtrado en los cuatro listados</t>
         </is>
       </c>
       <c r="E355" s="15" t="inlineStr"/>
@@ -19424,24 +20283,20 @@
       </c>
       <c r="G355" s="15" t="inlineStr">
         <is>
-          <t>Sprint 06</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H355" s="14" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I355" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I355" s="14" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="16" t="inlineStr">
         <is>
-          <t>T-36.4</t>
+          <t>T-88.2</t>
         </is>
       </c>
       <c r="B356" s="16" t="inlineStr">
@@ -19452,7 +20307,7 @@
       <c r="C356" s="16" t="inlineStr"/>
       <c r="D356" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Evitar que una segunda aprobación duplique o pise lo ya configurado</t>
+          <t xml:space="preserve">    Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
         </is>
       </c>
       <c r="E356" s="17" t="inlineStr"/>
@@ -19463,24 +20318,20 @@
       </c>
       <c r="G356" s="17" t="inlineStr">
         <is>
-          <t>Sprint 06</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H356" s="16" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I356" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I356" s="16" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="14" t="inlineStr">
         <is>
-          <t>T-36.5</t>
+          <t>T-88.3</t>
         </is>
       </c>
       <c r="B357" s="14" t="inlineStr">
@@ -19491,7 +20342,7 @@
       <c r="C357" s="14" t="inlineStr"/>
       <c r="D357" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Probar el alta de una empresa nueva de punta a punta</t>
+          <t xml:space="preserve">    Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
         </is>
       </c>
       <c r="E357" s="15" t="inlineStr"/>
@@ -19502,281 +20353,281 @@
       </c>
       <c r="G357" s="15" t="inlineStr">
         <is>
-          <t>Sprint 06</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H357" s="14" t="inlineStr">
         <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I357" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="358" ht="20" customHeight="1">
-      <c r="A358" s="9" t="inlineStr">
-        <is>
-          <t>E13</t>
-        </is>
-      </c>
-      <c r="B358" s="9" t="inlineStr">
-        <is>
-          <t>Épica</t>
-        </is>
-      </c>
-      <c r="C358" s="9" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D358" s="9" t="inlineStr">
-        <is>
-          <t>Catálogo de servicios que generan ingreso o egreso</t>
-        </is>
-      </c>
-      <c r="E358" s="10" t="inlineStr">
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I357" s="14" t="inlineStr"/>
+    </row>
+    <row r="358" ht="16" customHeight="1">
+      <c r="A358" s="12" t="inlineStr">
+        <is>
+          <t>HU-65</t>
+        </is>
+      </c>
+      <c r="B358" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C358" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D358" s="12" t="inlineStr">
+        <is>
+          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
+        </is>
+      </c>
+      <c r="E358" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F358" s="11" t="n"/>
-      <c r="G358" s="11" t="n"/>
-      <c r="H358" s="11" t="n"/>
-      <c r="I358" s="11" t="n"/>
-    </row>
-    <row r="359" ht="26" customHeight="1">
-      <c r="A359" s="12" t="inlineStr">
-        <is>
-          <t>HU-47</t>
-        </is>
-      </c>
-      <c r="B359" s="12" t="inlineStr">
+      <c r="F358" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G358" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H358" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I358" s="12" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="14" t="inlineStr">
+        <is>
+          <t>T-65.1</t>
+        </is>
+      </c>
+      <c r="B359" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C359" s="14" t="inlineStr"/>
+      <c r="D359" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revisar las pantallas de los módulos nuevos en ancho de celular</t>
+        </is>
+      </c>
+      <c r="E359" s="15" t="inlineStr"/>
+      <c r="F359" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G359" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H359" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I359" s="14" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="16" t="inlineStr">
+        <is>
+          <t>T-65.2</t>
+        </is>
+      </c>
+      <c r="B360" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C360" s="16" t="inlineStr"/>
+      <c r="D360" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Validar en Chrome y en un segundo navegador</t>
+        </is>
+      </c>
+      <c r="E360" s="17" t="inlineStr"/>
+      <c r="F360" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G360" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H360" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I360" s="16" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="14" t="inlineStr">
+        <is>
+          <t>T-65.3</t>
+        </is>
+      </c>
+      <c r="B361" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C361" s="14" t="inlineStr"/>
+      <c r="D361" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Validar en un celular real</t>
+        </is>
+      </c>
+      <c r="E361" s="15" t="inlineStr"/>
+      <c r="F361" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G361" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H361" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I361" s="14" t="inlineStr"/>
+    </row>
+    <row r="362" ht="16" customHeight="1">
+      <c r="A362" s="12" t="inlineStr">
+        <is>
+          <t>HU-66</t>
+        </is>
+      </c>
+      <c r="B362" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C359" s="12" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D359" s="12" t="inlineStr">
-        <is>
-          <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
-        </is>
-      </c>
-      <c r="E359" s="13" t="inlineStr">
+      <c r="C362" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D362" s="12" t="inlineStr">
+        <is>
+          <t>Como equipo quiero dejar el proyecto documentado para poder continuarlo el año próximo.</t>
+        </is>
+      </c>
+      <c r="E362" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F359" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G359" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H359" s="12" t="inlineStr">
+      <c r="F362" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G362" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H362" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I359" s="12" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" s="14" t="inlineStr">
-        <is>
-          <t>T-47.1</t>
-        </is>
-      </c>
-      <c r="B360" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C360" s="14" t="inlineStr"/>
-      <c r="D360" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Reutilizar el modelo de productos agregando la distinción de servicio</t>
-        </is>
-      </c>
-      <c r="E360" s="15" t="inlineStr"/>
-      <c r="F360" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G360" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H360" s="14" t="inlineStr">
+      <c r="I362" s="12" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="14" t="inlineStr">
+        <is>
+          <t>T-66.1</t>
+        </is>
+      </c>
+      <c r="B363" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C363" s="14" t="inlineStr"/>
+      <c r="D363" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Escribir el README con las instrucciones de instalación</t>
+        </is>
+      </c>
+      <c r="E363" s="15" t="inlineStr"/>
+      <c r="F363" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G363" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H363" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I360" s="14" t="inlineStr"/>
-    </row>
-    <row r="361">
-      <c r="A361" s="16" t="inlineStr">
-        <is>
-          <t>T-47.2</t>
-        </is>
-      </c>
-      <c r="B361" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C361" s="16" t="inlineStr"/>
-      <c r="D361" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el alta, la edición y la baja lógica</t>
-        </is>
-      </c>
-      <c r="E361" s="17" t="inlineStr"/>
-      <c r="F361" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G361" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H361" s="16" t="inlineStr">
+      <c r="I363" s="14" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="16" t="inlineStr">
+        <is>
+          <t>T-66.2</t>
+        </is>
+      </c>
+      <c r="B364" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C364" s="16" t="inlineStr"/>
+      <c r="D364" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Escribir el manual de usuario básico</t>
+        </is>
+      </c>
+      <c r="E364" s="17" t="inlineStr"/>
+      <c r="F364" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G364" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H364" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I361" s="16" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" s="14" t="inlineStr">
-        <is>
-          <t>T-47.3</t>
-        </is>
-      </c>
-      <c r="B362" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C362" s="14" t="inlineStr"/>
-      <c r="D362" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Diseñar la pantalla de servicios</t>
-        </is>
-      </c>
-      <c r="E362" s="15" t="inlineStr"/>
-      <c r="F362" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G362" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H362" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I362" s="14" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" s="16" t="inlineStr">
-        <is>
-          <t>T-47.4</t>
-        </is>
-      </c>
-      <c r="B363" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C363" s="16" t="inlineStr"/>
-      <c r="D363" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Verificar que los servicios no lleven existencias</t>
-        </is>
-      </c>
-      <c r="E363" s="17" t="inlineStr"/>
-      <c r="F363" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G363" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H363" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I363" s="16" t="inlineStr"/>
-    </row>
-    <row r="364" ht="26" customHeight="1">
-      <c r="A364" s="12" t="inlineStr">
-        <is>
-          <t>HU-48</t>
-        </is>
-      </c>
-      <c r="B364" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C364" s="12" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D364" s="12" t="inlineStr">
-        <is>
-          <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
-        </is>
-      </c>
-      <c r="E364" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F364" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G364" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H364" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I364" s="12" t="inlineStr"/>
+      <c r="I364" s="16" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="14" t="inlineStr">
         <is>
-          <t>T-48.1</t>
+          <t>T-66.3</t>
         </is>
       </c>
       <c r="B365" s="14" t="inlineStr">
@@ -19787,18 +20638,18 @@
       <c r="C365" s="14" t="inlineStr"/>
       <c r="D365" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Vincular el movimiento económico con el servicio</t>
+          <t xml:space="preserve">    Documentar el modelo de datos</t>
         </is>
       </c>
       <c r="E365" s="15" t="inlineStr"/>
       <c r="F365" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G365" s="15" t="inlineStr">
         <is>
-          <t>Sprint 09</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H365" s="14" t="inlineStr">
@@ -19811,7 +20662,7 @@
     <row r="366">
       <c r="A366" s="16" t="inlineStr">
         <is>
-          <t>T-48.2</t>
+          <t>T-66.4</t>
         </is>
       </c>
       <c r="B366" s="16" t="inlineStr">
@@ -19822,18 +20673,18 @@
       <c r="C366" s="16" t="inlineStr"/>
       <c r="D366" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Agregar el servicio al formulario de movimiento</t>
+          <t xml:space="preserve">    Documentar el diseño de los módulos que quedaron sin implementar</t>
         </is>
       </c>
       <c r="E366" s="17" t="inlineStr"/>
       <c r="F366" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G366" s="17" t="inlineStr">
         <is>
-          <t>Sprint 09</t>
+          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H366" s="16" t="inlineStr">
@@ -19843,158 +20694,158 @@
       </c>
       <c r="I366" s="16" t="inlineStr"/>
     </row>
-    <row r="367">
-      <c r="A367" s="14" t="inlineStr">
-        <is>
-          <t>T-48.3</t>
-        </is>
-      </c>
-      <c r="B367" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C367" s="14" t="inlineStr"/>
-      <c r="D367" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agregar el filtro por servicio en el listado</t>
-        </is>
-      </c>
-      <c r="E367" s="15" t="inlineStr"/>
-      <c r="F367" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G367" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H367" s="14" t="inlineStr">
+    <row r="367" ht="16" customHeight="1">
+      <c r="A367" s="12" t="inlineStr">
+        <is>
+          <t>HU-67</t>
+        </is>
+      </c>
+      <c r="B367" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C367" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D367" s="12" t="inlineStr">
+        <is>
+          <t>Como equipo quiero probar el sistema completo para entregar una versión estable.</t>
+        </is>
+      </c>
+      <c r="E367" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F367" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G367" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H367" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I367" s="14" t="inlineStr"/>
-    </row>
-    <row r="368" ht="16" customHeight="1">
-      <c r="A368" s="12" t="inlineStr">
-        <is>
-          <t>HU-49</t>
-        </is>
-      </c>
-      <c r="B368" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C368" s="12" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D368" s="12" t="inlineStr">
-        <is>
-          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
-        </is>
-      </c>
-      <c r="E368" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F368" s="13" t="inlineStr">
+      <c r="I367" s="12" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="14" t="inlineStr">
+        <is>
+          <t>T-67.1</t>
+        </is>
+      </c>
+      <c r="B368" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C368" s="14" t="inlineStr"/>
+      <c r="D368" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ejecutar la batería de pruebas de punta a punta</t>
+        </is>
+      </c>
+      <c r="E368" s="15" t="inlineStr"/>
+      <c r="F368" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G368" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H368" s="12" t="inlineStr">
+      <c r="G368" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H368" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I368" s="12" t="inlineStr"/>
+      <c r="I368" s="14" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="14" t="inlineStr">
-        <is>
-          <t>T-49.1</t>
-        </is>
-      </c>
-      <c r="B369" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C369" s="14" t="inlineStr"/>
-      <c r="D369" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar la consulta agrupada por servicio</t>
-        </is>
-      </c>
-      <c r="E369" s="15" t="inlineStr"/>
-      <c r="F369" s="15" t="inlineStr">
+      <c r="A369" s="16" t="inlineStr">
+        <is>
+          <t>T-67.2</t>
+        </is>
+      </c>
+      <c r="B369" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C369" s="16" t="inlineStr"/>
+      <c r="D369" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Corregir los errores detectados</t>
+        </is>
+      </c>
+      <c r="E369" s="17" t="inlineStr"/>
+      <c r="F369" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G369" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H369" s="14" t="inlineStr">
+      <c r="G369" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H369" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I369" s="14" t="inlineStr"/>
+      <c r="I369" s="16" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="16" t="inlineStr">
-        <is>
-          <t>T-49.2</t>
-        </is>
-      </c>
-      <c r="B370" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C370" s="16" t="inlineStr"/>
-      <c r="D370" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Diseñar la visualización del resumen</t>
-        </is>
-      </c>
-      <c r="E370" s="17" t="inlineStr"/>
-      <c r="F370" s="17" t="inlineStr">
+      <c r="A370" s="14" t="inlineStr">
+        <is>
+          <t>T-67.3</t>
+        </is>
+      </c>
+      <c r="B370" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C370" s="14" t="inlineStr"/>
+      <c r="D370" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Unificar la carga del encabezado en un archivo compartido</t>
+        </is>
+      </c>
+      <c r="E370" s="15" t="inlineStr"/>
+      <c r="F370" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G370" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H370" s="16" t="inlineStr">
+      <c r="G370" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H370" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I370" s="16" t="inlineStr"/>
+      <c r="I370" s="14" t="inlineStr"/>
     </row>
     <row r="371" ht="20" customHeight="1">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>E14</t>
+          <t>E11</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20004,12 +20855,12 @@
       </c>
       <c r="C371" s="9" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Chat y Notificaciones</t>
         </is>
       </c>
       <c r="D371" s="9" t="inlineStr">
         <is>
-          <t>Vacaciones, licencias y documentación del personal (backlog futuro)</t>
+          <t>Mensajería entre empresas (posterior al MVP)</t>
         </is>
       </c>
       <c r="E371" s="10" t="inlineStr">
@@ -20025,7 +20876,7 @@
     <row r="372" ht="16" customHeight="1">
       <c r="A372" s="12" t="inlineStr">
         <is>
-          <t>HU-68</t>
+          <t>HU-73</t>
         </is>
       </c>
       <c r="B372" s="12" t="inlineStr">
@@ -20035,17 +20886,17 @@
       </c>
       <c r="C372" s="12" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Chat y Notificaciones</t>
         </is>
       </c>
       <c r="D372" s="12" t="inlineStr">
         <is>
-          <t>Como empleado quiero solicitar días de vacaciones para gestionarlos sin papeles.</t>
+          <t>Como empresa quiero chatear con otra empresa para coordinar una articulación.</t>
         </is>
       </c>
       <c r="E372" s="13" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="F372" s="13" t="inlineStr">
@@ -20068,7 +20919,7 @@
     <row r="373">
       <c r="A373" s="14" t="inlineStr">
         <is>
-          <t>T-68.1</t>
+          <t>T-73.1</t>
         </is>
       </c>
       <c r="B373" s="14" t="inlineStr">
@@ -20079,7 +20930,7 @@
       <c r="C373" s="14" t="inlineStr"/>
       <c r="D373" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar el modelo de licencias y saldo de días</t>
+          <t xml:space="preserve">    Diseñar la pantalla de chat</t>
         </is>
       </c>
       <c r="E373" s="15" t="inlineStr"/>
@@ -20103,7 +20954,7 @@
     <row r="374">
       <c r="A374" s="16" t="inlineStr">
         <is>
-          <t>T-68.2</t>
+          <t>T-73.2</t>
         </is>
       </c>
       <c r="B374" s="16" t="inlineStr">
@@ -20114,7 +20965,7 @@
       <c r="C374" s="16" t="inlineStr"/>
       <c r="D374" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar el circuito de solicitud y aprobación</t>
+          <t xml:space="preserve">    Programar el envío y la recepción de mensajes</t>
         </is>
       </c>
       <c r="E374" s="17" t="inlineStr"/>
@@ -20138,7 +20989,7 @@
     <row r="375">
       <c r="A375" s="14" t="inlineStr">
         <is>
-          <t>T-68.3</t>
+          <t>T-73.3</t>
         </is>
       </c>
       <c r="B375" s="14" t="inlineStr">
@@ -20149,7 +21000,7 @@
       <c r="C375" s="14" t="inlineStr"/>
       <c r="D375" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar las pantallas de solicitud y de bandeja del responsable</t>
+          <t xml:space="preserve">    Agregar notificaciones de mensaje nuevo</t>
         </is>
       </c>
       <c r="E375" s="15" t="inlineStr"/>
@@ -20170,45 +21021,41 @@
       </c>
       <c r="I375" s="14" t="inlineStr"/>
     </row>
-    <row r="376">
-      <c r="A376" s="16" t="inlineStr">
-        <is>
-          <t>T-68.4</t>
-        </is>
-      </c>
-      <c r="B376" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C376" s="16" t="inlineStr"/>
-      <c r="D376" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el cálculo del saldo de días</t>
-        </is>
-      </c>
-      <c r="E376" s="17" t="inlineStr"/>
-      <c r="F376" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G376" s="17" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H376" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I376" s="16" t="inlineStr"/>
-    </row>
-    <row r="377" ht="16" customHeight="1">
+    <row r="376" ht="20" customHeight="1">
+      <c r="A376" s="9" t="inlineStr">
+        <is>
+          <t>E12</t>
+        </is>
+      </c>
+      <c r="B376" s="9" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="C376" s="9" t="inlineStr">
+        <is>
+          <t>Configuración de Módulos</t>
+        </is>
+      </c>
+      <c r="D376" s="9" t="inlineStr">
+        <is>
+          <t>Cada empresa activa sólo los módulos que usa</t>
+        </is>
+      </c>
+      <c r="E376" s="10" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F376" s="11" t="n"/>
+      <c r="G376" s="11" t="n"/>
+      <c r="H376" s="11" t="n"/>
+      <c r="I376" s="11" t="n"/>
+    </row>
+    <row r="377" ht="26" customHeight="1">
       <c r="A377" s="12" t="inlineStr">
         <is>
-          <t>HU-69</t>
+          <t>HU-34</t>
         </is>
       </c>
       <c r="B377" s="12" t="inlineStr">
@@ -20218,40 +21065,44 @@
       </c>
       <c r="C377" s="12" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Configuración de Módulos</t>
         </is>
       </c>
       <c r="D377" s="12" t="inlineStr">
         <is>
-          <t>Como empleado quiero subir mi orden médica para justificar una ausencia.</t>
+          <t>Como administrador de la empresa quiero activar sólo los módulos que mi empresa usa para no ver funciones que no necesito.</t>
         </is>
       </c>
       <c r="E377" s="13" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="F377" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G377" s="13" t="inlineStr">
         <is>
-          <t>Sin asignar</t>
+          <t>Sprint 06</t>
         </is>
       </c>
       <c r="H377" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I377" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I377" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="14" t="inlineStr">
         <is>
-          <t>T-69.1</t>
+          <t>T-34.1</t>
         </is>
       </c>
       <c r="B378" s="14" t="inlineStr">
@@ -20262,31 +21113,35 @@
       <c r="C378" s="14" t="inlineStr"/>
       <c r="D378" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el almacenamiento local de archivos adjuntos</t>
+          <t xml:space="preserve">    Crear la tabla de módulos activos por empresa</t>
         </is>
       </c>
       <c r="E378" s="15" t="inlineStr"/>
       <c r="F378" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G378" s="15" t="inlineStr">
         <is>
-          <t>Sin asignar</t>
+          <t>Sprint 06</t>
         </is>
       </c>
       <c r="H378" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I378" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I378" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="16" t="inlineStr">
         <is>
-          <t>T-69.2</t>
+          <t>T-34.2</t>
         </is>
       </c>
       <c r="B379" s="16" t="inlineStr">
@@ -20297,31 +21152,35 @@
       <c r="C379" s="16" t="inlineStr"/>
       <c r="D379" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar la subida con validación de tipo y tamaño</t>
+          <t xml:space="preserve">    Definir el conjunto de módulos disponibles</t>
         </is>
       </c>
       <c r="E379" s="17" t="inlineStr"/>
       <c r="F379" s="17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G379" s="17" t="inlineStr">
         <is>
-          <t>Sin asignar</t>
+          <t>Sprint 06</t>
         </is>
       </c>
       <c r="H379" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I379" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I379" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="14" t="inlineStr">
         <is>
-          <t>T-69.3</t>
+          <t>T-34.3</t>
         </is>
       </c>
       <c r="B380" s="14" t="inlineStr">
@@ -20332,31 +21191,35 @@
       <c r="C380" s="14" t="inlineStr"/>
       <c r="D380" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Restringir la visibilidad del archivo</t>
+          <t xml:space="preserve">    Programar los endpoints de consulta y actualización</t>
         </is>
       </c>
       <c r="E380" s="15" t="inlineStr"/>
       <c r="F380" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G380" s="15" t="inlineStr">
         <is>
-          <t>Sin asignar</t>
+          <t>Sprint 06</t>
         </is>
       </c>
       <c r="H380" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I380" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I380" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="16" t="inlineStr">
         <is>
-          <t>T-69.4</t>
+          <t>T-34.4</t>
         </is>
       </c>
       <c r="B381" s="16" t="inlineStr">
@@ -20367,147 +21230,1546 @@
       <c r="C381" s="16" t="inlineStr"/>
       <c r="D381" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el tratamiento de los datos de salud</t>
+          <t xml:space="preserve">    Diseñar la pantalla de configuración de módulos</t>
         </is>
       </c>
       <c r="E381" s="17" t="inlineStr"/>
       <c r="F381" s="17" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G381" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H381" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I381" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="14" t="inlineStr">
+        <is>
+          <t>T-34.5</t>
+        </is>
+      </c>
+      <c r="B382" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C382" s="14" t="inlineStr"/>
+      <c r="D382" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Mostrar en el menú sólo los módulos activos</t>
+        </is>
+      </c>
+      <c r="E382" s="15" t="inlineStr"/>
+      <c r="F382" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G382" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H382" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I382" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="26" customHeight="1">
+      <c r="A383" s="12" t="inlineStr">
+        <is>
+          <t>HU-35</t>
+        </is>
+      </c>
+      <c r="B383" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C383" s="12" t="inlineStr">
+        <is>
+          <t>Configuración de Módulos</t>
+        </is>
+      </c>
+      <c r="D383" s="12" t="inlineStr">
+        <is>
+          <t>Como sistema quiero rechazar los pedidos a módulos desactivados para que no se pueda entrar por fuera del menú.</t>
+        </is>
+      </c>
+      <c r="E383" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F383" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G383" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H383" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I383" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="14" t="inlineStr">
+        <is>
+          <t>T-35.1</t>
+        </is>
+      </c>
+      <c r="B384" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C384" s="14" t="inlineStr"/>
+      <c r="D384" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar el middleware de módulo activo</t>
+        </is>
+      </c>
+      <c r="E384" s="15" t="inlineStr"/>
+      <c r="F384" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G384" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H384" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I384" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="16" t="inlineStr">
+        <is>
+          <t>T-35.2</t>
+        </is>
+      </c>
+      <c r="B385" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C385" s="16" t="inlineStr"/>
+      <c r="D385" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Aplicarlo a las rutas de movimientos y categorías</t>
+        </is>
+      </c>
+      <c r="E385" s="17" t="inlineStr"/>
+      <c r="F385" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G385" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H385" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I385" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="14" t="inlineStr">
+        <is>
+          <t>T-35.3</t>
+        </is>
+      </c>
+      <c r="B386" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C386" s="14" t="inlineStr"/>
+      <c r="D386" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Mostrar en pantalla un aviso claro cuando el módulo está apagado</t>
+        </is>
+      </c>
+      <c r="E386" s="15" t="inlineStr"/>
+      <c r="F386" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G386" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H386" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I386" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="16" t="inlineStr">
+        <is>
+          <t>T-35.4</t>
+        </is>
+      </c>
+      <c r="B387" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C387" s="16" t="inlineStr"/>
+      <c r="D387" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Distinguir el aviso de módulo apagado del de falta de permiso</t>
+        </is>
+      </c>
+      <c r="E387" s="17" t="inlineStr"/>
+      <c r="F387" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G387" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H387" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I387" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="14" t="inlineStr">
+        <is>
+          <t>T-35.5</t>
+        </is>
+      </c>
+      <c r="B388" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C388" s="14" t="inlineStr"/>
+      <c r="D388" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Probar el acceso con el módulo apagado</t>
+        </is>
+      </c>
+      <c r="E388" s="15" t="inlineStr"/>
+      <c r="F388" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G388" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H388" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I388" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="26" customHeight="1">
+      <c r="A389" s="12" t="inlineStr">
+        <is>
+          <t>HU-36</t>
+        </is>
+      </c>
+      <c r="B389" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C389" s="12" t="inlineStr">
+        <is>
+          <t>Configuración de Módulos</t>
+        </is>
+      </c>
+      <c r="D389" s="12" t="inlineStr">
+        <is>
+          <t>Como empresa nueva quiero empezar con una configuración razonable para no tener que definir todo antes de usar el sistema.</t>
+        </is>
+      </c>
+      <c r="E389" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F389" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G389" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H389" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I389" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="14" t="inlineStr">
+        <is>
+          <t>T-36.1</t>
+        </is>
+      </c>
+      <c r="B390" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C390" s="14" t="inlineStr"/>
+      <c r="D390" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Definir el conjunto de módulos y categorías iniciales</t>
+        </is>
+      </c>
+      <c r="E390" s="15" t="inlineStr"/>
+      <c r="F390" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G390" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H390" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I390" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="16" t="inlineStr">
+        <is>
+          <t>T-36.2</t>
+        </is>
+      </c>
+      <c r="B391" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C391" s="16" t="inlineStr"/>
+      <c r="D391" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar la carga automática al aprobar la empresa</t>
+        </is>
+      </c>
+      <c r="E391" s="17" t="inlineStr"/>
+      <c r="F391" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G391" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H391" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I391" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="14" t="inlineStr">
+        <is>
+          <t>T-36.3</t>
+        </is>
+      </c>
+      <c r="B392" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C392" s="14" t="inlineStr"/>
+      <c r="D392" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Dejar la configuración escrita en la base, no deducida del catálogo</t>
+        </is>
+      </c>
+      <c r="E392" s="15" t="inlineStr"/>
+      <c r="F392" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G392" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H392" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I392" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="16" t="inlineStr">
+        <is>
+          <t>T-36.4</t>
+        </is>
+      </c>
+      <c r="B393" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C393" s="16" t="inlineStr"/>
+      <c r="D393" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Evitar que una segunda aprobación duplique o pise lo ya configurado</t>
+        </is>
+      </c>
+      <c r="E393" s="17" t="inlineStr"/>
+      <c r="F393" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G393" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H393" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I393" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="14" t="inlineStr">
+        <is>
+          <t>T-36.5</t>
+        </is>
+      </c>
+      <c r="B394" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C394" s="14" t="inlineStr"/>
+      <c r="D394" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Probar el alta de una empresa nueva de punta a punta</t>
+        </is>
+      </c>
+      <c r="E394" s="15" t="inlineStr"/>
+      <c r="F394" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G394" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H394" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I394" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="20" customHeight="1">
+      <c r="A395" s="9" t="inlineStr">
+        <is>
+          <t>E13</t>
+        </is>
+      </c>
+      <c r="B395" s="9" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="C395" s="9" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D395" s="9" t="inlineStr">
+        <is>
+          <t>Catálogo de servicios que generan ingreso o egreso</t>
+        </is>
+      </c>
+      <c r="E395" s="10" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F395" s="11" t="n"/>
+      <c r="G395" s="11" t="n"/>
+      <c r="H395" s="11" t="n"/>
+      <c r="I395" s="11" t="n"/>
+    </row>
+    <row r="396" ht="26" customHeight="1">
+      <c r="A396" s="12" t="inlineStr">
+        <is>
+          <t>HU-47</t>
+        </is>
+      </c>
+      <c r="B396" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C396" s="12" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D396" s="12" t="inlineStr">
+        <is>
+          <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
+        </is>
+      </c>
+      <c r="E396" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F396" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G396" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H396" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I396" s="12" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="14" t="inlineStr">
+        <is>
+          <t>T-47.1</t>
+        </is>
+      </c>
+      <c r="B397" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C397" s="14" t="inlineStr"/>
+      <c r="D397" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Reutilizar el modelo de productos agregando la distinción de servicio</t>
+        </is>
+      </c>
+      <c r="E397" s="15" t="inlineStr"/>
+      <c r="F397" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G397" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H397" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I397" s="14" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="16" t="inlineStr">
+        <is>
+          <t>T-47.2</t>
+        </is>
+      </c>
+      <c r="B398" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C398" s="16" t="inlineStr"/>
+      <c r="D398" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar el alta, la edición y la baja lógica</t>
+        </is>
+      </c>
+      <c r="E398" s="17" t="inlineStr"/>
+      <c r="F398" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G398" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H398" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I398" s="16" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="14" t="inlineStr">
+        <is>
+          <t>T-47.3</t>
+        </is>
+      </c>
+      <c r="B399" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C399" s="14" t="inlineStr"/>
+      <c r="D399" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar la pantalla de servicios</t>
+        </is>
+      </c>
+      <c r="E399" s="15" t="inlineStr"/>
+      <c r="F399" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G399" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H399" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I399" s="14" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="16" t="inlineStr">
+        <is>
+          <t>T-47.4</t>
+        </is>
+      </c>
+      <c r="B400" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C400" s="16" t="inlineStr"/>
+      <c r="D400" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Verificar que los servicios no lleven existencias</t>
+        </is>
+      </c>
+      <c r="E400" s="17" t="inlineStr"/>
+      <c r="F400" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G400" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H400" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I400" s="16" t="inlineStr"/>
+    </row>
+    <row r="401" ht="26" customHeight="1">
+      <c r="A401" s="12" t="inlineStr">
+        <is>
+          <t>HU-48</t>
+        </is>
+      </c>
+      <c r="B401" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C401" s="12" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D401" s="12" t="inlineStr">
+        <is>
+          <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
+        </is>
+      </c>
+      <c r="E401" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F401" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G401" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H401" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I401" s="12" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="14" t="inlineStr">
+        <is>
+          <t>T-48.1</t>
+        </is>
+      </c>
+      <c r="B402" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C402" s="14" t="inlineStr"/>
+      <c r="D402" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Vincular el movimiento económico con el servicio</t>
+        </is>
+      </c>
+      <c r="E402" s="15" t="inlineStr"/>
+      <c r="F402" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G402" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H402" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I402" s="14" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="16" t="inlineStr">
+        <is>
+          <t>T-48.2</t>
+        </is>
+      </c>
+      <c r="B403" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C403" s="16" t="inlineStr"/>
+      <c r="D403" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agregar el servicio al formulario de movimiento</t>
+        </is>
+      </c>
+      <c r="E403" s="17" t="inlineStr"/>
+      <c r="F403" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G403" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H403" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I403" s="16" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="14" t="inlineStr">
+        <is>
+          <t>T-48.3</t>
+        </is>
+      </c>
+      <c r="B404" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C404" s="14" t="inlineStr"/>
+      <c r="D404" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agregar el filtro por servicio en el listado</t>
+        </is>
+      </c>
+      <c r="E404" s="15" t="inlineStr"/>
+      <c r="F404" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G404" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H404" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I404" s="14" t="inlineStr"/>
+    </row>
+    <row r="405" ht="16" customHeight="1">
+      <c r="A405" s="12" t="inlineStr">
+        <is>
+          <t>HU-49</t>
+        </is>
+      </c>
+      <c r="B405" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C405" s="12" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D405" s="12" t="inlineStr">
+        <is>
+          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
+        </is>
+      </c>
+      <c r="E405" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F405" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G405" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H405" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I405" s="12" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="14" t="inlineStr">
+        <is>
+          <t>T-49.1</t>
+        </is>
+      </c>
+      <c r="B406" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C406" s="14" t="inlineStr"/>
+      <c r="D406" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar la consulta agrupada por servicio</t>
+        </is>
+      </c>
+      <c r="E406" s="15" t="inlineStr"/>
+      <c r="F406" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G406" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H406" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I406" s="14" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="16" t="inlineStr">
+        <is>
+          <t>T-49.2</t>
+        </is>
+      </c>
+      <c r="B407" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C407" s="16" t="inlineStr"/>
+      <c r="D407" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar la visualización del resumen</t>
+        </is>
+      </c>
+      <c r="E407" s="17" t="inlineStr"/>
+      <c r="F407" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G407" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H407" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I407" s="16" t="inlineStr"/>
+    </row>
+    <row r="408" ht="20" customHeight="1">
+      <c r="A408" s="9" t="inlineStr">
+        <is>
+          <t>E14</t>
+        </is>
+      </c>
+      <c r="B408" s="9" t="inlineStr">
+        <is>
+          <t>Épica</t>
+        </is>
+      </c>
+      <c r="C408" s="9" t="inlineStr">
+        <is>
+          <t>Recursos Humanos</t>
+        </is>
+      </c>
+      <c r="D408" s="9" t="inlineStr">
+        <is>
+          <t>Vacaciones, licencias y documentación del personal (backlog futuro)</t>
+        </is>
+      </c>
+      <c r="E408" s="10" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="F408" s="11" t="n"/>
+      <c r="G408" s="11" t="n"/>
+      <c r="H408" s="11" t="n"/>
+      <c r="I408" s="11" t="n"/>
+    </row>
+    <row r="409" ht="16" customHeight="1">
+      <c r="A409" s="12" t="inlineStr">
+        <is>
+          <t>HU-68</t>
+        </is>
+      </c>
+      <c r="B409" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C409" s="12" t="inlineStr">
+        <is>
+          <t>Recursos Humanos</t>
+        </is>
+      </c>
+      <c r="D409" s="12" t="inlineStr">
+        <is>
+          <t>Como empleado quiero solicitar días de vacaciones para gestionarlos sin papeles.</t>
+        </is>
+      </c>
+      <c r="E409" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F409" s="13" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G381" s="17" t="inlineStr">
+      <c r="G409" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H381" s="16" t="inlineStr">
+      <c r="H409" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I381" s="16" t="inlineStr"/>
-    </row>
-    <row r="382" ht="16" customHeight="1">
-      <c r="A382" s="12" t="inlineStr">
+      <c r="I409" s="12" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="14" t="inlineStr">
+        <is>
+          <t>T-68.1</t>
+        </is>
+      </c>
+      <c r="B410" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C410" s="14" t="inlineStr"/>
+      <c r="D410" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar el modelo de licencias y saldo de días</t>
+        </is>
+      </c>
+      <c r="E410" s="15" t="inlineStr"/>
+      <c r="F410" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G410" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H410" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I410" s="14" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="16" t="inlineStr">
+        <is>
+          <t>T-68.2</t>
+        </is>
+      </c>
+      <c r="B411" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C411" s="16" t="inlineStr"/>
+      <c r="D411" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar el circuito de solicitud y aprobación</t>
+        </is>
+      </c>
+      <c r="E411" s="17" t="inlineStr"/>
+      <c r="F411" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G411" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H411" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I411" s="16" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="14" t="inlineStr">
+        <is>
+          <t>T-68.3</t>
+        </is>
+      </c>
+      <c r="B412" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C412" s="14" t="inlineStr"/>
+      <c r="D412" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar las pantallas de solicitud y de bandeja del responsable</t>
+        </is>
+      </c>
+      <c r="E412" s="15" t="inlineStr"/>
+      <c r="F412" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G412" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H412" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I412" s="14" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="16" t="inlineStr">
+        <is>
+          <t>T-68.4</t>
+        </is>
+      </c>
+      <c r="B413" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C413" s="16" t="inlineStr"/>
+      <c r="D413" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar el cálculo del saldo de días</t>
+        </is>
+      </c>
+      <c r="E413" s="17" t="inlineStr"/>
+      <c r="F413" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G413" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H413" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I413" s="16" t="inlineStr"/>
+    </row>
+    <row r="414" ht="16" customHeight="1">
+      <c r="A414" s="12" t="inlineStr">
+        <is>
+          <t>HU-69</t>
+        </is>
+      </c>
+      <c r="B414" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C414" s="12" t="inlineStr">
+        <is>
+          <t>Recursos Humanos</t>
+        </is>
+      </c>
+      <c r="D414" s="12" t="inlineStr">
+        <is>
+          <t>Como empleado quiero subir mi orden médica para justificar una ausencia.</t>
+        </is>
+      </c>
+      <c r="E414" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F414" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G414" s="13" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H414" s="12" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I414" s="12" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="14" t="inlineStr">
+        <is>
+          <t>T-69.1</t>
+        </is>
+      </c>
+      <c r="B415" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C415" s="14" t="inlineStr"/>
+      <c r="D415" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Definir el almacenamiento local de archivos adjuntos</t>
+        </is>
+      </c>
+      <c r="E415" s="15" t="inlineStr"/>
+      <c r="F415" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G415" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H415" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I415" s="14" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="16" t="inlineStr">
+        <is>
+          <t>T-69.2</t>
+        </is>
+      </c>
+      <c r="B416" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C416" s="16" t="inlineStr"/>
+      <c r="D416" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar la subida con validación de tipo y tamaño</t>
+        </is>
+      </c>
+      <c r="E416" s="17" t="inlineStr"/>
+      <c r="F416" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G416" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H416" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I416" s="16" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="14" t="inlineStr">
+        <is>
+          <t>T-69.3</t>
+        </is>
+      </c>
+      <c r="B417" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C417" s="14" t="inlineStr"/>
+      <c r="D417" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Restringir la visibilidad del archivo</t>
+        </is>
+      </c>
+      <c r="E417" s="15" t="inlineStr"/>
+      <c r="F417" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G417" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H417" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I417" s="14" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="16" t="inlineStr">
+        <is>
+          <t>T-69.4</t>
+        </is>
+      </c>
+      <c r="B418" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C418" s="16" t="inlineStr"/>
+      <c r="D418" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Definir el tratamiento de los datos de salud</t>
+        </is>
+      </c>
+      <c r="E418" s="17" t="inlineStr"/>
+      <c r="F418" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G418" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H418" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I418" s="16" t="inlineStr"/>
+    </row>
+    <row r="419" ht="16" customHeight="1">
+      <c r="A419" s="12" t="inlineStr">
         <is>
           <t>HU-70</t>
         </is>
       </c>
-      <c r="B382" s="12" t="inlineStr">
+      <c r="B419" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C382" s="12" t="inlineStr">
+      <c r="C419" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D382" s="12" t="inlineStr">
+      <c r="D419" s="12" t="inlineStr">
         <is>
           <t>Como área de personal quiero ver el calendario de ausencias para organizar la cobertura.</t>
         </is>
       </c>
-      <c r="E382" s="13" t="inlineStr">
+      <c r="E419" s="13" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F382" s="13" t="inlineStr">
+      <c r="F419" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G382" s="13" t="inlineStr">
+      <c r="G419" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H382" s="12" t="inlineStr">
+      <c r="H419" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I382" s="12" t="inlineStr"/>
-    </row>
-    <row r="383">
-      <c r="A383" s="14" t="inlineStr">
+      <c r="I419" s="12" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="14" t="inlineStr">
         <is>
           <t>T-70.1</t>
         </is>
       </c>
-      <c r="B383" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C383" s="14" t="inlineStr"/>
-      <c r="D383" s="14" t="inlineStr">
+      <c r="B420" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C420" s="14" t="inlineStr"/>
+      <c r="D420" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar el calendario de ausencias</t>
         </is>
       </c>
-      <c r="E383" s="15" t="inlineStr"/>
-      <c r="F383" s="15" t="inlineStr">
+      <c r="E420" s="15" t="inlineStr"/>
+      <c r="F420" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G383" s="15" t="inlineStr">
+      <c r="G420" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H383" s="14" t="inlineStr">
+      <c r="H420" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I383" s="14" t="inlineStr"/>
-    </row>
-    <row r="384">
-      <c r="A384" s="16" t="inlineStr">
+      <c r="I420" s="14" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="16" t="inlineStr">
         <is>
           <t>T-70.2</t>
         </is>
       </c>
-      <c r="B384" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C384" s="16" t="inlineStr"/>
-      <c r="D384" s="16" t="inlineStr">
+      <c r="B421" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C421" s="16" t="inlineStr"/>
+      <c r="D421" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar la consulta por período</t>
         </is>
       </c>
-      <c r="E384" s="17" t="inlineStr"/>
-      <c r="F384" s="17" t="inlineStr">
+      <c r="E421" s="17" t="inlineStr"/>
+      <c r="F421" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G384" s="17" t="inlineStr">
+      <c r="G421" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H384" s="16" t="inlineStr">
+      <c r="H421" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I384" s="16" t="inlineStr"/>
+      <c r="I421" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I384"/>
+  <autoFilter ref="A4:I421"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H384">
+  <conditionalFormatting sqref="H5:H421">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -20522,13 +22784,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H5:H384" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H421" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E384" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E421" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I384" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I421" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20921,7 +23183,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Sprint 09</t>
@@ -20934,18 +23196,18 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Abrir el módulo de Servicios, que comparte estructura con Productos pero sin control de existencias.</t>
+          <t>Emparejar la base ANTES de duplicarla, y recién entonces abrir Servicios. El orden importa: Servicios copia las pantallas de Productos, así que cada nombre, cada tabla que no entra en el celular y cada pantalla de configuración mal ubicada que quede sin arreglar se copia a un lugar más. Primero el vocabulario, el celular y la configuración; después el módulo nuevo, que es un producto sin stock.</t>
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E13" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 09'!A6:A21,2)="T-")*1)</f>
+        <f>SUMPRODUCT((LEFT('Sprint 09'!A6:A50,2)="T-")*1)</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 09'!A6:A21,2)="T-")*('Sprint 09'!E6:E21="Hecho"))</f>
+        <f>SUMPRODUCT((LEFT('Sprint 09'!A6:A50,2)="T-")*('Sprint 09'!E6:E50="Hecho"))</f>
         <v/>
       </c>
       <c r="G13" s="18">
@@ -21069,7 +23331,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="52" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Sprint 13</t>
@@ -21082,18 +23344,18 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Cierre del ciclo: definir la identidad del producto, ajustar la interfaz, probar de punta a punta y documentar para la continuidad del proyecto.</t>
+          <t>Cierre del ciclo: definir la identidad del producto, terminar de ajustar la interfaz, probar de punta a punta y documentar para la continuidad del proyecto. Queda más liviano que en la planificación anterior porque el vocabulario, el celular y la configuración se adelantaron al Sprint 09, donde hacían falta.</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 13'!A6:A28,2)="T-")*1)</f>
+        <f>SUMPRODUCT((LEFT('Sprint 13'!A6:A36,2)="T-")*1)</f>
         <v/>
       </c>
       <c r="F17" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 13'!A6:A28,2)="T-")*('Sprint 13'!E6:E28="Hecho"))</f>
+        <f>SUMPRODUCT((LEFT('Sprint 13'!A6:A36,2)="T-")*('Sprint 13'!E6:E36="Hecho"))</f>
         <v/>
       </c>
       <c r="G17" s="18">

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -28,7 +28,7 @@
     <sheet name="Cambios vs. original" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$421</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$423</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2165,7 +2165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2600,10 +2600,14 @@
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr"/>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -2619,10 +2623,14 @@
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -2634,14 +2642,18 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Reemplazar 'naturaleza' por una pregunta en castellano llano</t>
+          <t xml:space="preserve">     Reemplazar 'naturaleza' por dos botones: entró o salió</t>
         </is>
       </c>
       <c r="C23" s="16" t="inlineStr"/>
-      <c r="D23" s="16" t="inlineStr"/>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -2653,14 +2665,18 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Ponerle apellido a las dos pantallas de categorías (dinero y productos)</t>
+          <t xml:space="preserve">     Ponerle apellido a las dos pantallas: categorías de movimientos y de productos</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -2676,10 +2692,14 @@
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr"/>
-      <c r="D25" s="16" t="inlineStr"/>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E25" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -2695,328 +2715,392 @@
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E26" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>T-84.6</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Aplicar el mismo vocabulario a los mensajes que devuelve el servidor</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr"/>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>HU-85</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Como operador quiero ver en el celular la columna que me importa para no tener que arrastrar la tabla de costado.</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D27" s="23" t="inlineStr"/>
-      <c r="E27" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>T-85.1</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Convertir los tres listados en tarjetas por debajo de 768 px</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr"/>
-      <c r="D28" s="14" t="inlineStr"/>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Escribir el patrón de tarjetas en una hoja compartida, para que lo use toda la app</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr"/>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>T-85.2</t>
         </is>
       </c>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Compactar el encabezado en celular</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr"/>
-      <c r="D29" s="16" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Convertir los listados en tarjetas por debajo de 768 px</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr"/>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>T-85.3</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Compactar el encabezado en celular con un botón de menú</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr"/>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>T-85.4</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Validar en 375 px que no quede scroll horizontal</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr"/>
-      <c r="D30" s="14" t="inlineStr"/>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="C32" s="16" t="inlineStr"/>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>HU-86</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>Como administrador quiero encontrar la configuración en un solo lugar para no buscarla abajo de mi nombre.</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr"/>
-      <c r="E31" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>T-86.1</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Agrupar las cuatro pantallas de configuración en el menú principal</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr"/>
-      <c r="D32" s="14" t="inlineStr"/>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>T-86.2</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Dejar en el menú del usuario sólo lo personal y cerrar sesión</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr"/>
-      <c r="D33" s="16" t="inlineStr"/>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>T-86.3</t>
+          <t>T-86.1</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Mover el acceso a motivos desde Productos a Stock</t>
+          <t xml:space="preserve">     Agrupar las cuatro pantallas de configuración en el menú principal</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr"/>
-      <c r="D34" s="14" t="inlineStr"/>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>HU-47</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr"/>
-      <c r="E35" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>T-86.2</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Dejar en el menú del usuario sólo lo personal y cerrar sesión</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr"/>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>T-47.1</t>
+          <t>T-86.3</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Reutilizar el modelo de productos agregando la distinción de servicio</t>
+          <t xml:space="preserve">     Mover el acceso a motivos desde Productos a Stock</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr"/>
-      <c r="D36" s="14" t="inlineStr"/>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>T-47.2</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Programar el alta, la edición y la baja lógica</t>
-        </is>
-      </c>
-      <c r="C37" s="16" t="inlineStr"/>
-      <c r="D37" s="16" t="inlineStr"/>
-      <c r="E37" s="17" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>HU-47</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>T-47.3</t>
+          <t>T-47.1</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Diseñar la pantalla de servicios</t>
+          <t xml:space="preserve">     Reutilizar el modelo de productos agregando la distinción de servicio</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr"/>
-      <c r="D38" s="14" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
+          <t>T-47.2</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Programar el alta, la edición y la baja lógica</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr"/>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>T-47.3</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Diseñar la pantalla de servicios</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr"/>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
           <t>T-47.4</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Verificar que los servicios no lleven existencias</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr"/>
-      <c r="D39" s="16" t="inlineStr"/>
-      <c r="E39" s="17" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr"/>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>HU-48</t>
         </is>
       </c>
-      <c r="B40" s="23" t="inlineStr">
+      <c r="B42" s="23" t="inlineStr">
         <is>
           <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
         </is>
       </c>
-      <c r="C40" s="23" t="inlineStr">
+      <c r="C42" s="23" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D40" s="23" t="inlineStr"/>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>T-48.1</t>
-        </is>
-      </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Vincular el movimiento económico con el servicio</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr"/>
-      <c r="D41" s="14" t="inlineStr"/>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>T-48.2</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Agregar el servicio al formulario de movimiento</t>
-        </is>
-      </c>
-      <c r="C42" s="16" t="inlineStr"/>
-      <c r="D42" s="16" t="inlineStr"/>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="D42" s="23" t="inlineStr"/>
+      <c r="E42" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -3025,12 +3109,12 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>T-48.3</t>
+          <t>T-48.1</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Agregar el filtro por servicio en el listado</t>
+          <t xml:space="preserve">     Vincular el movimiento económico con el servicio</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr"/>
@@ -3041,24 +3125,20 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>HU-49</t>
-        </is>
-      </c>
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
-        </is>
-      </c>
-      <c r="C44" s="23" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D44" s="23" t="inlineStr"/>
-      <c r="E44" s="24" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>T-48.2</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Agregar el servicio al formulario de movimiento</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr"/>
+      <c r="D44" s="16" t="inlineStr"/>
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -3067,12 +3147,12 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>T-49.1</t>
+          <t>T-48.3</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Programar la consulta agrupada por servicio</t>
+          <t xml:space="preserve">     Agregar el filtro por servicio en el listado</t>
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr"/>
@@ -3083,81 +3163,85 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>HU-49</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr"/>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>T-49.1</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Programar la consulta agrupada por servicio</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr"/>
+      <c r="D47" s="14" t="inlineStr"/>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>T-49.2</t>
         </is>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Diseñar la visualización del resumen</t>
         </is>
       </c>
-      <c r="C46" s="16" t="inlineStr"/>
-      <c r="D46" s="16" t="inlineStr"/>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr"/>
+      <c r="D48" s="16" t="inlineStr"/>
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>HU-50</t>
         </is>
       </c>
-      <c r="B47" s="23" t="inlineStr">
+      <c r="B49" s="23" t="inlineStr">
         <is>
           <t>Como equipo quiero probar los módulos de productos y servicios para entregarlos sin errores.</t>
         </is>
       </c>
-      <c r="C47" s="23" t="inlineStr">
+      <c r="C49" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D47" s="23" t="inlineStr"/>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>T-50.1</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Escribir y ejecutar los casos de prueba de stock</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="inlineStr"/>
-      <c r="D48" s="14" t="inlineStr"/>
-      <c r="E48" s="15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>T-50.2</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Escribir y ejecutar los casos de prueba de servicios</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="inlineStr"/>
-      <c r="D49" s="16" t="inlineStr"/>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="D49" s="23" t="inlineStr"/>
+      <c r="E49" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -3166,12 +3250,12 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>T-50.3</t>
+          <t>T-50.1</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Validar ambas pantallas en celular</t>
+          <t xml:space="preserve">     Escribir y ejecutar los casos de prueba de stock</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr"/>
@@ -3182,15 +3266,53 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>T-50.2</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Escribir y ejecutar los casos de prueba de servicios</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr"/>
+      <c r="D51" s="16" t="inlineStr"/>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
-      <c r="C52" s="19" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>T-50.3</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Validar ambas pantallas en celular</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr"/>
+      <c r="D52" s="14" t="inlineStr"/>
+      <c r="E52" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>AVANCE DEL SPRINT (tareas terminadas)</t>
         </is>
       </c>
-      <c r="D52" s="20" t="n"/>
-      <c r="E52" s="20">
-        <f>TEXT(SUMPRODUCT((LEFT(A6:A50,2)="T-")*(E6:E50="Hecho"))/SUMPRODUCT((LEFT(A6:A50,2)="T-")*1),"0%")</f>
+      <c r="D54" s="20" t="n"/>
+      <c r="E54" s="20">
+        <f>TEXT(SUMPRODUCT((LEFT(A6:A52,2)="T-")*(E6:E52="Hecho"))/SUMPRODUCT((LEFT(A6:A52,2)="T-")*1),"0%")</f>
         <v/>
       </c>
     </row>
@@ -3200,7 +3322,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E50">
+  <conditionalFormatting sqref="E6:E52">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -3215,10 +3337,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E6:E50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:D50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5871,7 +5993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6042,83 +6164,83 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="39" customHeight="1">
+    <row r="11" ht="65" customHeight="1">
       <c r="A11" s="15" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Productos y Servicios NO son categorías de movimientos</t>
+          <t>Servicios comparte las tablas de Productos, no las duplica</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>El dinero ya tiene su propia clasificación (categoría y tipo). Productos y Servicios son módulos operativos que generan movimientos. Si se mezclaran, la misma venta quedaría clasificada dos veces y los totales no cerrarían.</t>
+          <t>Un servicio es un producto sin stock: misma estructura de categoría y subcategoría, y mañana el mismo vínculo con los movimientos. Se guardan en las mismas tablas, separados por una columna, con dos pantallas arriba. Duplicar el modelo habría significado corregir cada error dos veces y decidir después a cuál de los dos catálogos apunta un movimiento de dinero.</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>E3 y E4 frente a E6 y E13</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
+          <t>HU-47 · Sprint 09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39" customHeight="1">
       <c r="A12" s="17" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>Los motivos de movimiento de stock llevan su impacto configurado</t>
+          <t>Productos y Servicios NO son categorías de movimientos</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Cada motivo dice si suma o resta existencias y si genera ingreso, egreso o nada, así el administrador arma los suyos sin tocar código. Pérdida y robo no generan movimiento de dinero, pero se ven valorizados en un reporte aparte para no ensuciar el balance.</t>
+          <t>El dinero ya tiene su propia clasificación (categoría y tipo). Productos y Servicios son módulos operativos que generan movimientos. Si se mezclaran, la misma venta quedaría clasificada dos veces y los totales no cerrarían.</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>HU-41 y HU-53</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
+          <t>E3 y E4 frente a E6 y E13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
       <c r="A13" s="15" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Recursos Humanos quedó en el backlog futuro</t>
+          <t>Los motivos de movimiento de stock llevan su impacto configurado</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Es el módulo más grande de los propuestos (circuito de aprobación, saldo de días, archivos adjuntos con datos de salud) y el único que no toca el flujo de dinero, que es el eje del producto. Con siete sprints por delante no entra sin poner en riesgo el resto. Se deja diseñado y documentado para el ciclo siguiente.</t>
+          <t>Cada motivo dice si suma o resta existencias y si genera ingreso, egreso o nada, así el administrador arma los suyos sin tocar código. Pérdida y robo no generan movimiento de dinero, pero se ven valorizados en un reporte aparte para no ensuciar el balance.</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Nueva E14 · HU-68 a HU-70, sin sprint</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="39" customHeight="1">
+          <t>HU-41 y HU-53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="65" customHeight="1">
       <c r="A14" s="17" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>La articulación se mantuvo pese al cambio de público</t>
+          <t>Recursos Humanos quedó en el backlog futuro</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Es lo único del producto que no ofrece un sistema de gestión convencional. Se conserva acotada a PyMEs, donde la coincidencia entre necesidades y ofertas tiene sentido real.</t>
+          <t>Es el módulo más grande de los propuestos (circuito de aprobación, saldo de días, archivos adjuntos con datos de salud) y el único que no toca el flujo de dinero, que es el eje del producto. Con siete sprints por delante no entra sin poner en riesgo el resto. Se deja diseñado y documentado para el ciclo siguiente.</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>E8 · Sprints 11 y 12</t>
+          <t>Nueva E14 · HU-68 a HU-70, sin sprint</t>
         </is>
       </c>
     </row>
@@ -6128,57 +6250,57 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Los sprints 04 a 06 originales se consolidaron en dos</t>
+          <t>La articulación se mantuvo pese al cambio de público</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>El equipo entregó categorías, movimientos, consulta, anulación, resumen y dashboard real en menos tiempo del planificado. El backlog refleja lo entregado, no la planificación anterior.</t>
+          <t>Es lo único del producto que no ofrece un sistema de gestión convencional. Se conserva acotada a PyMEs, donde la coincidencia entre necesidades y ofertas tiene sentido real.</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Sprint 04 (categorías) y Sprint 05 (movimientos y resumen)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+          <t>E8 · Sprints 11 y 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="39" customHeight="1">
       <c r="A16" s="17" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>Las subcategorías de movimientos pasaron a llamarse tipos</t>
+          <t>Los sprints 04 a 06 originales se consolidaron en dos</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Es el nombre que quedó implementado: naturaleza, categoría y tipo. El backlog usa el mismo vocabulario que el sistema para que no haya dos idiomas.</t>
+          <t>El equipo entregó categorías, movimientos, consulta, anulación, resumen y dashboard real en menos tiempo del planificado. El backlog refleja lo entregado, no la planificación anterior.</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>E3 · HU-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="39" customHeight="1">
+          <t>Sprint 04 (categorías) y Sprint 05 (movimientos y resumen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="15" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Se agregó un sprint de corrección de deuda técnica</t>
+          <t>Las subcategorías de movimientos pasaron a llamarse tipos</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>La revisión del módulo de movimientos encontró seis errores, entre ellos textos del usuario que se ejecutaban como código en la pantalla y montos que se guardaban en cero. No estaban representados en ninguna historia.</t>
+          <t>Es el nombre que quedó implementado: naturaleza, categoría y tipo. El backlog usa el mismo vocabulario que el sistema para que no haya dos idiomas.</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>HU-31 · Sprint 06</t>
+          <t>E3 · HU-19</t>
         </is>
       </c>
     </row>
@@ -6188,117 +6310,117 @@
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>El Sprint 1 original se dividió en dos sprints</t>
+          <t>Se agregó un sprint de corrección de deuda técnica</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Concentraba ocho historias y dos módulos distintos (alta de empresas y acceso al sistema). Partido en dos queda un sprint por tema y el seguimiento semanal es realista.</t>
+          <t>La revisión del módulo de movimientos encontró seis errores, entre ellos textos del usuario que se ejecutaban como código en la pantalla y montos que se guardaban en cero. No estaban representados en ninguna historia.</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Sprint 01 (base y registro) + Sprint 02 (acceso y usuarios)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+          <t>HU-31 · Sprint 06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39" customHeight="1">
       <c r="A19" s="15" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Se quitaron las columnas de horas estimadas y reales</t>
+          <t>El Sprint 1 original se dividió en dos sprints</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Las estimaciones eran una suposición sin velocidad real medida del equipo, y una columna que nadie completa con datos confiables ensucia el seguimiento.</t>
+          <t>Concentraba ocho historias y dos módulos distintos (alta de empresas y acceso al sistema). Partido en dos queda un sprint por tema y el seguimiento semanal es realista.</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Product Backlog, hojas de sprint y Seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="39" customHeight="1">
+          <t>Sprint 01 (base y registro) + Sprint 02 (acceso y usuarios)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="17" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>El recupero de contraseña por correo se reemplazó por reseteo por el administrador</t>
+          <t>Se quitaron las columnas de horas estimadas y reales</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>El proyecto corre sólo en local: no hay servidor de correo. El administrador de la plataforma resetea a los administradores de empresa, y cada administrador a los usuarios de su empresa.</t>
+          <t>Las estimaciones eran una suposición sin velocidad real medida del equipo, y una columna que nadie completa con datos confiables ensucia el seguimiento.</t>
         </is>
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>HU-10 y HU-11 · el recupero por correo pasó a HU-71, sin sprint</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
+          <t>Product Backlog, hojas de sprint y Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="39" customHeight="1">
       <c r="A21" s="15" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Se unificaron las épicas Operaciones financieras y Registro de movimientos diarios</t>
+          <t>El recupero de contraseña por correo se reemplazó por reseteo por el administrador</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>En el backlog original describían el mismo módulo con distinto nombre y sus historias se superponían.</t>
+          <t>El proyecto corre sólo en local: no hay servidor de correo. El administrador de la plataforma resetea a los administradores de empresa, y cada administrador a los usuarios de su empresa.</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>E3 y E5 originales → E4 Movimientos Económico-Financieros</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="39" customHeight="1">
+          <t>HU-10 y HU-11 · el recupero por correo pasó a HU-71, sin sprint</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="17" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>Se agregó la épica de Calidad, UX y Documentación</t>
+          <t>Se unificaron las épicas Operaciones financieras y Registro de movimientos diarios</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>La Definición de Terminado exige validación en celular y en dos navegadores, y el proyecto se continúa el año próximo. Ese trabajo no estaba representado en ninguna historia.</t>
+          <t>En el backlog original describían el mismo módulo con distinto nombre y sus historias se superponían.</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>E10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t>E3 y E5 originales → E4 Movimientos Económico-Financieros</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="39" customHeight="1">
       <c r="A23" s="15" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>El chat pasó al backlog futuro</t>
+          <t>Se agregó la épica de Calidad, UX y Documentación</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>No forma parte del MVP y compite con funcionalidades críticas.</t>
+          <t>La Definición de Terminado exige validación en celular y en dos navegadores, y el proyecto se continúa el año próximo. Ese trabajo no estaba representado en ninguna historia.</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>E11, sin sprint asignado</t>
+          <t>E10</t>
         </is>
       </c>
     </row>
@@ -6308,92 +6430,92 @@
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>Todas las historias se escriben en formato Como… quiero… para…</t>
+          <t>El chat pasó al backlog futuro</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>El backlog original mezclaba historias de usuario con nombres de pantalla y tareas técnicas.</t>
+          <t>No forma parte del MVP y compite con funcionalidades críticas.</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Todas las HU</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="52" customHeight="1">
+          <t>E11, sin sprint asignado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="A25" s="15" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>La subcategoría del producto quedó opcional</t>
+          <t>Todas las historias se escriben en formato Como… quiero… para…</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Exigirla obligaba a inventar una subcategoría de relleno ("General") en cada categoría que la empresa no quiere subdividir, sólo para poder cargar el primer producto. Es fricción justo para el tipo de usuario del proyecto. La categoría sí es obligatoria: es lo que ordena el catálogo.</t>
+          <t>El backlog original mezclaba historias de usuario con nombres de pantalla y tareas técnicas.</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>HU-38 · Sprint 07</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
+          <t>Todas las HU</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
       <c r="A26" s="17" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>La existencia no se guarda en una columna: se calcula</t>
+          <t>La subcategoría del producto quedó opcional</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>Un campo "stock actual" hay que mantenerlo sincronizado a mano en cada alta, cada anulación y cada corrección, y el día que una se olvida el número queda mal para siempre sin que nadie se entere. Calculándolo a partir de los movimientos, la anulación corrige el stock sola y el historial siempre explica el número que se ve en pantalla.</t>
+          <t>Exigirla obligaba a inventar una subcategoría de relleno ("General") en cada categoría que la empresa no quiere subdividir, sólo para poder cargar el primer producto. Es fricción justo para el tipo de usuario del proyecto. La categoría sí es obligatoria: es lo que ordena el catálogo.</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>HU-42, HU-46 · Sprint 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="52" customHeight="1">
+          <t>HU-38 · Sprint 07</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="65" customHeight="1">
       <c r="A27" s="15" t="n">
         <v>23</v>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>El efecto de un motivo de stock no se puede cambiar una vez usado</t>
+          <t>La existencia no se guarda en una columna: se calcula</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>El stock se calcula recorriendo los movimientos y subiendo al motivo para saber si suman o restan. Dar vuelta "Venta" de salida a entrada reinterpretaría todo el historial y las existencias cambiarían solas. El nombre sí se puede corregir siempre.</t>
+          <t>Un campo "stock actual" hay que mantenerlo sincronizado a mano en cada alta, cada anulación y cada corrección, y el día que una se olvida el número queda mal para siempre sin que nadie se entere. Calculándolo a partir de los movimientos, la anulación corrige el stock sola y el historial siempre explica el número que se ve en pantalla.</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>HU-41 · Sprint 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="39" customHeight="1">
+          <t>HU-42, HU-46 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
       <c r="A28" s="17" t="n">
         <v>24</v>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>El ajuste de stock quedó partido en dos motivos</t>
+          <t>El efecto de un motivo de stock no se puede cambiar una vez usado</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>El backlog pedía un motivo "ajuste" a secas, pero un mismo motivo no puede a veces sumar y a veces restar: si el efecto no es fijo, el historial es imposible de interpretar. Se cargan "Ajuste positivo" y "Ajuste negativo".</t>
+          <t>El stock se calcula recorriendo los movimientos y subiendo al motivo para saber si suman o restan. Dar vuelta "Venta" de salida a entrada reinterpretaría todo el historial y las existencias cambiarían solas. El nombre sí se puede corregir siempre.</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
@@ -6402,41 +6524,61 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
+    <row r="29" ht="39" customHeight="1">
       <c r="A29" s="15" t="n">
         <v>25</v>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>El movimiento de dinero se ofrece, no se crea solo</t>
+          <t>El ajuste de stock quedó partido en dos motivos</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>El sistema no conoce los precios, así que no puede calcular el monto; y una venta puede haberse cobrado de otra manera. El sistema propone el movimiento con la fecha y el detalle ya armados, y la persona decide. Si dice que no, el movimiento de stock queda marcado como "falta el dinero" en el historial, que es lo que después descuadra.</t>
+          <t>El backlog pedía un motivo "ajuste" a secas, pero un mismo motivo no puede a veces sumar y a veces restar: si el efecto no es fijo, el historial es imposible de interpretar. Se cargan "Ajuste positivo" y "Ajuste negativo".</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>HU-45 · Sprint 08</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="39" customHeight="1">
+          <t>HU-41 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="65" customHeight="1">
       <c r="A30" s="17" t="n">
         <v>26</v>
       </c>
       <c r="B30" s="26" t="inlineStr">
         <is>
+          <t>El movimiento de dinero se ofrece, no se crea solo</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>El sistema no conoce los precios, así que no puede calcular el monto; y una venta puede haberse cobrado de otra manera. El sistema propone el movimiento con la fecha y el detalle ya armados, y la persona decide. Si dice que no, el movimiento de stock queda marcado como "falta el dinero" en el historial, que es lo que después descuadra.</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>HU-45 · Sprint 08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="39" customHeight="1">
+      <c r="A31" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="inlineStr">
+        <is>
           <t>La unidad de medida es una lista cerrada, no un texto libre</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Con texto libre conviven "kg", "Kg", "kilo" y "kilos" en el mismo catálogo, y después no hay forma de sumar el stock ni de agrupar un reporte. La lista vive en un archivo de configuración, así que ampliarla es una línea.</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>HU-38 · Sprint 07</t>
         </is>
@@ -6457,7 +6599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I421"/>
+  <dimension ref="A1:I423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18999,10 +19141,14 @@
       </c>
       <c r="H320" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I320" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I320" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="14" t="inlineStr">
@@ -19034,10 +19180,14 @@
       </c>
       <c r="H321" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I321" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I321" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="16" t="inlineStr">
@@ -19053,7 +19203,7 @@
       <c r="C322" s="16" t="inlineStr"/>
       <c r="D322" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Reemplazar 'naturaleza' por una pregunta en castellano llano</t>
+          <t xml:space="preserve">    Reemplazar 'naturaleza' por dos botones: entró o salió</t>
         </is>
       </c>
       <c r="E322" s="17" t="inlineStr"/>
@@ -19069,10 +19219,14 @@
       </c>
       <c r="H322" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I322" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I322" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="14" t="inlineStr">
@@ -19088,7 +19242,7 @@
       <c r="C323" s="14" t="inlineStr"/>
       <c r="D323" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Ponerle apellido a las dos pantallas de categorías (dinero y productos)</t>
+          <t xml:space="preserve">    Ponerle apellido a las dos pantallas: categorías de movimientos y de productos</t>
         </is>
       </c>
       <c r="E323" s="15" t="inlineStr"/>
@@ -19104,10 +19258,14 @@
       </c>
       <c r="H323" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I323" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I323" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="16" t="inlineStr">
@@ -19139,10 +19297,14 @@
       </c>
       <c r="H324" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I324" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I324" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="14" t="inlineStr">
@@ -19174,276 +19336,308 @@
       </c>
       <c r="H325" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I325" s="14" t="inlineStr"/>
-    </row>
-    <row r="326" ht="26" customHeight="1">
-      <c r="A326" s="12" t="inlineStr">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I325" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="16" t="inlineStr">
+        <is>
+          <t>T-84.6</t>
+        </is>
+      </c>
+      <c r="B326" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C326" s="16" t="inlineStr"/>
+      <c r="D326" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Aplicar el mismo vocabulario a los mensajes que devuelve el servidor</t>
+        </is>
+      </c>
+      <c r="E326" s="17" t="inlineStr"/>
+      <c r="F326" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G326" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H326" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I326" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="26" customHeight="1">
+      <c r="A327" s="12" t="inlineStr">
         <is>
           <t>HU-85</t>
         </is>
       </c>
-      <c r="B326" s="12" t="inlineStr">
+      <c r="B327" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C326" s="12" t="inlineStr">
+      <c r="C327" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D326" s="12" t="inlineStr">
+      <c r="D327" s="12" t="inlineStr">
         <is>
           <t>Como operador quiero ver en el celular la columna que me importa para no tener que arrastrar la tabla de costado.</t>
         </is>
       </c>
-      <c r="E326" s="13" t="inlineStr">
+      <c r="E327" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F326" s="13" t="inlineStr">
+      <c r="F327" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G326" s="13" t="inlineStr">
+      <c r="G327" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H326" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I326" s="12" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" s="14" t="inlineStr">
+      <c r="H327" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I327" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="14" t="inlineStr">
         <is>
           <t>T-85.1</t>
         </is>
       </c>
-      <c r="B327" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C327" s="14" t="inlineStr"/>
-      <c r="D327" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Convertir los tres listados en tarjetas por debajo de 768 px</t>
-        </is>
-      </c>
-      <c r="E327" s="15" t="inlineStr"/>
-      <c r="F327" s="15" t="inlineStr">
+      <c r="B328" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C328" s="14" t="inlineStr"/>
+      <c r="D328" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Escribir el patrón de tarjetas en una hoja compartida, para que lo use toda la app</t>
+        </is>
+      </c>
+      <c r="E328" s="15" t="inlineStr"/>
+      <c r="F328" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G327" s="15" t="inlineStr">
+      <c r="G328" s="15" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H327" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I327" s="14" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" s="16" t="inlineStr">
+      <c r="H328" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I328" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="16" t="inlineStr">
         <is>
           <t>T-85.2</t>
         </is>
       </c>
-      <c r="B328" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C328" s="16" t="inlineStr"/>
-      <c r="D328" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Compactar el encabezado en celular</t>
-        </is>
-      </c>
-      <c r="E328" s="17" t="inlineStr"/>
-      <c r="F328" s="17" t="inlineStr">
+      <c r="B329" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C329" s="16" t="inlineStr"/>
+      <c r="D329" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Convertir los listados en tarjetas por debajo de 768 px</t>
+        </is>
+      </c>
+      <c r="E329" s="17" t="inlineStr"/>
+      <c r="F329" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G328" s="17" t="inlineStr">
+      <c r="G329" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H328" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I328" s="16" t="inlineStr"/>
-    </row>
-    <row r="329">
-      <c r="A329" s="14" t="inlineStr">
+      <c r="H329" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I329" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="14" t="inlineStr">
         <is>
           <t>T-85.3</t>
         </is>
       </c>
-      <c r="B329" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C329" s="14" t="inlineStr"/>
-      <c r="D329" s="14" t="inlineStr">
+      <c r="B330" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C330" s="14" t="inlineStr"/>
+      <c r="D330" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Compactar el encabezado en celular con un botón de menú</t>
+        </is>
+      </c>
+      <c r="E330" s="15" t="inlineStr"/>
+      <c r="F330" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G330" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H330" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I330" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="16" t="inlineStr">
+        <is>
+          <t>T-85.4</t>
+        </is>
+      </c>
+      <c r="B331" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C331" s="16" t="inlineStr"/>
+      <c r="D331" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Validar en 375 px que no quede scroll horizontal</t>
         </is>
       </c>
-      <c r="E329" s="15" t="inlineStr"/>
-      <c r="F329" s="15" t="inlineStr">
+      <c r="E331" s="17" t="inlineStr"/>
+      <c r="F331" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G329" s="15" t="inlineStr">
+      <c r="G331" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H329" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I329" s="14" t="inlineStr"/>
-    </row>
-    <row r="330" ht="26" customHeight="1">
-      <c r="A330" s="12" t="inlineStr">
+      <c r="H331" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I331" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="26" customHeight="1">
+      <c r="A332" s="12" t="inlineStr">
         <is>
           <t>HU-86</t>
         </is>
       </c>
-      <c r="B330" s="12" t="inlineStr">
+      <c r="B332" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C330" s="12" t="inlineStr">
+      <c r="C332" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D330" s="12" t="inlineStr">
+      <c r="D332" s="12" t="inlineStr">
         <is>
           <t>Como administrador quiero encontrar la configuración en un solo lugar para no buscarla abajo de mi nombre.</t>
         </is>
       </c>
-      <c r="E330" s="13" t="inlineStr">
+      <c r="E332" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F330" s="13" t="inlineStr">
+      <c r="F332" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G330" s="13" t="inlineStr">
+      <c r="G332" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H330" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I330" s="12" t="inlineStr"/>
-    </row>
-    <row r="331">
-      <c r="A331" s="14" t="inlineStr">
-        <is>
-          <t>T-86.1</t>
-        </is>
-      </c>
-      <c r="B331" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C331" s="14" t="inlineStr"/>
-      <c r="D331" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agrupar las cuatro pantallas de configuración en el menú principal</t>
-        </is>
-      </c>
-      <c r="E331" s="15" t="inlineStr"/>
-      <c r="F331" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G331" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H331" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I331" s="14" t="inlineStr"/>
-    </row>
-    <row r="332">
-      <c r="A332" s="16" t="inlineStr">
-        <is>
-          <t>T-86.2</t>
-        </is>
-      </c>
-      <c r="B332" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C332" s="16" t="inlineStr"/>
-      <c r="D332" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Dejar en el menú del usuario sólo lo personal y cerrar sesión</t>
-        </is>
-      </c>
-      <c r="E332" s="17" t="inlineStr"/>
-      <c r="F332" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G332" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H332" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I332" s="16" t="inlineStr"/>
+      <c r="H332" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I332" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="14" t="inlineStr">
         <is>
-          <t>T-86.3</t>
+          <t>T-86.1</t>
         </is>
       </c>
       <c r="B333" s="14" t="inlineStr">
@@ -19454,7 +19648,7 @@
       <c r="C333" s="14" t="inlineStr"/>
       <c r="D333" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Mover el acceso a motivos desde Productos a Stock</t>
+          <t xml:space="preserve">    Agrupar las cuatro pantallas de configuración en el menú principal</t>
         </is>
       </c>
       <c r="E333" s="15" t="inlineStr"/>
@@ -19470,58 +19664,58 @@
       </c>
       <c r="H333" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I333" s="14" t="inlineStr"/>
-    </row>
-    <row r="334" ht="26" customHeight="1">
-      <c r="A334" s="12" t="inlineStr">
-        <is>
-          <t>HU-50</t>
-        </is>
-      </c>
-      <c r="B334" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C334" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D334" s="12" t="inlineStr">
-        <is>
-          <t>Como equipo quiero probar los módulos de productos y servicios para entregarlos sin errores.</t>
-        </is>
-      </c>
-      <c r="E334" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F334" s="13" t="inlineStr">
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I333" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="16" t="inlineStr">
+        <is>
+          <t>T-86.2</t>
+        </is>
+      </c>
+      <c r="B334" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C334" s="16" t="inlineStr"/>
+      <c r="D334" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Dejar en el menú del usuario sólo lo personal y cerrar sesión</t>
+        </is>
+      </c>
+      <c r="E334" s="17" t="inlineStr"/>
+      <c r="F334" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G334" s="13" t="inlineStr">
+      <c r="G334" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H334" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I334" s="12" t="inlineStr"/>
+      <c r="H334" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I334" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="14" t="inlineStr">
         <is>
-          <t>T-50.1</t>
+          <t>T-86.3</t>
         </is>
       </c>
       <c r="B335" s="14" t="inlineStr">
@@ -19532,7 +19726,7 @@
       <c r="C335" s="14" t="inlineStr"/>
       <c r="D335" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de stock</t>
+          <t xml:space="preserve">    Mover el acceso a motivos desde Productos a Stock</t>
         </is>
       </c>
       <c r="E335" s="15" t="inlineStr"/>
@@ -19548,50 +19742,62 @@
       </c>
       <c r="H335" s="14" t="inlineStr">
         <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I335" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="26" customHeight="1">
+      <c r="A336" s="12" t="inlineStr">
+        <is>
+          <t>HU-50</t>
+        </is>
+      </c>
+      <c r="B336" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C336" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D336" s="12" t="inlineStr">
+        <is>
+          <t>Como equipo quiero probar los módulos de productos y servicios para entregarlos sin errores.</t>
+        </is>
+      </c>
+      <c r="E336" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F336" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G336" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H336" s="12" t="inlineStr">
+        <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I335" s="14" t="inlineStr"/>
-    </row>
-    <row r="336">
-      <c r="A336" s="16" t="inlineStr">
-        <is>
-          <t>T-50.2</t>
-        </is>
-      </c>
-      <c r="B336" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C336" s="16" t="inlineStr"/>
-      <c r="D336" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de servicios</t>
-        </is>
-      </c>
-      <c r="E336" s="17" t="inlineStr"/>
-      <c r="F336" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G336" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H336" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I336" s="16" t="inlineStr"/>
+      <c r="I336" s="12" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="14" t="inlineStr">
         <is>
-          <t>T-50.3</t>
+          <t>T-50.1</t>
         </is>
       </c>
       <c r="B337" s="14" t="inlineStr">
@@ -19602,7 +19808,7 @@
       <c r="C337" s="14" t="inlineStr"/>
       <c r="D337" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Validar ambas pantallas en celular</t>
+          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de stock</t>
         </is>
       </c>
       <c r="E337" s="15" t="inlineStr"/>
@@ -19623,53 +19829,45 @@
       </c>
       <c r="I337" s="14" t="inlineStr"/>
     </row>
-    <row r="338" ht="16" customHeight="1">
-      <c r="A338" s="12" t="inlineStr">
-        <is>
-          <t>HU-62</t>
-        </is>
-      </c>
-      <c r="B338" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C338" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D338" s="12" t="inlineStr">
-        <is>
-          <t>Como equipo quiero probar el módulo de articulación para entregarlo funcionando.</t>
-        </is>
-      </c>
-      <c r="E338" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F338" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G338" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 12</t>
-        </is>
-      </c>
-      <c r="H338" s="12" t="inlineStr">
+    <row r="338">
+      <c r="A338" s="16" t="inlineStr">
+        <is>
+          <t>T-50.2</t>
+        </is>
+      </c>
+      <c r="B338" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C338" s="16" t="inlineStr"/>
+      <c r="D338" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de servicios</t>
+        </is>
+      </c>
+      <c r="E338" s="17" t="inlineStr"/>
+      <c r="F338" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G338" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H338" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I338" s="12" t="inlineStr"/>
+      <c r="I338" s="16" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="14" t="inlineStr">
         <is>
-          <t>T-62.1</t>
+          <t>T-50.3</t>
         </is>
       </c>
       <c r="B339" s="14" t="inlineStr">
@@ -19680,61 +19878,61 @@
       <c r="C339" s="14" t="inlineStr"/>
       <c r="D339" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de coincidencia</t>
+          <t xml:space="preserve">    Validar ambas pantallas en celular</t>
         </is>
       </c>
       <c r="E339" s="15" t="inlineStr"/>
       <c r="F339" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G339" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H339" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I339" s="14" t="inlineStr"/>
+    </row>
+    <row r="340" ht="16" customHeight="1">
+      <c r="A340" s="12" t="inlineStr">
+        <is>
+          <t>HU-62</t>
+        </is>
+      </c>
+      <c r="B340" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C340" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D340" s="12" t="inlineStr">
+        <is>
+          <t>Como equipo quiero probar el módulo de articulación para entregarlo funcionando.</t>
+        </is>
+      </c>
+      <c r="E340" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F340" s="13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G339" s="15" t="inlineStr">
+      <c r="G340" s="13" t="inlineStr">
         <is>
           <t>Sprint 12</t>
-        </is>
-      </c>
-      <c r="H339" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I339" s="14" t="inlineStr"/>
-    </row>
-    <row r="340" ht="26" customHeight="1">
-      <c r="A340" s="12" t="inlineStr">
-        <is>
-          <t>HU-63</t>
-        </is>
-      </c>
-      <c r="B340" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C340" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D340" s="12" t="inlineStr">
-        <is>
-          <t>Como equipo quiero definir el nombre y la identidad del producto para que acompañen al público al que apunta.</t>
-        </is>
-      </c>
-      <c r="E340" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F340" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G340" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
         </is>
       </c>
       <c r="H340" s="12" t="inlineStr">
@@ -19747,7 +19945,7 @@
     <row r="341">
       <c r="A341" s="14" t="inlineStr">
         <is>
-          <t>T-63.1</t>
+          <t>T-62.1</t>
         </is>
       </c>
       <c r="B341" s="14" t="inlineStr">
@@ -19758,7 +19956,7 @@
       <c r="C341" s="14" t="inlineStr"/>
       <c r="D341" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el nombre del producto con el equipo</t>
+          <t xml:space="preserve">    Escribir y ejecutar los casos de prueba de coincidencia</t>
         </is>
       </c>
       <c r="E341" s="15" t="inlineStr"/>
@@ -19769,55 +19967,63 @@
       </c>
       <c r="G341" s="15" t="inlineStr">
         <is>
+          <t>Sprint 12</t>
+        </is>
+      </c>
+      <c r="H341" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I341" s="14" t="inlineStr"/>
+    </row>
+    <row r="342" ht="26" customHeight="1">
+      <c r="A342" s="12" t="inlineStr">
+        <is>
+          <t>HU-63</t>
+        </is>
+      </c>
+      <c r="B342" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C342" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D342" s="12" t="inlineStr">
+        <is>
+          <t>Como equipo quiero definir el nombre y la identidad del producto para que acompañen al público al que apunta.</t>
+        </is>
+      </c>
+      <c r="E342" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F342" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G342" s="13" t="inlineStr">
+        <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H341" s="14" t="inlineStr">
+      <c r="H342" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I341" s="14" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" s="16" t="inlineStr">
-        <is>
-          <t>T-63.2</t>
-        </is>
-      </c>
-      <c r="B342" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C342" s="16" t="inlineStr"/>
-      <c r="D342" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Aplicarlo en la interfaz y en los títulos de las pantallas</t>
-        </is>
-      </c>
-      <c r="E342" s="17" t="inlineStr"/>
-      <c r="F342" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G342" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H342" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I342" s="16" t="inlineStr"/>
+      <c r="I342" s="12" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="14" t="inlineStr">
         <is>
-          <t>T-63.3</t>
+          <t>T-63.1</t>
         </is>
       </c>
       <c r="B343" s="14" t="inlineStr">
@@ -19828,7 +20034,7 @@
       <c r="C343" s="14" t="inlineStr"/>
       <c r="D343" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Renombrar la base de datos y el repositorio</t>
+          <t xml:space="preserve">    Definir el nombre del producto con el equipo</t>
         </is>
       </c>
       <c r="E343" s="15" t="inlineStr"/>
@@ -19852,7 +20058,7 @@
     <row r="344">
       <c r="A344" s="16" t="inlineStr">
         <is>
-          <t>T-63.4</t>
+          <t>T-63.2</t>
         </is>
       </c>
       <c r="B344" s="16" t="inlineStr">
@@ -19863,7 +20069,7 @@
       <c r="C344" s="16" t="inlineStr"/>
       <c r="D344" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Actualizar la documentación y la validación de idea</t>
+          <t xml:space="preserve">    Aplicarlo en la interfaz y en los títulos de las pantallas</t>
         </is>
       </c>
       <c r="E344" s="17" t="inlineStr"/>
@@ -19884,123 +20090,123 @@
       </c>
       <c r="I344" s="16" t="inlineStr"/>
     </row>
-    <row r="345" ht="26" customHeight="1">
-      <c r="A345" s="12" t="inlineStr">
+    <row r="345">
+      <c r="A345" s="14" t="inlineStr">
+        <is>
+          <t>T-63.3</t>
+        </is>
+      </c>
+      <c r="B345" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C345" s="14" t="inlineStr"/>
+      <c r="D345" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Renombrar la base de datos y el repositorio</t>
+        </is>
+      </c>
+      <c r="E345" s="15" t="inlineStr"/>
+      <c r="F345" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G345" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H345" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I345" s="14" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="16" t="inlineStr">
+        <is>
+          <t>T-63.4</t>
+        </is>
+      </c>
+      <c r="B346" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C346" s="16" t="inlineStr"/>
+      <c r="D346" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Actualizar la documentación y la validación de idea</t>
+        </is>
+      </c>
+      <c r="E346" s="17" t="inlineStr"/>
+      <c r="F346" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G346" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H346" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I346" s="16" t="inlineStr"/>
+    </row>
+    <row r="347" ht="26" customHeight="1">
+      <c r="A347" s="12" t="inlineStr">
         <is>
           <t>HU-64</t>
         </is>
       </c>
-      <c r="B345" s="12" t="inlineStr">
+      <c r="B347" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C345" s="12" t="inlineStr">
+      <c r="C347" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D345" s="12" t="inlineStr">
+      <c r="D347" s="12" t="inlineStr">
         <is>
           <t>Como usuario con poca experiencia digital quiero una interfaz clara para poder usar el sistema sin ayuda.</t>
         </is>
       </c>
-      <c r="E345" s="13" t="inlineStr">
+      <c r="E347" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F345" s="13" t="inlineStr">
+      <c r="F347" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G345" s="13" t="inlineStr">
+      <c r="G347" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H345" s="12" t="inlineStr">
+      <c r="H347" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I345" s="12" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" s="14" t="inlineStr">
-        <is>
-          <t>T-64.1</t>
-        </is>
-      </c>
-      <c r="B346" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C346" s="14" t="inlineStr"/>
-      <c r="D346" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Revisar los textos y rótulos de todas las pantallas</t>
-        </is>
-      </c>
-      <c r="E346" s="15" t="inlineStr"/>
-      <c r="F346" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G346" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H346" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I346" s="14" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" s="16" t="inlineStr">
-        <is>
-          <t>T-64.2</t>
-        </is>
-      </c>
-      <c r="B347" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C347" s="16" t="inlineStr"/>
-      <c r="D347" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agregar ayudas contextuales</t>
-        </is>
-      </c>
-      <c r="E347" s="17" t="inlineStr"/>
-      <c r="F347" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G347" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H347" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I347" s="16" t="inlineStr"/>
+      <c r="I347" s="12" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="14" t="inlineStr">
         <is>
-          <t>T-64.3</t>
+          <t>T-64.1</t>
         </is>
       </c>
       <c r="B348" s="14" t="inlineStr">
@@ -20011,7 +20217,7 @@
       <c r="C348" s="14" t="inlineStr"/>
       <c r="D348" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Revisar el contraste y el tamaño de la tipografía</t>
+          <t xml:space="preserve">    Revisar los textos y rótulos de todas las pantallas</t>
         </is>
       </c>
       <c r="E348" s="15" t="inlineStr"/>
@@ -20035,7 +20241,7 @@
     <row r="349">
       <c r="A349" s="16" t="inlineStr">
         <is>
-          <t>T-64.4</t>
+          <t>T-64.2</t>
         </is>
       </c>
       <c r="B349" s="16" t="inlineStr">
@@ -20046,7 +20252,7 @@
       <c r="C349" s="16" t="inlineStr"/>
       <c r="D349" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Validar la interfaz con un usuario real</t>
+          <t xml:space="preserve">    Agregar ayudas contextuales</t>
         </is>
       </c>
       <c r="E349" s="17" t="inlineStr"/>
@@ -20067,123 +20273,123 @@
       </c>
       <c r="I349" s="16" t="inlineStr"/>
     </row>
-    <row r="350" ht="26" customHeight="1">
-      <c r="A350" s="12" t="inlineStr">
+    <row r="350">
+      <c r="A350" s="14" t="inlineStr">
+        <is>
+          <t>T-64.3</t>
+        </is>
+      </c>
+      <c r="B350" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C350" s="14" t="inlineStr"/>
+      <c r="D350" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revisar el contraste y el tamaño de la tipografía</t>
+        </is>
+      </c>
+      <c r="E350" s="15" t="inlineStr"/>
+      <c r="F350" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G350" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H350" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I350" s="14" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="16" t="inlineStr">
+        <is>
+          <t>T-64.4</t>
+        </is>
+      </c>
+      <c r="B351" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C351" s="16" t="inlineStr"/>
+      <c r="D351" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Validar la interfaz con un usuario real</t>
+        </is>
+      </c>
+      <c r="E351" s="17" t="inlineStr"/>
+      <c r="F351" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G351" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H351" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I351" s="16" t="inlineStr"/>
+    </row>
+    <row r="352" ht="26" customHeight="1">
+      <c r="A352" s="12" t="inlineStr">
         <is>
           <t>HU-87</t>
         </is>
       </c>
-      <c r="B350" s="12" t="inlineStr">
+      <c r="B352" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C350" s="12" t="inlineStr">
+      <c r="C352" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D350" s="12" t="inlineStr">
+      <c r="D352" s="12" t="inlineStr">
         <is>
           <t>Como tesorero quiero cargar un movimiento en menos pasos para no contestar tres preguntas encadenadas.</t>
         </is>
       </c>
-      <c r="E350" s="13" t="inlineStr">
+      <c r="E352" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F350" s="13" t="inlineStr">
+      <c r="F352" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G350" s="13" t="inlineStr">
+      <c r="G352" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H350" s="12" t="inlineStr">
+      <c r="H352" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I350" s="12" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" s="14" t="inlineStr">
-        <is>
-          <t>T-87.1</t>
-        </is>
-      </c>
-      <c r="B351" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C351" s="14" t="inlineStr"/>
-      <c r="D351" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Reemplazar los tres desplegables encadenados por uno solo</t>
-        </is>
-      </c>
-      <c r="E351" s="15" t="inlineStr"/>
-      <c r="F351" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G351" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H351" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I351" s="14" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="16" t="inlineStr">
-        <is>
-          <t>T-87.2</t>
-        </is>
-      </c>
-      <c r="B352" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C352" s="16" t="inlineStr"/>
-      <c r="D352" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Ofrecer entró/salió como dos botones en vez de un desplegable</t>
-        </is>
-      </c>
-      <c r="E352" s="17" t="inlineStr"/>
-      <c r="F352" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G352" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H352" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I352" s="16" t="inlineStr"/>
+      <c r="I352" s="12" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="14" t="inlineStr">
         <is>
-          <t>T-87.3</t>
+          <t>T-87.1</t>
         </is>
       </c>
       <c r="B353" s="14" t="inlineStr">
@@ -20194,7 +20400,7 @@
       <c r="C353" s="14" t="inlineStr"/>
       <c r="D353" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
+          <t xml:space="preserve">    Reemplazar los tres desplegables encadenados por uno solo</t>
         </is>
       </c>
       <c r="E353" s="15" t="inlineStr"/>
@@ -20215,53 +20421,45 @@
       </c>
       <c r="I353" s="14" t="inlineStr"/>
     </row>
-    <row r="354" ht="26" customHeight="1">
-      <c r="A354" s="12" t="inlineStr">
-        <is>
-          <t>HU-88</t>
-        </is>
-      </c>
-      <c r="B354" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C354" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D354" s="12" t="inlineStr">
-        <is>
-          <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
-        </is>
-      </c>
-      <c r="E354" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F354" s="13" t="inlineStr">
+    <row r="354">
+      <c r="A354" s="16" t="inlineStr">
+        <is>
+          <t>T-87.2</t>
+        </is>
+      </c>
+      <c r="B354" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C354" s="16" t="inlineStr"/>
+      <c r="D354" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Ofrecer entró/salió como dos botones en vez de un desplegable</t>
+        </is>
+      </c>
+      <c r="E354" s="17" t="inlineStr"/>
+      <c r="F354" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G354" s="13" t="inlineStr">
+      <c r="G354" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H354" s="12" t="inlineStr">
+      <c r="H354" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I354" s="12" t="inlineStr"/>
+      <c r="I354" s="16" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="14" t="inlineStr">
         <is>
-          <t>T-88.1</t>
+          <t>T-87.3</t>
         </is>
       </c>
       <c r="B355" s="14" t="inlineStr">
@@ -20272,7 +20470,7 @@
       <c r="C355" s="14" t="inlineStr"/>
       <c r="D355" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Separar el listado vacío del listado filtrado en los cuatro listados</t>
+          <t xml:space="preserve">    Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
         </is>
       </c>
       <c r="E355" s="15" t="inlineStr"/>
@@ -20293,45 +20491,53 @@
       </c>
       <c r="I355" s="14" t="inlineStr"/>
     </row>
-    <row r="356">
-      <c r="A356" s="16" t="inlineStr">
-        <is>
-          <t>T-88.2</t>
-        </is>
-      </c>
-      <c r="B356" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C356" s="16" t="inlineStr"/>
-      <c r="D356" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
-        </is>
-      </c>
-      <c r="E356" s="17" t="inlineStr"/>
-      <c r="F356" s="17" t="inlineStr">
+    <row r="356" ht="26" customHeight="1">
+      <c r="A356" s="12" t="inlineStr">
+        <is>
+          <t>HU-88</t>
+        </is>
+      </c>
+      <c r="B356" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C356" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D356" s="12" t="inlineStr">
+        <is>
+          <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
+        </is>
+      </c>
+      <c r="E356" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F356" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G356" s="17" t="inlineStr">
+      <c r="G356" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H356" s="16" t="inlineStr">
+      <c r="H356" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I356" s="16" t="inlineStr"/>
+      <c r="I356" s="12" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="14" t="inlineStr">
         <is>
-          <t>T-88.3</t>
+          <t>T-88.1</t>
         </is>
       </c>
       <c r="B357" s="14" t="inlineStr">
@@ -20342,7 +20548,7 @@
       <c r="C357" s="14" t="inlineStr"/>
       <c r="D357" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
+          <t xml:space="preserve">    Separar el listado vacío del listado filtrado en los cuatro listados</t>
         </is>
       </c>
       <c r="E357" s="15" t="inlineStr"/>
@@ -20363,53 +20569,45 @@
       </c>
       <c r="I357" s="14" t="inlineStr"/>
     </row>
-    <row r="358" ht="16" customHeight="1">
-      <c r="A358" s="12" t="inlineStr">
-        <is>
-          <t>HU-65</t>
-        </is>
-      </c>
-      <c r="B358" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C358" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D358" s="12" t="inlineStr">
-        <is>
-          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
-        </is>
-      </c>
-      <c r="E358" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F358" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G358" s="13" t="inlineStr">
+    <row r="358">
+      <c r="A358" s="16" t="inlineStr">
+        <is>
+          <t>T-88.2</t>
+        </is>
+      </c>
+      <c r="B358" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C358" s="16" t="inlineStr"/>
+      <c r="D358" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
+        </is>
+      </c>
+      <c r="E358" s="17" t="inlineStr"/>
+      <c r="F358" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G358" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H358" s="12" t="inlineStr">
+      <c r="H358" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I358" s="12" t="inlineStr"/>
+      <c r="I358" s="16" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="14" t="inlineStr">
         <is>
-          <t>T-65.1</t>
+          <t>T-88.3</t>
         </is>
       </c>
       <c r="B359" s="14" t="inlineStr">
@@ -20420,66 +20618,74 @@
       <c r="C359" s="14" t="inlineStr"/>
       <c r="D359" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Revisar las pantallas de los módulos nuevos en ancho de celular</t>
+          <t xml:space="preserve">    Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
         </is>
       </c>
       <c r="E359" s="15" t="inlineStr"/>
       <c r="F359" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G359" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H359" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I359" s="14" t="inlineStr"/>
+    </row>
+    <row r="360" ht="16" customHeight="1">
+      <c r="A360" s="12" t="inlineStr">
+        <is>
+          <t>HU-65</t>
+        </is>
+      </c>
+      <c r="B360" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C360" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D360" s="12" t="inlineStr">
+        <is>
+          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
+        </is>
+      </c>
+      <c r="E360" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F360" s="13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G359" s="15" t="inlineStr">
+      <c r="G360" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H359" s="14" t="inlineStr">
+      <c r="H360" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I359" s="14" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" s="16" t="inlineStr">
-        <is>
-          <t>T-65.2</t>
-        </is>
-      </c>
-      <c r="B360" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C360" s="16" t="inlineStr"/>
-      <c r="D360" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Validar en Chrome y en un segundo navegador</t>
-        </is>
-      </c>
-      <c r="E360" s="17" t="inlineStr"/>
-      <c r="F360" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G360" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H360" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I360" s="16" t="inlineStr"/>
+      <c r="I360" s="12" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="14" t="inlineStr">
         <is>
-          <t>T-65.3</t>
+          <t>T-65.1</t>
         </is>
       </c>
       <c r="B361" s="14" t="inlineStr">
@@ -20490,7 +20696,7 @@
       <c r="C361" s="14" t="inlineStr"/>
       <c r="D361" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Validar en un celular real</t>
+          <t xml:space="preserve">    Revisar las pantallas de los módulos nuevos en ancho de celular</t>
         </is>
       </c>
       <c r="E361" s="15" t="inlineStr"/>
@@ -20511,53 +20717,45 @@
       </c>
       <c r="I361" s="14" t="inlineStr"/>
     </row>
-    <row r="362" ht="16" customHeight="1">
-      <c r="A362" s="12" t="inlineStr">
-        <is>
-          <t>HU-66</t>
-        </is>
-      </c>
-      <c r="B362" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C362" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D362" s="12" t="inlineStr">
-        <is>
-          <t>Como equipo quiero dejar el proyecto documentado para poder continuarlo el año próximo.</t>
-        </is>
-      </c>
-      <c r="E362" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F362" s="13" t="inlineStr">
+    <row r="362">
+      <c r="A362" s="16" t="inlineStr">
+        <is>
+          <t>T-65.2</t>
+        </is>
+      </c>
+      <c r="B362" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C362" s="16" t="inlineStr"/>
+      <c r="D362" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Validar en Chrome y en un segundo navegador</t>
+        </is>
+      </c>
+      <c r="E362" s="17" t="inlineStr"/>
+      <c r="F362" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G362" s="13" t="inlineStr">
+      <c r="G362" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H362" s="12" t="inlineStr">
+      <c r="H362" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I362" s="12" t="inlineStr"/>
+      <c r="I362" s="16" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="14" t="inlineStr">
         <is>
-          <t>T-66.1</t>
+          <t>T-65.3</t>
         </is>
       </c>
       <c r="B363" s="14" t="inlineStr">
@@ -20568,7 +20766,7 @@
       <c r="C363" s="14" t="inlineStr"/>
       <c r="D363" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Escribir el README con las instrucciones de instalación</t>
+          <t xml:space="preserve">    Validar en un celular real</t>
         </is>
       </c>
       <c r="E363" s="15" t="inlineStr"/>
@@ -20589,45 +20787,53 @@
       </c>
       <c r="I363" s="14" t="inlineStr"/>
     </row>
-    <row r="364">
-      <c r="A364" s="16" t="inlineStr">
-        <is>
-          <t>T-66.2</t>
-        </is>
-      </c>
-      <c r="B364" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C364" s="16" t="inlineStr"/>
-      <c r="D364" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Escribir el manual de usuario básico</t>
-        </is>
-      </c>
-      <c r="E364" s="17" t="inlineStr"/>
-      <c r="F364" s="17" t="inlineStr">
+    <row r="364" ht="16" customHeight="1">
+      <c r="A364" s="12" t="inlineStr">
+        <is>
+          <t>HU-66</t>
+        </is>
+      </c>
+      <c r="B364" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C364" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D364" s="12" t="inlineStr">
+        <is>
+          <t>Como equipo quiero dejar el proyecto documentado para poder continuarlo el año próximo.</t>
+        </is>
+      </c>
+      <c r="E364" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F364" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G364" s="17" t="inlineStr">
+      <c r="G364" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H364" s="16" t="inlineStr">
+      <c r="H364" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I364" s="16" t="inlineStr"/>
+      <c r="I364" s="12" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="14" t="inlineStr">
         <is>
-          <t>T-66.3</t>
+          <t>T-66.1</t>
         </is>
       </c>
       <c r="B365" s="14" t="inlineStr">
@@ -20638,7 +20844,7 @@
       <c r="C365" s="14" t="inlineStr"/>
       <c r="D365" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Documentar el modelo de datos</t>
+          <t xml:space="preserve">    Escribir el README con las instrucciones de instalación</t>
         </is>
       </c>
       <c r="E365" s="15" t="inlineStr"/>
@@ -20662,7 +20868,7 @@
     <row r="366">
       <c r="A366" s="16" t="inlineStr">
         <is>
-          <t>T-66.4</t>
+          <t>T-66.2</t>
         </is>
       </c>
       <c r="B366" s="16" t="inlineStr">
@@ -20673,7 +20879,7 @@
       <c r="C366" s="16" t="inlineStr"/>
       <c r="D366" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Documentar el diseño de los módulos que quedaron sin implementar</t>
+          <t xml:space="preserve">    Escribir el manual de usuario básico</t>
         </is>
       </c>
       <c r="E366" s="17" t="inlineStr"/>
@@ -20694,123 +20900,123 @@
       </c>
       <c r="I366" s="16" t="inlineStr"/>
     </row>
-    <row r="367" ht="16" customHeight="1">
-      <c r="A367" s="12" t="inlineStr">
+    <row r="367">
+      <c r="A367" s="14" t="inlineStr">
+        <is>
+          <t>T-66.3</t>
+        </is>
+      </c>
+      <c r="B367" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C367" s="14" t="inlineStr"/>
+      <c r="D367" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Documentar el modelo de datos</t>
+        </is>
+      </c>
+      <c r="E367" s="15" t="inlineStr"/>
+      <c r="F367" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G367" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H367" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I367" s="14" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="16" t="inlineStr">
+        <is>
+          <t>T-66.4</t>
+        </is>
+      </c>
+      <c r="B368" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C368" s="16" t="inlineStr"/>
+      <c r="D368" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Documentar el diseño de los módulos que quedaron sin implementar</t>
+        </is>
+      </c>
+      <c r="E368" s="17" t="inlineStr"/>
+      <c r="F368" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G368" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H368" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I368" s="16" t="inlineStr"/>
+    </row>
+    <row r="369" ht="16" customHeight="1">
+      <c r="A369" s="12" t="inlineStr">
         <is>
           <t>HU-67</t>
         </is>
       </c>
-      <c r="B367" s="12" t="inlineStr">
+      <c r="B369" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C367" s="12" t="inlineStr">
+      <c r="C369" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D367" s="12" t="inlineStr">
+      <c r="D369" s="12" t="inlineStr">
         <is>
           <t>Como equipo quiero probar el sistema completo para entregar una versión estable.</t>
         </is>
       </c>
-      <c r="E367" s="13" t="inlineStr">
+      <c r="E369" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F367" s="13" t="inlineStr">
+      <c r="F369" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G367" s="13" t="inlineStr">
+      <c r="G369" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H367" s="12" t="inlineStr">
+      <c r="H369" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I367" s="12" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" s="14" t="inlineStr">
-        <is>
-          <t>T-67.1</t>
-        </is>
-      </c>
-      <c r="B368" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C368" s="14" t="inlineStr"/>
-      <c r="D368" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Ejecutar la batería de pruebas de punta a punta</t>
-        </is>
-      </c>
-      <c r="E368" s="15" t="inlineStr"/>
-      <c r="F368" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G368" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H368" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I368" s="14" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" s="16" t="inlineStr">
-        <is>
-          <t>T-67.2</t>
-        </is>
-      </c>
-      <c r="B369" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C369" s="16" t="inlineStr"/>
-      <c r="D369" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Corregir los errores detectados</t>
-        </is>
-      </c>
-      <c r="E369" s="17" t="inlineStr"/>
-      <c r="F369" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G369" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H369" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I369" s="16" t="inlineStr"/>
+      <c r="I369" s="12" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="14" t="inlineStr">
         <is>
-          <t>T-67.3</t>
+          <t>T-67.1</t>
         </is>
       </c>
       <c r="B370" s="14" t="inlineStr">
@@ -20821,7 +21027,7 @@
       <c r="C370" s="14" t="inlineStr"/>
       <c r="D370" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Unificar la carga del encabezado en un archivo compartido</t>
+          <t xml:space="preserve">    Ejecutar la batería de pruebas de punta a punta</t>
         </is>
       </c>
       <c r="E370" s="15" t="inlineStr"/>
@@ -20842,154 +21048,154 @@
       </c>
       <c r="I370" s="14" t="inlineStr"/>
     </row>
-    <row r="371" ht="20" customHeight="1">
-      <c r="A371" s="9" t="inlineStr">
+    <row r="371">
+      <c r="A371" s="16" t="inlineStr">
+        <is>
+          <t>T-67.2</t>
+        </is>
+      </c>
+      <c r="B371" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C371" s="16" t="inlineStr"/>
+      <c r="D371" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Corregir los errores detectados</t>
+        </is>
+      </c>
+      <c r="E371" s="17" t="inlineStr"/>
+      <c r="F371" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G371" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H371" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I371" s="16" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="14" t="inlineStr">
+        <is>
+          <t>T-67.3</t>
+        </is>
+      </c>
+      <c r="B372" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C372" s="14" t="inlineStr"/>
+      <c r="D372" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Unificar la carga del encabezado en un archivo compartido</t>
+        </is>
+      </c>
+      <c r="E372" s="15" t="inlineStr"/>
+      <c r="F372" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G372" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H372" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I372" s="14" t="inlineStr"/>
+    </row>
+    <row r="373" ht="20" customHeight="1">
+      <c r="A373" s="9" t="inlineStr">
         <is>
           <t>E11</t>
         </is>
       </c>
-      <c r="B371" s="9" t="inlineStr">
+      <c r="B373" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C371" s="9" t="inlineStr">
+      <c r="C373" s="9" t="inlineStr">
         <is>
           <t>Chat y Notificaciones</t>
         </is>
       </c>
-      <c r="D371" s="9" t="inlineStr">
+      <c r="D373" s="9" t="inlineStr">
         <is>
           <t>Mensajería entre empresas (posterior al MVP)</t>
         </is>
       </c>
-      <c r="E371" s="10" t="inlineStr">
+      <c r="E373" s="10" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F371" s="11" t="n"/>
-      <c r="G371" s="11" t="n"/>
-      <c r="H371" s="11" t="n"/>
-      <c r="I371" s="11" t="n"/>
-    </row>
-    <row r="372" ht="16" customHeight="1">
-      <c r="A372" s="12" t="inlineStr">
+      <c r="F373" s="11" t="n"/>
+      <c r="G373" s="11" t="n"/>
+      <c r="H373" s="11" t="n"/>
+      <c r="I373" s="11" t="n"/>
+    </row>
+    <row r="374" ht="16" customHeight="1">
+      <c r="A374" s="12" t="inlineStr">
         <is>
           <t>HU-73</t>
         </is>
       </c>
-      <c r="B372" s="12" t="inlineStr">
+      <c r="B374" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C372" s="12" t="inlineStr">
+      <c r="C374" s="12" t="inlineStr">
         <is>
           <t>Chat y Notificaciones</t>
         </is>
       </c>
-      <c r="D372" s="12" t="inlineStr">
+      <c r="D374" s="12" t="inlineStr">
         <is>
           <t>Como empresa quiero chatear con otra empresa para coordinar una articulación.</t>
         </is>
       </c>
-      <c r="E372" s="13" t="inlineStr">
+      <c r="E374" s="13" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F372" s="13" t="inlineStr">
+      <c r="F374" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G372" s="13" t="inlineStr">
+      <c r="G374" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H372" s="12" t="inlineStr">
+      <c r="H374" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I372" s="12" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" s="14" t="inlineStr">
-        <is>
-          <t>T-73.1</t>
-        </is>
-      </c>
-      <c r="B373" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C373" s="14" t="inlineStr"/>
-      <c r="D373" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Diseñar la pantalla de chat</t>
-        </is>
-      </c>
-      <c r="E373" s="15" t="inlineStr"/>
-      <c r="F373" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G373" s="15" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H373" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I373" s="14" t="inlineStr"/>
-    </row>
-    <row r="374">
-      <c r="A374" s="16" t="inlineStr">
-        <is>
-          <t>T-73.2</t>
-        </is>
-      </c>
-      <c r="B374" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C374" s="16" t="inlineStr"/>
-      <c r="D374" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el envío y la recepción de mensajes</t>
-        </is>
-      </c>
-      <c r="E374" s="17" t="inlineStr"/>
-      <c r="F374" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G374" s="17" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H374" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I374" s="16" t="inlineStr"/>
+      <c r="I374" s="12" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="14" t="inlineStr">
         <is>
-          <t>T-73.3</t>
+          <t>T-73.1</t>
         </is>
       </c>
       <c r="B375" s="14" t="inlineStr">
@@ -21000,7 +21206,7 @@
       <c r="C375" s="14" t="inlineStr"/>
       <c r="D375" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Agregar notificaciones de mensaje nuevo</t>
+          <t xml:space="preserve">    Diseñar la pantalla de chat</t>
         </is>
       </c>
       <c r="E375" s="15" t="inlineStr"/>
@@ -21021,157 +21227,149 @@
       </c>
       <c r="I375" s="14" t="inlineStr"/>
     </row>
-    <row r="376" ht="20" customHeight="1">
-      <c r="A376" s="9" t="inlineStr">
+    <row r="376">
+      <c r="A376" s="16" t="inlineStr">
+        <is>
+          <t>T-73.2</t>
+        </is>
+      </c>
+      <c r="B376" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C376" s="16" t="inlineStr"/>
+      <c r="D376" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar el envío y la recepción de mensajes</t>
+        </is>
+      </c>
+      <c r="E376" s="17" t="inlineStr"/>
+      <c r="F376" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G376" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H376" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I376" s="16" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="14" t="inlineStr">
+        <is>
+          <t>T-73.3</t>
+        </is>
+      </c>
+      <c r="B377" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C377" s="14" t="inlineStr"/>
+      <c r="D377" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agregar notificaciones de mensaje nuevo</t>
+        </is>
+      </c>
+      <c r="E377" s="15" t="inlineStr"/>
+      <c r="F377" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G377" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H377" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I377" s="14" t="inlineStr"/>
+    </row>
+    <row r="378" ht="20" customHeight="1">
+      <c r="A378" s="9" t="inlineStr">
         <is>
           <t>E12</t>
         </is>
       </c>
-      <c r="B376" s="9" t="inlineStr">
+      <c r="B378" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C376" s="9" t="inlineStr">
+      <c r="C378" s="9" t="inlineStr">
         <is>
           <t>Configuración de Módulos</t>
         </is>
       </c>
-      <c r="D376" s="9" t="inlineStr">
+      <c r="D378" s="9" t="inlineStr">
         <is>
           <t>Cada empresa activa sólo los módulos que usa</t>
         </is>
       </c>
-      <c r="E376" s="10" t="inlineStr">
+      <c r="E378" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F376" s="11" t="n"/>
-      <c r="G376" s="11" t="n"/>
-      <c r="H376" s="11" t="n"/>
-      <c r="I376" s="11" t="n"/>
-    </row>
-    <row r="377" ht="26" customHeight="1">
-      <c r="A377" s="12" t="inlineStr">
+      <c r="F378" s="11" t="n"/>
+      <c r="G378" s="11" t="n"/>
+      <c r="H378" s="11" t="n"/>
+      <c r="I378" s="11" t="n"/>
+    </row>
+    <row r="379" ht="26" customHeight="1">
+      <c r="A379" s="12" t="inlineStr">
         <is>
           <t>HU-34</t>
         </is>
       </c>
-      <c r="B377" s="12" t="inlineStr">
+      <c r="B379" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C377" s="12" t="inlineStr">
+      <c r="C379" s="12" t="inlineStr">
         <is>
           <t>Configuración de Módulos</t>
         </is>
       </c>
-      <c r="D377" s="12" t="inlineStr">
+      <c r="D379" s="12" t="inlineStr">
         <is>
           <t>Como administrador de la empresa quiero activar sólo los módulos que mi empresa usa para no ver funciones que no necesito.</t>
         </is>
       </c>
-      <c r="E377" s="13" t="inlineStr">
+      <c r="E379" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F377" s="13" t="inlineStr">
+      <c r="F379" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G377" s="13" t="inlineStr">
+      <c r="G379" s="13" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H377" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I377" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" s="14" t="inlineStr">
-        <is>
-          <t>T-34.1</t>
-        </is>
-      </c>
-      <c r="B378" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C378" s="14" t="inlineStr"/>
-      <c r="D378" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Crear la tabla de módulos activos por empresa</t>
-        </is>
-      </c>
-      <c r="E378" s="15" t="inlineStr"/>
-      <c r="F378" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G378" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H378" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I378" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="16" t="inlineStr">
-        <is>
-          <t>T-34.2</t>
-        </is>
-      </c>
-      <c r="B379" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C379" s="16" t="inlineStr"/>
-      <c r="D379" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Definir el conjunto de módulos disponibles</t>
-        </is>
-      </c>
-      <c r="E379" s="17" t="inlineStr"/>
-      <c r="F379" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G379" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 06</t>
-        </is>
-      </c>
-      <c r="H379" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I379" s="16" t="inlineStr">
+      <c r="H379" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I379" s="12" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
@@ -21180,7 +21378,7 @@
     <row r="380">
       <c r="A380" s="14" t="inlineStr">
         <is>
-          <t>T-34.3</t>
+          <t>T-34.1</t>
         </is>
       </c>
       <c r="B380" s="14" t="inlineStr">
@@ -21191,7 +21389,7 @@
       <c r="C380" s="14" t="inlineStr"/>
       <c r="D380" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar los endpoints de consulta y actualización</t>
+          <t xml:space="preserve">    Crear la tabla de módulos activos por empresa</t>
         </is>
       </c>
       <c r="E380" s="15" t="inlineStr"/>
@@ -21219,7 +21417,7 @@
     <row r="381">
       <c r="A381" s="16" t="inlineStr">
         <is>
-          <t>T-34.4</t>
+          <t>T-34.2</t>
         </is>
       </c>
       <c r="B381" s="16" t="inlineStr">
@@ -21230,7 +21428,7 @@
       <c r="C381" s="16" t="inlineStr"/>
       <c r="D381" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar la pantalla de configuración de módulos</t>
+          <t xml:space="preserve">    Definir el conjunto de módulos disponibles</t>
         </is>
       </c>
       <c r="E381" s="17" t="inlineStr"/>
@@ -21258,7 +21456,7 @@
     <row r="382">
       <c r="A382" s="14" t="inlineStr">
         <is>
-          <t>T-34.5</t>
+          <t>T-34.3</t>
         </is>
       </c>
       <c r="B382" s="14" t="inlineStr">
@@ -21269,7 +21467,7 @@
       <c r="C382" s="14" t="inlineStr"/>
       <c r="D382" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Mostrar en el menú sólo los módulos activos</t>
+          <t xml:space="preserve">    Programar los endpoints de consulta y actualización</t>
         </is>
       </c>
       <c r="E382" s="15" t="inlineStr"/>
@@ -21294,48 +21492,40 @@
         </is>
       </c>
     </row>
-    <row r="383" ht="26" customHeight="1">
-      <c r="A383" s="12" t="inlineStr">
-        <is>
-          <t>HU-35</t>
-        </is>
-      </c>
-      <c r="B383" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C383" s="12" t="inlineStr">
-        <is>
-          <t>Configuración de Módulos</t>
-        </is>
-      </c>
-      <c r="D383" s="12" t="inlineStr">
-        <is>
-          <t>Como sistema quiero rechazar los pedidos a módulos desactivados para que no se pueda entrar por fuera del menú.</t>
-        </is>
-      </c>
-      <c r="E383" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F383" s="13" t="inlineStr">
+    <row r="383">
+      <c r="A383" s="16" t="inlineStr">
+        <is>
+          <t>T-34.4</t>
+        </is>
+      </c>
+      <c r="B383" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C383" s="16" t="inlineStr"/>
+      <c r="D383" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar la pantalla de configuración de módulos</t>
+        </is>
+      </c>
+      <c r="E383" s="17" t="inlineStr"/>
+      <c r="F383" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G383" s="13" t="inlineStr">
+      <c r="G383" s="17" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H383" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I383" s="12" t="inlineStr">
+      <c r="H383" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I383" s="16" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
@@ -21344,7 +21534,7 @@
     <row r="384">
       <c r="A384" s="14" t="inlineStr">
         <is>
-          <t>T-35.1</t>
+          <t>T-34.5</t>
         </is>
       </c>
       <c r="B384" s="14" t="inlineStr">
@@ -21355,7 +21545,7 @@
       <c r="C384" s="14" t="inlineStr"/>
       <c r="D384" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar el middleware de módulo activo</t>
+          <t xml:space="preserve">    Mostrar en el menú sólo los módulos activos</t>
         </is>
       </c>
       <c r="E384" s="15" t="inlineStr"/>
@@ -21380,40 +21570,48 @@
         </is>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" s="16" t="inlineStr">
-        <is>
-          <t>T-35.2</t>
-        </is>
-      </c>
-      <c r="B385" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C385" s="16" t="inlineStr"/>
-      <c r="D385" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Aplicarlo a las rutas de movimientos y categorías</t>
-        </is>
-      </c>
-      <c r="E385" s="17" t="inlineStr"/>
-      <c r="F385" s="17" t="inlineStr">
+    <row r="385" ht="26" customHeight="1">
+      <c r="A385" s="12" t="inlineStr">
+        <is>
+          <t>HU-35</t>
+        </is>
+      </c>
+      <c r="B385" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C385" s="12" t="inlineStr">
+        <is>
+          <t>Configuración de Módulos</t>
+        </is>
+      </c>
+      <c r="D385" s="12" t="inlineStr">
+        <is>
+          <t>Como sistema quiero rechazar los pedidos a módulos desactivados para que no se pueda entrar por fuera del menú.</t>
+        </is>
+      </c>
+      <c r="E385" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F385" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G385" s="17" t="inlineStr">
+      <c r="G385" s="13" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H385" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I385" s="16" t="inlineStr">
+      <c r="H385" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I385" s="12" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
@@ -21422,7 +21620,7 @@
     <row r="386">
       <c r="A386" s="14" t="inlineStr">
         <is>
-          <t>T-35.3</t>
+          <t>T-35.1</t>
         </is>
       </c>
       <c r="B386" s="14" t="inlineStr">
@@ -21433,7 +21631,7 @@
       <c r="C386" s="14" t="inlineStr"/>
       <c r="D386" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Mostrar en pantalla un aviso claro cuando el módulo está apagado</t>
+          <t xml:space="preserve">    Programar el middleware de módulo activo</t>
         </is>
       </c>
       <c r="E386" s="15" t="inlineStr"/>
@@ -21461,7 +21659,7 @@
     <row r="387">
       <c r="A387" s="16" t="inlineStr">
         <is>
-          <t>T-35.4</t>
+          <t>T-35.2</t>
         </is>
       </c>
       <c r="B387" s="16" t="inlineStr">
@@ -21472,7 +21670,7 @@
       <c r="C387" s="16" t="inlineStr"/>
       <c r="D387" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Distinguir el aviso de módulo apagado del de falta de permiso</t>
+          <t xml:space="preserve">    Aplicarlo a las rutas de movimientos y categorías</t>
         </is>
       </c>
       <c r="E387" s="17" t="inlineStr"/>
@@ -21500,7 +21698,7 @@
     <row r="388">
       <c r="A388" s="14" t="inlineStr">
         <is>
-          <t>T-35.5</t>
+          <t>T-35.3</t>
         </is>
       </c>
       <c r="B388" s="14" t="inlineStr">
@@ -21511,7 +21709,7 @@
       <c r="C388" s="14" t="inlineStr"/>
       <c r="D388" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Probar el acceso con el módulo apagado</t>
+          <t xml:space="preserve">    Mostrar en pantalla un aviso claro cuando el módulo está apagado</t>
         </is>
       </c>
       <c r="E388" s="15" t="inlineStr"/>
@@ -21536,48 +21734,40 @@
         </is>
       </c>
     </row>
-    <row r="389" ht="26" customHeight="1">
-      <c r="A389" s="12" t="inlineStr">
-        <is>
-          <t>HU-36</t>
-        </is>
-      </c>
-      <c r="B389" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C389" s="12" t="inlineStr">
-        <is>
-          <t>Configuración de Módulos</t>
-        </is>
-      </c>
-      <c r="D389" s="12" t="inlineStr">
-        <is>
-          <t>Como empresa nueva quiero empezar con una configuración razonable para no tener que definir todo antes de usar el sistema.</t>
-        </is>
-      </c>
-      <c r="E389" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F389" s="13" t="inlineStr">
+    <row r="389">
+      <c r="A389" s="16" t="inlineStr">
+        <is>
+          <t>T-35.4</t>
+        </is>
+      </c>
+      <c r="B389" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C389" s="16" t="inlineStr"/>
+      <c r="D389" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Distinguir el aviso de módulo apagado del de falta de permiso</t>
+        </is>
+      </c>
+      <c r="E389" s="17" t="inlineStr"/>
+      <c r="F389" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G389" s="13" t="inlineStr">
+      <c r="G389" s="17" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H389" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I389" s="12" t="inlineStr">
+      <c r="H389" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I389" s="16" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
@@ -21586,7 +21776,7 @@
     <row r="390">
       <c r="A390" s="14" t="inlineStr">
         <is>
-          <t>T-36.1</t>
+          <t>T-35.5</t>
         </is>
       </c>
       <c r="B390" s="14" t="inlineStr">
@@ -21597,7 +21787,7 @@
       <c r="C390" s="14" t="inlineStr"/>
       <c r="D390" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el conjunto de módulos y categorías iniciales</t>
+          <t xml:space="preserve">    Probar el acceso con el módulo apagado</t>
         </is>
       </c>
       <c r="E390" s="15" t="inlineStr"/>
@@ -21622,40 +21812,48 @@
         </is>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" s="16" t="inlineStr">
-        <is>
-          <t>T-36.2</t>
-        </is>
-      </c>
-      <c r="B391" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C391" s="16" t="inlineStr"/>
-      <c r="D391" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar la carga automática al aprobar la empresa</t>
-        </is>
-      </c>
-      <c r="E391" s="17" t="inlineStr"/>
-      <c r="F391" s="17" t="inlineStr">
+    <row r="391" ht="26" customHeight="1">
+      <c r="A391" s="12" t="inlineStr">
+        <is>
+          <t>HU-36</t>
+        </is>
+      </c>
+      <c r="B391" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C391" s="12" t="inlineStr">
+        <is>
+          <t>Configuración de Módulos</t>
+        </is>
+      </c>
+      <c r="D391" s="12" t="inlineStr">
+        <is>
+          <t>Como empresa nueva quiero empezar con una configuración razonable para no tener que definir todo antes de usar el sistema.</t>
+        </is>
+      </c>
+      <c r="E391" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F391" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G391" s="17" t="inlineStr">
+      <c r="G391" s="13" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H391" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I391" s="16" t="inlineStr">
+      <c r="H391" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I391" s="12" t="inlineStr">
         <is>
           <t>Equipo</t>
         </is>
@@ -21664,7 +21862,7 @@
     <row r="392">
       <c r="A392" s="14" t="inlineStr">
         <is>
-          <t>T-36.3</t>
+          <t>T-36.1</t>
         </is>
       </c>
       <c r="B392" s="14" t="inlineStr">
@@ -21675,7 +21873,7 @@
       <c r="C392" s="14" t="inlineStr"/>
       <c r="D392" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Dejar la configuración escrita en la base, no deducida del catálogo</t>
+          <t xml:space="preserve">    Definir el conjunto de módulos y categorías iniciales</t>
         </is>
       </c>
       <c r="E392" s="15" t="inlineStr"/>
@@ -21703,7 +21901,7 @@
     <row r="393">
       <c r="A393" s="16" t="inlineStr">
         <is>
-          <t>T-36.4</t>
+          <t>T-36.2</t>
         </is>
       </c>
       <c r="B393" s="16" t="inlineStr">
@@ -21714,7 +21912,7 @@
       <c r="C393" s="16" t="inlineStr"/>
       <c r="D393" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Evitar que una segunda aprobación duplique o pise lo ya configurado</t>
+          <t xml:space="preserve">    Programar la carga automática al aprobar la empresa</t>
         </is>
       </c>
       <c r="E393" s="17" t="inlineStr"/>
@@ -21742,7 +21940,7 @@
     <row r="394">
       <c r="A394" s="14" t="inlineStr">
         <is>
-          <t>T-36.5</t>
+          <t>T-36.3</t>
         </is>
       </c>
       <c r="B394" s="14" t="inlineStr">
@@ -21753,7 +21951,7 @@
       <c r="C394" s="14" t="inlineStr"/>
       <c r="D394" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Probar el alta de una empresa nueva de punta a punta</t>
+          <t xml:space="preserve">    Dejar la configuración escrita en la base, no deducida del catálogo</t>
         </is>
       </c>
       <c r="E394" s="15" t="inlineStr"/>
@@ -21778,154 +21976,166 @@
         </is>
       </c>
     </row>
-    <row r="395" ht="20" customHeight="1">
-      <c r="A395" s="9" t="inlineStr">
+    <row r="395">
+      <c r="A395" s="16" t="inlineStr">
+        <is>
+          <t>T-36.4</t>
+        </is>
+      </c>
+      <c r="B395" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C395" s="16" t="inlineStr"/>
+      <c r="D395" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Evitar que una segunda aprobación duplique o pise lo ya configurado</t>
+        </is>
+      </c>
+      <c r="E395" s="17" t="inlineStr"/>
+      <c r="F395" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G395" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H395" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I395" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="14" t="inlineStr">
+        <is>
+          <t>T-36.5</t>
+        </is>
+      </c>
+      <c r="B396" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C396" s="14" t="inlineStr"/>
+      <c r="D396" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Probar el alta de una empresa nueva de punta a punta</t>
+        </is>
+      </c>
+      <c r="E396" s="15" t="inlineStr"/>
+      <c r="F396" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G396" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 06</t>
+        </is>
+      </c>
+      <c r="H396" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I396" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="20" customHeight="1">
+      <c r="A397" s="9" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B395" s="9" t="inlineStr">
+      <c r="B397" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C395" s="9" t="inlineStr">
+      <c r="C397" s="9" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D395" s="9" t="inlineStr">
+      <c r="D397" s="9" t="inlineStr">
         <is>
           <t>Catálogo de servicios que generan ingreso o egreso</t>
         </is>
       </c>
-      <c r="E395" s="10" t="inlineStr">
+      <c r="E397" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F395" s="11" t="n"/>
-      <c r="G395" s="11" t="n"/>
-      <c r="H395" s="11" t="n"/>
-      <c r="I395" s="11" t="n"/>
-    </row>
-    <row r="396" ht="26" customHeight="1">
-      <c r="A396" s="12" t="inlineStr">
+      <c r="F397" s="11" t="n"/>
+      <c r="G397" s="11" t="n"/>
+      <c r="H397" s="11" t="n"/>
+      <c r="I397" s="11" t="n"/>
+    </row>
+    <row r="398" ht="26" customHeight="1">
+      <c r="A398" s="12" t="inlineStr">
         <is>
           <t>HU-47</t>
         </is>
       </c>
-      <c r="B396" s="12" t="inlineStr">
+      <c r="B398" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C396" s="12" t="inlineStr">
+      <c r="C398" s="12" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D396" s="12" t="inlineStr">
+      <c r="D398" s="12" t="inlineStr">
         <is>
           <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
         </is>
       </c>
-      <c r="E396" s="13" t="inlineStr">
+      <c r="E398" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F396" s="13" t="inlineStr">
+      <c r="F398" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G396" s="13" t="inlineStr">
+      <c r="G398" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H396" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I396" s="12" t="inlineStr"/>
-    </row>
-    <row r="397">
-      <c r="A397" s="14" t="inlineStr">
-        <is>
-          <t>T-47.1</t>
-        </is>
-      </c>
-      <c r="B397" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C397" s="14" t="inlineStr"/>
-      <c r="D397" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Reutilizar el modelo de productos agregando la distinción de servicio</t>
-        </is>
-      </c>
-      <c r="E397" s="15" t="inlineStr"/>
-      <c r="F397" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G397" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H397" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I397" s="14" t="inlineStr"/>
-    </row>
-    <row r="398">
-      <c r="A398" s="16" t="inlineStr">
-        <is>
-          <t>T-47.2</t>
-        </is>
-      </c>
-      <c r="B398" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C398" s="16" t="inlineStr"/>
-      <c r="D398" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el alta, la edición y la baja lógica</t>
-        </is>
-      </c>
-      <c r="E398" s="17" t="inlineStr"/>
-      <c r="F398" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G398" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H398" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I398" s="16" t="inlineStr"/>
+      <c r="H398" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I398" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="14" t="inlineStr">
         <is>
-          <t>T-47.3</t>
+          <t>T-47.1</t>
         </is>
       </c>
       <c r="B399" s="14" t="inlineStr">
@@ -21936,7 +22146,7 @@
       <c r="C399" s="14" t="inlineStr"/>
       <c r="D399" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar la pantalla de servicios</t>
+          <t xml:space="preserve">    Reutilizar el modelo de productos agregando la distinción de servicio</t>
         </is>
       </c>
       <c r="E399" s="15" t="inlineStr"/>
@@ -21952,15 +22162,19 @@
       </c>
       <c r="H399" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I399" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I399" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="16" t="inlineStr">
         <is>
-          <t>T-47.4</t>
+          <t>T-47.2</t>
         </is>
       </c>
       <c r="B400" s="16" t="inlineStr">
@@ -21971,7 +22185,7 @@
       <c r="C400" s="16" t="inlineStr"/>
       <c r="D400" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Verificar que los servicios no lleven existencias</t>
+          <t xml:space="preserve">    Programar el alta, la edición y la baja lógica</t>
         </is>
       </c>
       <c r="E400" s="17" t="inlineStr"/>
@@ -21987,128 +22201,140 @@
       </c>
       <c r="H400" s="16" t="inlineStr">
         <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I400" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="14" t="inlineStr">
+        <is>
+          <t>T-47.3</t>
+        </is>
+      </c>
+      <c r="B401" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C401" s="14" t="inlineStr"/>
+      <c r="D401" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar la pantalla de servicios</t>
+        </is>
+      </c>
+      <c r="E401" s="15" t="inlineStr"/>
+      <c r="F401" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G401" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H401" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I401" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="16" t="inlineStr">
+        <is>
+          <t>T-47.4</t>
+        </is>
+      </c>
+      <c r="B402" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C402" s="16" t="inlineStr"/>
+      <c r="D402" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Verificar que los servicios no lleven existencias</t>
+        </is>
+      </c>
+      <c r="E402" s="17" t="inlineStr"/>
+      <c r="F402" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G402" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H402" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I402" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="26" customHeight="1">
+      <c r="A403" s="12" t="inlineStr">
+        <is>
+          <t>HU-48</t>
+        </is>
+      </c>
+      <c r="B403" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C403" s="12" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D403" s="12" t="inlineStr">
+        <is>
+          <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
+        </is>
+      </c>
+      <c r="E403" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F403" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G403" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H403" s="12" t="inlineStr">
+        <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I400" s="16" t="inlineStr"/>
-    </row>
-    <row r="401" ht="26" customHeight="1">
-      <c r="A401" s="12" t="inlineStr">
-        <is>
-          <t>HU-48</t>
-        </is>
-      </c>
-      <c r="B401" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C401" s="12" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D401" s="12" t="inlineStr">
-        <is>
-          <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
-        </is>
-      </c>
-      <c r="E401" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F401" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G401" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H401" s="12" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I401" s="12" t="inlineStr"/>
-    </row>
-    <row r="402">
-      <c r="A402" s="14" t="inlineStr">
-        <is>
-          <t>T-48.1</t>
-        </is>
-      </c>
-      <c r="B402" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C402" s="14" t="inlineStr"/>
-      <c r="D402" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Vincular el movimiento económico con el servicio</t>
-        </is>
-      </c>
-      <c r="E402" s="15" t="inlineStr"/>
-      <c r="F402" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G402" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H402" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I402" s="14" t="inlineStr"/>
-    </row>
-    <row r="403">
-      <c r="A403" s="16" t="inlineStr">
-        <is>
-          <t>T-48.2</t>
-        </is>
-      </c>
-      <c r="B403" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C403" s="16" t="inlineStr"/>
-      <c r="D403" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agregar el servicio al formulario de movimiento</t>
-        </is>
-      </c>
-      <c r="E403" s="17" t="inlineStr"/>
-      <c r="F403" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G403" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 09</t>
-        </is>
-      </c>
-      <c r="H403" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I403" s="16" t="inlineStr"/>
+      <c r="I403" s="12" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="14" t="inlineStr">
         <is>
-          <t>T-48.3</t>
+          <t>T-48.1</t>
         </is>
       </c>
       <c r="B404" s="14" t="inlineStr">
@@ -22119,7 +22345,7 @@
       <c r="C404" s="14" t="inlineStr"/>
       <c r="D404" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Agregar el filtro por servicio en el listado</t>
+          <t xml:space="preserve">    Vincular el movimiento económico con el servicio</t>
         </is>
       </c>
       <c r="E404" s="15" t="inlineStr"/>
@@ -22140,53 +22366,45 @@
       </c>
       <c r="I404" s="14" t="inlineStr"/>
     </row>
-    <row r="405" ht="16" customHeight="1">
-      <c r="A405" s="12" t="inlineStr">
-        <is>
-          <t>HU-49</t>
-        </is>
-      </c>
-      <c r="B405" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C405" s="12" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="D405" s="12" t="inlineStr">
-        <is>
-          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
-        </is>
-      </c>
-      <c r="E405" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F405" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G405" s="13" t="inlineStr">
+    <row r="405">
+      <c r="A405" s="16" t="inlineStr">
+        <is>
+          <t>T-48.2</t>
+        </is>
+      </c>
+      <c r="B405" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C405" s="16" t="inlineStr"/>
+      <c r="D405" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agregar el servicio al formulario de movimiento</t>
+        </is>
+      </c>
+      <c r="E405" s="17" t="inlineStr"/>
+      <c r="F405" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G405" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H405" s="12" t="inlineStr">
+      <c r="H405" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I405" s="12" t="inlineStr"/>
+      <c r="I405" s="16" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="14" t="inlineStr">
         <is>
-          <t>T-49.1</t>
+          <t>T-48.3</t>
         </is>
       </c>
       <c r="B406" s="14" t="inlineStr">
@@ -22197,210 +22415,218 @@
       <c r="C406" s="14" t="inlineStr"/>
       <c r="D406" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar la consulta agrupada por servicio</t>
+          <t xml:space="preserve">    Agregar el filtro por servicio en el listado</t>
         </is>
       </c>
       <c r="E406" s="15" t="inlineStr"/>
       <c r="F406" s="15" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G406" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H406" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I406" s="14" t="inlineStr"/>
+    </row>
+    <row r="407" ht="16" customHeight="1">
+      <c r="A407" s="12" t="inlineStr">
+        <is>
+          <t>HU-49</t>
+        </is>
+      </c>
+      <c r="B407" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C407" s="12" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="D407" s="12" t="inlineStr">
+        <is>
+          <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
+        </is>
+      </c>
+      <c r="E407" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F407" s="13" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G406" s="15" t="inlineStr">
+      <c r="G407" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H406" s="14" t="inlineStr">
+      <c r="H407" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I406" s="14" t="inlineStr"/>
-    </row>
-    <row r="407">
-      <c r="A407" s="16" t="inlineStr">
+      <c r="I407" s="12" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="14" t="inlineStr">
+        <is>
+          <t>T-49.1</t>
+        </is>
+      </c>
+      <c r="B408" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C408" s="14" t="inlineStr"/>
+      <c r="D408" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar la consulta agrupada por servicio</t>
+        </is>
+      </c>
+      <c r="E408" s="15" t="inlineStr"/>
+      <c r="F408" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G408" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 09</t>
+        </is>
+      </c>
+      <c r="H408" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I408" s="14" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="16" t="inlineStr">
         <is>
           <t>T-49.2</t>
         </is>
       </c>
-      <c r="B407" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C407" s="16" t="inlineStr"/>
-      <c r="D407" s="16" t="inlineStr">
+      <c r="B409" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C409" s="16" t="inlineStr"/>
+      <c r="D409" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar la visualización del resumen</t>
         </is>
       </c>
-      <c r="E407" s="17" t="inlineStr"/>
-      <c r="F407" s="17" t="inlineStr">
+      <c r="E409" s="17" t="inlineStr"/>
+      <c r="F409" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G407" s="17" t="inlineStr">
+      <c r="G409" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H407" s="16" t="inlineStr">
+      <c r="H409" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I407" s="16" t="inlineStr"/>
-    </row>
-    <row r="408" ht="20" customHeight="1">
-      <c r="A408" s="9" t="inlineStr">
+      <c r="I409" s="16" t="inlineStr"/>
+    </row>
+    <row r="410" ht="20" customHeight="1">
+      <c r="A410" s="9" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B408" s="9" t="inlineStr">
+      <c r="B410" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C408" s="9" t="inlineStr">
+      <c r="C410" s="9" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D408" s="9" t="inlineStr">
+      <c r="D410" s="9" t="inlineStr">
         <is>
           <t>Vacaciones, licencias y documentación del personal (backlog futuro)</t>
         </is>
       </c>
-      <c r="E408" s="10" t="inlineStr">
+      <c r="E410" s="10" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F408" s="11" t="n"/>
-      <c r="G408" s="11" t="n"/>
-      <c r="H408" s="11" t="n"/>
-      <c r="I408" s="11" t="n"/>
-    </row>
-    <row r="409" ht="16" customHeight="1">
-      <c r="A409" s="12" t="inlineStr">
+      <c r="F410" s="11" t="n"/>
+      <c r="G410" s="11" t="n"/>
+      <c r="H410" s="11" t="n"/>
+      <c r="I410" s="11" t="n"/>
+    </row>
+    <row r="411" ht="16" customHeight="1">
+      <c r="A411" s="12" t="inlineStr">
         <is>
           <t>HU-68</t>
         </is>
       </c>
-      <c r="B409" s="12" t="inlineStr">
+      <c r="B411" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C409" s="12" t="inlineStr">
+      <c r="C411" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D409" s="12" t="inlineStr">
+      <c r="D411" s="12" t="inlineStr">
         <is>
           <t>Como empleado quiero solicitar días de vacaciones para gestionarlos sin papeles.</t>
         </is>
       </c>
-      <c r="E409" s="13" t="inlineStr">
+      <c r="E411" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F409" s="13" t="inlineStr">
+      <c r="F411" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G409" s="13" t="inlineStr">
+      <c r="G411" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H409" s="12" t="inlineStr">
+      <c r="H411" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I409" s="12" t="inlineStr"/>
-    </row>
-    <row r="410">
-      <c r="A410" s="14" t="inlineStr">
-        <is>
-          <t>T-68.1</t>
-        </is>
-      </c>
-      <c r="B410" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C410" s="14" t="inlineStr"/>
-      <c r="D410" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Diseñar el modelo de licencias y saldo de días</t>
-        </is>
-      </c>
-      <c r="E410" s="15" t="inlineStr"/>
-      <c r="F410" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G410" s="15" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H410" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I410" s="14" t="inlineStr"/>
-    </row>
-    <row r="411">
-      <c r="A411" s="16" t="inlineStr">
-        <is>
-          <t>T-68.2</t>
-        </is>
-      </c>
-      <c r="B411" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C411" s="16" t="inlineStr"/>
-      <c r="D411" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar el circuito de solicitud y aprobación</t>
-        </is>
-      </c>
-      <c r="E411" s="17" t="inlineStr"/>
-      <c r="F411" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G411" s="17" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H411" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I411" s="16" t="inlineStr"/>
+      <c r="I411" s="12" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="14" t="inlineStr">
         <is>
-          <t>T-68.3</t>
+          <t>T-68.1</t>
         </is>
       </c>
       <c r="B412" s="14" t="inlineStr">
@@ -22411,7 +22637,7 @@
       <c r="C412" s="14" t="inlineStr"/>
       <c r="D412" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Diseñar las pantallas de solicitud y de bandeja del responsable</t>
+          <t xml:space="preserve">    Diseñar el modelo de licencias y saldo de días</t>
         </is>
       </c>
       <c r="E412" s="15" t="inlineStr"/>
@@ -22435,7 +22661,7 @@
     <row r="413">
       <c r="A413" s="16" t="inlineStr">
         <is>
-          <t>T-68.4</t>
+          <t>T-68.2</t>
         </is>
       </c>
       <c r="B413" s="16" t="inlineStr">
@@ -22446,7 +22672,7 @@
       <c r="C413" s="16" t="inlineStr"/>
       <c r="D413" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Programar el cálculo del saldo de días</t>
+          <t xml:space="preserve">    Programar el circuito de solicitud y aprobación</t>
         </is>
       </c>
       <c r="E413" s="17" t="inlineStr"/>
@@ -22467,123 +22693,123 @@
       </c>
       <c r="I413" s="16" t="inlineStr"/>
     </row>
-    <row r="414" ht="16" customHeight="1">
-      <c r="A414" s="12" t="inlineStr">
+    <row r="414">
+      <c r="A414" s="14" t="inlineStr">
+        <is>
+          <t>T-68.3</t>
+        </is>
+      </c>
+      <c r="B414" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C414" s="14" t="inlineStr"/>
+      <c r="D414" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Diseñar las pantallas de solicitud y de bandeja del responsable</t>
+        </is>
+      </c>
+      <c r="E414" s="15" t="inlineStr"/>
+      <c r="F414" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G414" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H414" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I414" s="14" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="16" t="inlineStr">
+        <is>
+          <t>T-68.4</t>
+        </is>
+      </c>
+      <c r="B415" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C415" s="16" t="inlineStr"/>
+      <c r="D415" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Programar el cálculo del saldo de días</t>
+        </is>
+      </c>
+      <c r="E415" s="17" t="inlineStr"/>
+      <c r="F415" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G415" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H415" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I415" s="16" t="inlineStr"/>
+    </row>
+    <row r="416" ht="16" customHeight="1">
+      <c r="A416" s="12" t="inlineStr">
         <is>
           <t>HU-69</t>
         </is>
       </c>
-      <c r="B414" s="12" t="inlineStr">
+      <c r="B416" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C414" s="12" t="inlineStr">
+      <c r="C416" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D414" s="12" t="inlineStr">
+      <c r="D416" s="12" t="inlineStr">
         <is>
           <t>Como empleado quiero subir mi orden médica para justificar una ausencia.</t>
         </is>
       </c>
-      <c r="E414" s="13" t="inlineStr">
+      <c r="E416" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F414" s="13" t="inlineStr">
+      <c r="F416" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G414" s="13" t="inlineStr">
+      <c r="G416" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H414" s="12" t="inlineStr">
+      <c r="H416" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I414" s="12" t="inlineStr"/>
-    </row>
-    <row r="415">
-      <c r="A415" s="14" t="inlineStr">
-        <is>
-          <t>T-69.1</t>
-        </is>
-      </c>
-      <c r="B415" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C415" s="14" t="inlineStr"/>
-      <c r="D415" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Definir el almacenamiento local de archivos adjuntos</t>
-        </is>
-      </c>
-      <c r="E415" s="15" t="inlineStr"/>
-      <c r="F415" s="15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G415" s="15" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H415" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I415" s="14" t="inlineStr"/>
-    </row>
-    <row r="416">
-      <c r="A416" s="16" t="inlineStr">
-        <is>
-          <t>T-69.2</t>
-        </is>
-      </c>
-      <c r="B416" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C416" s="16" t="inlineStr"/>
-      <c r="D416" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Programar la subida con validación de tipo y tamaño</t>
-        </is>
-      </c>
-      <c r="E416" s="17" t="inlineStr"/>
-      <c r="F416" s="17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G416" s="17" t="inlineStr">
-        <is>
-          <t>Sin asignar</t>
-        </is>
-      </c>
-      <c r="H416" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I416" s="16" t="inlineStr"/>
+      <c r="I416" s="12" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="14" t="inlineStr">
         <is>
-          <t>T-69.3</t>
+          <t>T-69.1</t>
         </is>
       </c>
       <c r="B417" s="14" t="inlineStr">
@@ -22594,7 +22820,7 @@
       <c r="C417" s="14" t="inlineStr"/>
       <c r="D417" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Restringir la visibilidad del archivo</t>
+          <t xml:space="preserve">    Definir el almacenamiento local de archivos adjuntos</t>
         </is>
       </c>
       <c r="E417" s="15" t="inlineStr"/>
@@ -22618,7 +22844,7 @@
     <row r="418">
       <c r="A418" s="16" t="inlineStr">
         <is>
-          <t>T-69.4</t>
+          <t>T-69.2</t>
         </is>
       </c>
       <c r="B418" s="16" t="inlineStr">
@@ -22629,7 +22855,7 @@
       <c r="C418" s="16" t="inlineStr"/>
       <c r="D418" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Definir el tratamiento de los datos de salud</t>
+          <t xml:space="preserve">    Programar la subida con validación de tipo y tamaño</t>
         </is>
       </c>
       <c r="E418" s="17" t="inlineStr"/>
@@ -22650,126 +22876,196 @@
       </c>
       <c r="I418" s="16" t="inlineStr"/>
     </row>
-    <row r="419" ht="16" customHeight="1">
-      <c r="A419" s="12" t="inlineStr">
+    <row r="419">
+      <c r="A419" s="14" t="inlineStr">
+        <is>
+          <t>T-69.3</t>
+        </is>
+      </c>
+      <c r="B419" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C419" s="14" t="inlineStr"/>
+      <c r="D419" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Restringir la visibilidad del archivo</t>
+        </is>
+      </c>
+      <c r="E419" s="15" t="inlineStr"/>
+      <c r="F419" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G419" s="15" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H419" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I419" s="14" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="16" t="inlineStr">
+        <is>
+          <t>T-69.4</t>
+        </is>
+      </c>
+      <c r="B420" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C420" s="16" t="inlineStr"/>
+      <c r="D420" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Definir el tratamiento de los datos de salud</t>
+        </is>
+      </c>
+      <c r="E420" s="17" t="inlineStr"/>
+      <c r="F420" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G420" s="17" t="inlineStr">
+        <is>
+          <t>Sin asignar</t>
+        </is>
+      </c>
+      <c r="H420" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I420" s="16" t="inlineStr"/>
+    </row>
+    <row r="421" ht="16" customHeight="1">
+      <c r="A421" s="12" t="inlineStr">
         <is>
           <t>HU-70</t>
         </is>
       </c>
-      <c r="B419" s="12" t="inlineStr">
+      <c r="B421" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C419" s="12" t="inlineStr">
+      <c r="C421" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D419" s="12" t="inlineStr">
+      <c r="D421" s="12" t="inlineStr">
         <is>
           <t>Como área de personal quiero ver el calendario de ausencias para organizar la cobertura.</t>
         </is>
       </c>
-      <c r="E419" s="13" t="inlineStr">
+      <c r="E421" s="13" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F419" s="13" t="inlineStr">
+      <c r="F421" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G419" s="13" t="inlineStr">
+      <c r="G421" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H419" s="12" t="inlineStr">
+      <c r="H421" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I419" s="12" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" s="14" t="inlineStr">
+      <c r="I421" s="12" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="14" t="inlineStr">
         <is>
           <t>T-70.1</t>
         </is>
       </c>
-      <c r="B420" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C420" s="14" t="inlineStr"/>
-      <c r="D420" s="14" t="inlineStr">
+      <c r="B422" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C422" s="14" t="inlineStr"/>
+      <c r="D422" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar el calendario de ausencias</t>
         </is>
       </c>
-      <c r="E420" s="15" t="inlineStr"/>
-      <c r="F420" s="15" t="inlineStr">
+      <c r="E422" s="15" t="inlineStr"/>
+      <c r="F422" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G420" s="15" t="inlineStr">
+      <c r="G422" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H420" s="14" t="inlineStr">
+      <c r="H422" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I420" s="14" t="inlineStr"/>
-    </row>
-    <row r="421">
-      <c r="A421" s="16" t="inlineStr">
+      <c r="I422" s="14" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="16" t="inlineStr">
         <is>
           <t>T-70.2</t>
         </is>
       </c>
-      <c r="B421" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C421" s="16" t="inlineStr"/>
-      <c r="D421" s="16" t="inlineStr">
+      <c r="B423" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C423" s="16" t="inlineStr"/>
+      <c r="D423" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar la consulta por período</t>
         </is>
       </c>
-      <c r="E421" s="17" t="inlineStr"/>
-      <c r="F421" s="17" t="inlineStr">
+      <c r="E423" s="17" t="inlineStr"/>
+      <c r="F423" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G421" s="17" t="inlineStr">
+      <c r="G423" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H421" s="16" t="inlineStr">
+      <c r="H423" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I421" s="16" t="inlineStr"/>
+      <c r="I423" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I421"/>
+  <autoFilter ref="A4:I423"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H421">
+  <conditionalFormatting sqref="H5:H423">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -22784,13 +23080,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H5:H421" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H423" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E421" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E423" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I421" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I423" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23203,11 +23499,11 @@
         <v>9</v>
       </c>
       <c r="E13" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 09'!A6:A50,2)="T-")*1)</f>
+        <f>SUMPRODUCT((LEFT('Sprint 09'!A6:A52,2)="T-")*1)</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 09'!A6:A50,2)="T-")*('Sprint 09'!E6:E50="Hecho"))</f>
+        <f>SUMPRODUCT((LEFT('Sprint 09'!A6:A52,2)="T-")*('Sprint 09'!E6:E52="Hecho"))</f>
         <v/>
       </c>
       <c r="G13" s="18">

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -3099,10 +3099,14 @@
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr"/>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E42" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3118,10 +3122,14 @@
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr"/>
-      <c r="D43" s="14" t="inlineStr"/>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3137,10 +3145,14 @@
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr"/>
-      <c r="D44" s="16" t="inlineStr"/>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3156,10 +3168,14 @@
         </is>
       </c>
       <c r="C45" s="14" t="inlineStr"/>
-      <c r="D45" s="14" t="inlineStr"/>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -22326,10 +22342,14 @@
       </c>
       <c r="H403" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I403" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I403" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="14" t="inlineStr">
@@ -22361,10 +22381,14 @@
       </c>
       <c r="H404" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I404" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I404" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="16" t="inlineStr">
@@ -22396,10 +22420,14 @@
       </c>
       <c r="H405" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I405" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I405" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="14" t="inlineStr">
@@ -22431,10 +22459,14 @@
       </c>
       <c r="H406" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I406" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I406" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="407" ht="16" customHeight="1">
       <c r="A407" s="12" t="inlineStr">

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -3195,10 +3195,14 @@
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D46" s="23" t="inlineStr"/>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E46" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3214,10 +3218,14 @@
         </is>
       </c>
       <c r="C47" s="14" t="inlineStr"/>
-      <c r="D47" s="14" t="inlineStr"/>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3233,10 +3241,14 @@
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr"/>
-      <c r="D48" s="16" t="inlineStr"/>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -22506,10 +22518,14 @@
       </c>
       <c r="H407" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I407" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I407" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="14" t="inlineStr">
@@ -22541,10 +22557,14 @@
       </c>
       <c r="H408" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I408" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I408" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="16" t="inlineStr">
@@ -22576,10 +22596,14 @@
       </c>
       <c r="H409" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I409" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I409" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="410" ht="20" customHeight="1">
       <c r="A410" s="9" t="inlineStr">

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -4909,7 +4909,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Ofrecer entró/salió como dos botones en vez de un desplegable</t>
+          <t xml:space="preserve">     Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr"/>
@@ -4920,180 +4920,180 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>T-87.3</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="14" t="inlineStr"/>
-      <c r="E19" s="15" t="inlineStr">
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>HU-88</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr"/>
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>HU-88</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>T-88.1</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Separar el listado vacío del listado filtrado en los cuatro listados</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr"/>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>T-88.2</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr"/>
+      <c r="D21" s="16" t="inlineStr"/>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>T-88.3</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>HU-65</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr"/>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr"/>
+      <c r="E23" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>T-88.1</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Separar el listado vacío del listado filtrado en los cuatro listados</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="14" t="inlineStr"/>
-      <c r="E21" s="15" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>T-65.1</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Colapsar los filtros detrás de un botón en las pantallas de listado</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr"/>
+      <c r="D24" s="14" t="inlineStr"/>
+      <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>T-88.2</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr"/>
-      <c r="D22" s="16" t="inlineStr"/>
-      <c r="E22" s="17" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>T-65.2</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Revisar las pantallas de los módulos nuevos en ancho de celular</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr"/>
+      <c r="D25" s="16" t="inlineStr"/>
+      <c r="E25" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>T-88.3</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr"/>
-      <c r="D23" s="14" t="inlineStr"/>
-      <c r="E23" s="15" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>T-65.3</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Validar en Chrome y en un segundo navegador</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
+      <c r="D26" s="14" t="inlineStr"/>
+      <c r="E26" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>HU-65</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr"/>
-      <c r="E24" s="24" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>T-65.1</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Revisar las pantallas de los módulos nuevos en ancho de celular</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr"/>
-      <c r="D25" s="14" t="inlineStr"/>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>T-65.2</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Validar en Chrome y en un segundo navegador</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr"/>
-      <c r="D26" s="16" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>T-65.3</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>T-65.4</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Validar en un celular real</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr"/>
-      <c r="D27" s="14" t="inlineStr"/>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr"/>
+      <c r="D27" s="16" t="inlineStr"/>
+      <c r="E27" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
@@ -20463,7 +20463,7 @@
       <c r="C354" s="16" t="inlineStr"/>
       <c r="D354" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Ofrecer entró/salió como dos botones en vez de un desplegable</t>
+          <t xml:space="preserve">    Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
         </is>
       </c>
       <c r="E354" s="17" t="inlineStr"/>
@@ -20484,336 +20484,336 @@
       </c>
       <c r="I354" s="16" t="inlineStr"/>
     </row>
-    <row r="355">
-      <c r="A355" s="14" t="inlineStr">
-        <is>
-          <t>T-87.3</t>
-        </is>
-      </c>
-      <c r="B355" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C355" s="14" t="inlineStr"/>
-      <c r="D355" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
-        </is>
-      </c>
-      <c r="E355" s="15" t="inlineStr"/>
-      <c r="F355" s="15" t="inlineStr">
+    <row r="355" ht="26" customHeight="1">
+      <c r="A355" s="12" t="inlineStr">
+        <is>
+          <t>HU-88</t>
+        </is>
+      </c>
+      <c r="B355" s="12" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="C355" s="12" t="inlineStr">
+        <is>
+          <t>Calidad, UX y Documentación</t>
+        </is>
+      </c>
+      <c r="D355" s="12" t="inlineStr">
+        <is>
+          <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
+        </is>
+      </c>
+      <c r="E355" s="13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="F355" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G355" s="15" t="inlineStr">
+      <c r="G355" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H355" s="14" t="inlineStr">
+      <c r="H355" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I355" s="14" t="inlineStr"/>
-    </row>
-    <row r="356" ht="26" customHeight="1">
-      <c r="A356" s="12" t="inlineStr">
-        <is>
-          <t>HU-88</t>
-        </is>
-      </c>
-      <c r="B356" s="12" t="inlineStr">
+      <c r="I355" s="12" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="14" t="inlineStr">
+        <is>
+          <t>T-88.1</t>
+        </is>
+      </c>
+      <c r="B356" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C356" s="14" t="inlineStr"/>
+      <c r="D356" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Separar el listado vacío del listado filtrado en los cuatro listados</t>
+        </is>
+      </c>
+      <c r="E356" s="15" t="inlineStr"/>
+      <c r="F356" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G356" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H356" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I356" s="14" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="16" t="inlineStr">
+        <is>
+          <t>T-88.2</t>
+        </is>
+      </c>
+      <c r="B357" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C357" s="16" t="inlineStr"/>
+      <c r="D357" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
+        </is>
+      </c>
+      <c r="E357" s="17" t="inlineStr"/>
+      <c r="F357" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G357" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H357" s="16" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I357" s="16" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="14" t="inlineStr">
+        <is>
+          <t>T-88.3</t>
+        </is>
+      </c>
+      <c r="B358" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C358" s="14" t="inlineStr"/>
+      <c r="D358" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
+        </is>
+      </c>
+      <c r="E358" s="15" t="inlineStr"/>
+      <c r="F358" s="15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G358" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H358" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I358" s="14" t="inlineStr"/>
+    </row>
+    <row r="359" ht="16" customHeight="1">
+      <c r="A359" s="12" t="inlineStr">
+        <is>
+          <t>HU-65</t>
+        </is>
+      </c>
+      <c r="B359" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C356" s="12" t="inlineStr">
+      <c r="C359" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D356" s="12" t="inlineStr">
-        <is>
-          <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
-        </is>
-      </c>
-      <c r="E356" s="13" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F356" s="13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G356" s="13" t="inlineStr">
+      <c r="D359" s="12" t="inlineStr">
+        <is>
+          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
+        </is>
+      </c>
+      <c r="E359" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F359" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G359" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H356" s="12" t="inlineStr">
+      <c r="H359" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I356" s="12" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" s="14" t="inlineStr">
-        <is>
-          <t>T-88.1</t>
-        </is>
-      </c>
-      <c r="B357" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C357" s="14" t="inlineStr"/>
-      <c r="D357" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Separar el listado vacío del listado filtrado en los cuatro listados</t>
-        </is>
-      </c>
-      <c r="E357" s="15" t="inlineStr"/>
-      <c r="F357" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G357" s="15" t="inlineStr">
+      <c r="I359" s="12" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="14" t="inlineStr">
+        <is>
+          <t>T-65.1</t>
+        </is>
+      </c>
+      <c r="B360" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C360" s="14" t="inlineStr"/>
+      <c r="D360" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Colapsar los filtros detrás de un botón en las pantallas de listado</t>
+        </is>
+      </c>
+      <c r="E360" s="15" t="inlineStr"/>
+      <c r="F360" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G360" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H357" s="14" t="inlineStr">
+      <c r="H360" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I357" s="14" t="inlineStr"/>
-    </row>
-    <row r="358">
-      <c r="A358" s="16" t="inlineStr">
-        <is>
-          <t>T-88.2</t>
-        </is>
-      </c>
-      <c r="B358" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C358" s="16" t="inlineStr"/>
-      <c r="D358" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
-        </is>
-      </c>
-      <c r="E358" s="17" t="inlineStr"/>
-      <c r="F358" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G358" s="17" t="inlineStr">
+      <c r="I360" s="14" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="16" t="inlineStr">
+        <is>
+          <t>T-65.2</t>
+        </is>
+      </c>
+      <c r="B361" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C361" s="16" t="inlineStr"/>
+      <c r="D361" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revisar las pantallas de los módulos nuevos en ancho de celular</t>
+        </is>
+      </c>
+      <c r="E361" s="17" t="inlineStr"/>
+      <c r="F361" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G361" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H358" s="16" t="inlineStr">
+      <c r="H361" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I358" s="16" t="inlineStr"/>
-    </row>
-    <row r="359">
-      <c r="A359" s="14" t="inlineStr">
-        <is>
-          <t>T-88.3</t>
-        </is>
-      </c>
-      <c r="B359" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C359" s="14" t="inlineStr"/>
-      <c r="D359" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
-        </is>
-      </c>
-      <c r="E359" s="15" t="inlineStr"/>
-      <c r="F359" s="15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G359" s="15" t="inlineStr">
+      <c r="I361" s="16" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="14" t="inlineStr">
+        <is>
+          <t>T-65.3</t>
+        </is>
+      </c>
+      <c r="B362" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C362" s="14" t="inlineStr"/>
+      <c r="D362" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Validar en Chrome y en un segundo navegador</t>
+        </is>
+      </c>
+      <c r="E362" s="15" t="inlineStr"/>
+      <c r="F362" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G362" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H359" s="14" t="inlineStr">
+      <c r="H362" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I359" s="14" t="inlineStr"/>
-    </row>
-    <row r="360" ht="16" customHeight="1">
-      <c r="A360" s="12" t="inlineStr">
-        <is>
-          <t>HU-65</t>
-        </is>
-      </c>
-      <c r="B360" s="12" t="inlineStr">
-        <is>
-          <t>HU</t>
-        </is>
-      </c>
-      <c r="C360" s="12" t="inlineStr">
-        <is>
-          <t>Calidad, UX y Documentación</t>
-        </is>
-      </c>
-      <c r="D360" s="12" t="inlineStr">
-        <is>
-          <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
-        </is>
-      </c>
-      <c r="E360" s="13" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F360" s="13" t="inlineStr">
+      <c r="I362" s="14" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="16" t="inlineStr">
+        <is>
+          <t>T-65.4</t>
+        </is>
+      </c>
+      <c r="B363" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C363" s="16" t="inlineStr"/>
+      <c r="D363" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Validar en un celular real</t>
+        </is>
+      </c>
+      <c r="E363" s="17" t="inlineStr"/>
+      <c r="F363" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G360" s="13" t="inlineStr">
+      <c r="G363" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H360" s="12" t="inlineStr">
+      <c r="H363" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I360" s="12" t="inlineStr"/>
-    </row>
-    <row r="361">
-      <c r="A361" s="14" t="inlineStr">
-        <is>
-          <t>T-65.1</t>
-        </is>
-      </c>
-      <c r="B361" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C361" s="14" t="inlineStr"/>
-      <c r="D361" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Revisar las pantallas de los módulos nuevos en ancho de celular</t>
-        </is>
-      </c>
-      <c r="E361" s="15" t="inlineStr"/>
-      <c r="F361" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G361" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H361" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I361" s="14" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" s="16" t="inlineStr">
-        <is>
-          <t>T-65.2</t>
-        </is>
-      </c>
-      <c r="B362" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C362" s="16" t="inlineStr"/>
-      <c r="D362" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Validar en Chrome y en un segundo navegador</t>
-        </is>
-      </c>
-      <c r="E362" s="17" t="inlineStr"/>
-      <c r="F362" s="17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G362" s="17" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H362" s="16" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I362" s="16" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" s="14" t="inlineStr">
-        <is>
-          <t>T-65.3</t>
-        </is>
-      </c>
-      <c r="B363" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C363" s="14" t="inlineStr"/>
-      <c r="D363" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Validar en un celular real</t>
-        </is>
-      </c>
-      <c r="E363" s="15" t="inlineStr"/>
-      <c r="F363" s="15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G363" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 13</t>
-        </is>
-      </c>
-      <c r="H363" s="14" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I363" s="14" t="inlineStr"/>
+      <c r="I363" s="16" t="inlineStr"/>
     </row>
     <row r="364" ht="16" customHeight="1">
       <c r="A364" s="12" t="inlineStr">

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Léeme" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Product Backlog" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Seguimiento" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sprint 01" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sprint 02" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sprint 03" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sprint 04" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sprint 05" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Sprint 06" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Sprint 07" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Sprint 08" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sprint 09" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Sprint 10" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Sprint 11" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Sprint 12" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Sprint 13" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Incremento" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="DOD" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Cambios vs. original" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Product Backlog" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 01" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 02" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 03" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 04" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 05" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 06" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 07" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 08" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 09" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 10" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 11" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 12" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint 13" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Incremento" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOD" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cambios vs. original" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$423</definedName>
@@ -3464,10 +3464,14 @@
           <t>Reportes</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr"/>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3483,10 +3487,14 @@
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr"/>
-      <c r="D7" s="14" t="inlineStr"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3502,10 +3510,14 @@
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr"/>
-      <c r="D8" s="16" t="inlineStr"/>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3521,10 +3533,14 @@
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="14" t="inlineStr"/>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E9" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3540,10 +3556,14 @@
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr"/>
-      <c r="D10" s="16" t="inlineStr"/>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E10" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -14767,10 +14787,14 @@
       </c>
       <c r="H206" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I206" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I206" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="14" t="inlineStr">
@@ -14802,10 +14826,14 @@
       </c>
       <c r="H207" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I207" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I207" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="16" t="inlineStr">
@@ -14837,10 +14865,14 @@
       </c>
       <c r="H208" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I208" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I208" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="14" t="inlineStr">
@@ -14872,10 +14904,14 @@
       </c>
       <c r="H209" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I209" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I209" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="16" t="inlineStr">
@@ -14907,10 +14943,14 @@
       </c>
       <c r="H210" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I210" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I210" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="16" customHeight="1">
       <c r="A211" s="12" t="inlineStr">

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -3583,10 +3583,14 @@
           <t>Reportes</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr"/>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3602,10 +3606,14 @@
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E12" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3621,10 +3629,14 @@
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr"/>
-      <c r="D13" s="16" t="inlineStr"/>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3640,10 +3652,14 @@
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr"/>
-      <c r="D14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -14990,10 +15006,14 @@
       </c>
       <c r="H211" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I211" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I211" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="14" t="inlineStr">
@@ -15025,10 +15045,14 @@
       </c>
       <c r="H212" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I212" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I212" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="16" t="inlineStr">
@@ -15060,10 +15084,14 @@
       </c>
       <c r="H213" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I213" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I213" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="14" t="inlineStr">
@@ -15095,10 +15123,14 @@
       </c>
       <c r="H214" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I214" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I214" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="26" customHeight="1">
       <c r="A215" s="12" t="inlineStr">

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -3679,10 +3679,14 @@
           <t>Reportes</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr"/>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3698,10 +3702,14 @@
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr"/>
-      <c r="D16" s="14" t="inlineStr"/>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3717,10 +3725,14 @@
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr"/>
-      <c r="D17" s="16" t="inlineStr"/>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3736,10 +3748,14 @@
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr"/>
-      <c r="D18" s="14" t="inlineStr"/>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E18" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -15170,10 +15186,14 @@
       </c>
       <c r="H215" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I215" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I215" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="14" t="inlineStr">
@@ -15205,10 +15225,14 @@
       </c>
       <c r="H216" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I216" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I216" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="16" t="inlineStr">
@@ -15240,10 +15264,14 @@
       </c>
       <c r="H217" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I217" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I217" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="14" t="inlineStr">
@@ -15275,10 +15303,14 @@
       </c>
       <c r="H218" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I218" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I218" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="12" t="inlineStr">

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -3775,10 +3775,14 @@
           <t>Reportes</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr"/>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3794,10 +3798,14 @@
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr"/>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E20" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3813,10 +3821,14 @@
         </is>
       </c>
       <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="16" t="inlineStr"/>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3832,10 +3844,14 @@
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="14" t="inlineStr"/>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E22" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -15350,10 +15366,14 @@
       </c>
       <c r="H219" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I219" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I219" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="14" t="inlineStr">
@@ -15385,10 +15405,14 @@
       </c>
       <c r="H220" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I220" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I220" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="16" t="inlineStr">
@@ -15420,10 +15444,14 @@
       </c>
       <c r="H221" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I221" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I221" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="14" t="inlineStr">
@@ -15455,10 +15483,14 @@
       </c>
       <c r="H222" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I222" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I222" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="20" customHeight="1">
       <c r="A223" s="9" t="inlineStr">

--- a/Backlog_CooperApp_2026.xlsx
+++ b/Backlog_CooperApp_2026.xlsx
@@ -28,7 +28,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cambios vs. original" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$423</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Product Backlog'!$A$4:$I$424</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -928,7 +928,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Período: 21/09 al 27/09    |    Estado: En curso</t>
+          <t>Período: 21/09 al 27/09    |    Estado: Cerrado</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1451,7 +1451,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Período: 28/09 al 04/10    |    Estado: En curso</t>
+          <t>Período: 28/09 al 04/10    |    Estado: Cerrado</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2189,7 +2189,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Período: 05/10 al 11/10    |    Estado: Planificado</t>
+          <t>Período: 05/10 al 11/10    |    Estado: En curso</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3268,10 +3268,14 @@
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D49" s="23" t="inlineStr"/>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3291,14 @@
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr"/>
-      <c r="D50" s="14" t="inlineStr"/>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3306,10 +3314,14 @@
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr"/>
-      <c r="D51" s="16" t="inlineStr"/>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E51" s="17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3325,10 +3337,14 @@
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr"/>
-      <c r="D52" s="14" t="inlineStr"/>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Hecho</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3422,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Período: 12/10 al 18/10    |    Estado: Planificado</t>
+          <t>Período: 12/10 al 18/10    |    Estado: En curso</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -4663,7 +4679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4927,434 +4943,453 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>T-64.5</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Decidir con usuarios si el resultado por servicio vive en Movimientos o en Reportes</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr"/>
+      <c r="D16" s="14" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
         <is>
           <t>HU-87</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>Como tesorero quiero cargar un movimiento en menos pasos para no contestar tres preguntas encadenadas.</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr"/>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr"/>
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>T-87.1</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Reemplazar los tres desplegables encadenados por uno solo</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr"/>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr"/>
+      <c r="D18" s="14" t="inlineStr"/>
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>T-87.2</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr"/>
-      <c r="D18" s="16" t="inlineStr"/>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr"/>
+      <c r="D19" s="16" t="inlineStr"/>
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
         <is>
           <t>HU-88</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr"/>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr"/>
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>T-88.1</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Separar el listado vacío del listado filtrado en los cuatro listados</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr"/>
+      <c r="D21" s="14" t="inlineStr"/>
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>T-88.2</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr"/>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="C22" s="16" t="inlineStr"/>
+      <c r="D22" s="16" t="inlineStr"/>
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>T-88.3</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="14" t="inlineStr"/>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr"/>
+      <c r="D23" s="14" t="inlineStr"/>
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>HU-65</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr"/>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr"/>
+      <c r="E24" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>T-65.1</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Colapsar los filtros detrás de un botón en las pantallas de listado</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr"/>
-      <c r="D24" s="14" t="inlineStr"/>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr"/>
+      <c r="D25" s="14" t="inlineStr"/>
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>T-65.2</t>
         </is>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B26" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Revisar las pantallas de los módulos nuevos en ancho de celular</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr"/>
-      <c r="D25" s="16" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr"/>
+      <c r="D26" s="16" t="inlineStr"/>
+      <c r="E26" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>T-65.3</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Validar en Chrome y en un segundo navegador</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="14" t="inlineStr"/>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr"/>
+      <c r="D27" s="14" t="inlineStr"/>
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>T-65.4</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Validar en un celular real</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr"/>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="C28" s="16" t="inlineStr"/>
+      <c r="D28" s="16" t="inlineStr"/>
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="23" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>HU-66</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>Como equipo quiero dejar el proyecto documentado para poder continuarlo el año próximo.</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D28" s="23" t="inlineStr"/>
-      <c r="E28" s="24" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr"/>
+      <c r="E29" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>T-66.1</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Escribir el README con las instrucciones de instalación</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr"/>
-      <c r="D29" s="14" t="inlineStr"/>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr"/>
+      <c r="D30" s="14" t="inlineStr"/>
+      <c r="E30" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>T-66.2</t>
         </is>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Escribir el manual de usuario básico</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr"/>
-      <c r="D30" s="16" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="C31" s="16" t="inlineStr"/>
+      <c r="D31" s="16" t="inlineStr"/>
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>T-66.3</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Documentar el modelo de datos</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr"/>
-      <c r="D31" s="14" t="inlineStr"/>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr"/>
+      <c r="D32" s="14" t="inlineStr"/>
+      <c r="E32" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>T-66.4</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Documentar el diseño de los módulos que quedaron sin implementar</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr"/>
-      <c r="D32" s="16" t="inlineStr"/>
-      <c r="E32" s="17" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr"/>
+      <c r="D33" s="16" t="inlineStr"/>
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>HU-67</t>
         </is>
       </c>
-      <c r="B33" s="23" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>Como equipo quiero probar el sistema completo para entregar una versión estable.</t>
         </is>
       </c>
-      <c r="C33" s="23" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D33" s="23" t="inlineStr"/>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr"/>
+      <c r="E34" s="24" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>T-67.1</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Ejecutar la batería de pruebas de punta a punta</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr"/>
-      <c r="D34" s="14" t="inlineStr"/>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr"/>
+      <c r="D35" s="14" t="inlineStr"/>
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>T-67.2</t>
         </is>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">     Corregir los errores detectados</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr"/>
-      <c r="D35" s="16" t="inlineStr"/>
-      <c r="E35" s="17" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr"/>
+      <c r="D36" s="16" t="inlineStr"/>
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>T-67.3</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">     Unificar la carga del encabezado en un archivo compartido</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr"/>
-      <c r="D36" s="14" t="inlineStr"/>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr"/>
+      <c r="D37" s="14" t="inlineStr"/>
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="C38" s="19" t="inlineStr">
+    <row r="39">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>AVANCE DEL SPRINT (tareas terminadas)</t>
         </is>
       </c>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="20">
-        <f>TEXT(SUMPRODUCT((LEFT(A6:A36,2)="T-")*(E6:E36="Hecho"))/SUMPRODUCT((LEFT(A6:A36,2)="T-")*1),"0%")</f>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20">
+        <f>TEXT(SUMPRODUCT((LEFT(A6:A37,2)="T-")*(E6:E37="Hecho"))/SUMPRODUCT((LEFT(A6:A37,2)="T-")*1),"0%")</f>
         <v/>
       </c>
     </row>
@@ -5364,7 +5399,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E36">
+  <conditionalFormatting sqref="E6:E37">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -5379,10 +5414,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E6:E36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E6:E37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="D6:D36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6695,7 +6730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I423"/>
+  <dimension ref="A1:I424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19953,10 +19988,14 @@
       </c>
       <c r="H336" s="12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I336" s="12" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I336" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="14" t="inlineStr">
@@ -19988,10 +20027,14 @@
       </c>
       <c r="H337" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I337" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I337" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="16" t="inlineStr">
@@ -20023,10 +20066,14 @@
       </c>
       <c r="H338" s="16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I338" s="16" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I338" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="14" t="inlineStr">
@@ -20058,10 +20105,14 @@
       </c>
       <c r="H339" s="14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="I339" s="14" t="inlineStr"/>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I339" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
     </row>
     <row r="340" ht="16" customHeight="1">
       <c r="A340" s="12" t="inlineStr">
@@ -20507,2757 +20558,2792 @@
       </c>
       <c r="I351" s="16" t="inlineStr"/>
     </row>
-    <row r="352" ht="26" customHeight="1">
-      <c r="A352" s="12" t="inlineStr">
+    <row r="352">
+      <c r="A352" s="14" t="inlineStr">
+        <is>
+          <t>T-64.5</t>
+        </is>
+      </c>
+      <c r="B352" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C352" s="14" t="inlineStr"/>
+      <c r="D352" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Decidir con usuarios si el resultado por servicio vive en Movimientos o en Reportes</t>
+        </is>
+      </c>
+      <c r="E352" s="15" t="inlineStr"/>
+      <c r="F352" s="15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G352" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 13</t>
+        </is>
+      </c>
+      <c r="H352" s="14" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="I352" s="14" t="inlineStr"/>
+    </row>
+    <row r="353" ht="26" customHeight="1">
+      <c r="A353" s="12" t="inlineStr">
         <is>
           <t>HU-87</t>
         </is>
       </c>
-      <c r="B352" s="12" t="inlineStr">
+      <c r="B353" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C352" s="12" t="inlineStr">
+      <c r="C353" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D352" s="12" t="inlineStr">
+      <c r="D353" s="12" t="inlineStr">
         <is>
           <t>Como tesorero quiero cargar un movimiento en menos pasos para no contestar tres preguntas encadenadas.</t>
         </is>
       </c>
-      <c r="E352" s="13" t="inlineStr">
+      <c r="E353" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F352" s="13" t="inlineStr">
+      <c r="F353" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G352" s="13" t="inlineStr">
+      <c r="G353" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H352" s="12" t="inlineStr">
+      <c r="H353" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I352" s="12" t="inlineStr"/>
-    </row>
-    <row r="353">
-      <c r="A353" s="14" t="inlineStr">
+      <c r="I353" s="12" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="14" t="inlineStr">
         <is>
           <t>T-87.1</t>
         </is>
       </c>
-      <c r="B353" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C353" s="14" t="inlineStr"/>
-      <c r="D353" s="14" t="inlineStr">
+      <c r="B354" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C354" s="14" t="inlineStr"/>
+      <c r="D354" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Reemplazar los tres desplegables encadenados por uno solo</t>
         </is>
       </c>
-      <c r="E353" s="15" t="inlineStr"/>
-      <c r="F353" s="15" t="inlineStr">
+      <c r="E354" s="15" t="inlineStr"/>
+      <c r="F354" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G353" s="15" t="inlineStr">
+      <c r="G354" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H353" s="14" t="inlineStr">
+      <c r="H354" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I353" s="14" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" s="16" t="inlineStr">
+      <c r="I354" s="14" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="16" t="inlineStr">
         <is>
           <t>T-87.2</t>
         </is>
       </c>
-      <c r="B354" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C354" s="16" t="inlineStr"/>
-      <c r="D354" s="16" t="inlineStr">
+      <c r="B355" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C355" s="16" t="inlineStr"/>
+      <c r="D355" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Permitir corregir un movimiento anulado sin escribirlo de nuevo</t>
         </is>
       </c>
-      <c r="E354" s="17" t="inlineStr"/>
-      <c r="F354" s="17" t="inlineStr">
+      <c r="E355" s="17" t="inlineStr"/>
+      <c r="F355" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G354" s="17" t="inlineStr">
+      <c r="G355" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H354" s="16" t="inlineStr">
+      <c r="H355" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I354" s="16" t="inlineStr"/>
-    </row>
-    <row r="355" ht="26" customHeight="1">
-      <c r="A355" s="12" t="inlineStr">
+      <c r="I355" s="16" t="inlineStr"/>
+    </row>
+    <row r="356" ht="26" customHeight="1">
+      <c r="A356" s="12" t="inlineStr">
         <is>
           <t>HU-88</t>
         </is>
       </c>
-      <c r="B355" s="12" t="inlineStr">
+      <c r="B356" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C355" s="12" t="inlineStr">
+      <c r="C356" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D355" s="12" t="inlineStr">
+      <c r="D356" s="12" t="inlineStr">
         <is>
           <t>Como usuario quiero que las pantallas vacías me digan por dónde empezar en vez de culpar a un filtro que no toqué.</t>
         </is>
       </c>
-      <c r="E355" s="13" t="inlineStr">
+      <c r="E356" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F355" s="13" t="inlineStr">
+      <c r="F356" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G355" s="13" t="inlineStr">
+      <c r="G356" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H355" s="12" t="inlineStr">
+      <c r="H356" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I355" s="12" t="inlineStr"/>
-    </row>
-    <row r="356">
-      <c r="A356" s="14" t="inlineStr">
+      <c r="I356" s="12" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="14" t="inlineStr">
         <is>
           <t>T-88.1</t>
         </is>
       </c>
-      <c r="B356" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C356" s="14" t="inlineStr"/>
-      <c r="D356" s="14" t="inlineStr">
+      <c r="B357" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C357" s="14" t="inlineStr"/>
+      <c r="D357" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Separar el listado vacío del listado filtrado en los cuatro listados</t>
         </is>
       </c>
-      <c r="E356" s="15" t="inlineStr"/>
-      <c r="F356" s="15" t="inlineStr">
+      <c r="E357" s="15" t="inlineStr"/>
+      <c r="F357" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G356" s="15" t="inlineStr">
+      <c r="G357" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H356" s="14" t="inlineStr">
+      <c r="H357" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I356" s="14" t="inlineStr"/>
-    </row>
-    <row r="357">
-      <c r="A357" s="16" t="inlineStr">
+      <c r="I357" s="14" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="16" t="inlineStr">
         <is>
           <t>T-88.2</t>
         </is>
       </c>
-      <c r="B357" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C357" s="16" t="inlineStr"/>
-      <c r="D357" s="16" t="inlineStr">
+      <c r="B358" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C358" s="16" t="inlineStr"/>
+      <c r="D358" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Agregar un bloque de primeros pasos al panel de una empresa nueva</t>
         </is>
       </c>
-      <c r="E357" s="17" t="inlineStr"/>
-      <c r="F357" s="17" t="inlineStr">
+      <c r="E358" s="17" t="inlineStr"/>
+      <c r="F358" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G357" s="17" t="inlineStr">
+      <c r="G358" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H357" s="16" t="inlineStr">
+      <c r="H358" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I357" s="16" t="inlineStr"/>
-    </row>
-    <row r="358">
-      <c r="A358" s="14" t="inlineStr">
+      <c r="I358" s="16" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="14" t="inlineStr">
         <is>
           <t>T-88.3</t>
         </is>
       </c>
-      <c r="B358" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C358" s="14" t="inlineStr"/>
-      <c r="D358" s="14" t="inlineStr">
+      <c r="B359" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C359" s="14" t="inlineStr"/>
+      <c r="D359" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Poner 'Sin acceso' en los indicadores que el rol no puede ver</t>
         </is>
       </c>
-      <c r="E358" s="15" t="inlineStr"/>
-      <c r="F358" s="15" t="inlineStr">
+      <c r="E359" s="15" t="inlineStr"/>
+      <c r="F359" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G358" s="15" t="inlineStr">
+      <c r="G359" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H358" s="14" t="inlineStr">
+      <c r="H359" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I358" s="14" t="inlineStr"/>
-    </row>
-    <row r="359" ht="16" customHeight="1">
-      <c r="A359" s="12" t="inlineStr">
+      <c r="I359" s="14" t="inlineStr"/>
+    </row>
+    <row r="360" ht="16" customHeight="1">
+      <c r="A360" s="12" t="inlineStr">
         <is>
           <t>HU-65</t>
         </is>
       </c>
-      <c r="B359" s="12" t="inlineStr">
+      <c r="B360" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C359" s="12" t="inlineStr">
+      <c r="C360" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D359" s="12" t="inlineStr">
+      <c r="D360" s="12" t="inlineStr">
         <is>
           <t>Como usuario quiero usar todo el sistema desde el celular para trabajar donde estoy.</t>
         </is>
       </c>
-      <c r="E359" s="13" t="inlineStr">
+      <c r="E360" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F359" s="13" t="inlineStr">
+      <c r="F360" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G359" s="13" t="inlineStr">
+      <c r="G360" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H359" s="12" t="inlineStr">
+      <c r="H360" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I359" s="12" t="inlineStr"/>
-    </row>
-    <row r="360">
-      <c r="A360" s="14" t="inlineStr">
+      <c r="I360" s="12" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="14" t="inlineStr">
         <is>
           <t>T-65.1</t>
         </is>
       </c>
-      <c r="B360" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C360" s="14" t="inlineStr"/>
-      <c r="D360" s="14" t="inlineStr">
+      <c r="B361" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C361" s="14" t="inlineStr"/>
+      <c r="D361" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Colapsar los filtros detrás de un botón en las pantallas de listado</t>
         </is>
       </c>
-      <c r="E360" s="15" t="inlineStr"/>
-      <c r="F360" s="15" t="inlineStr">
+      <c r="E361" s="15" t="inlineStr"/>
+      <c r="F361" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G360" s="15" t="inlineStr">
+      <c r="G361" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H360" s="14" t="inlineStr">
+      <c r="H361" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I360" s="14" t="inlineStr"/>
-    </row>
-    <row r="361">
-      <c r="A361" s="16" t="inlineStr">
+      <c r="I361" s="14" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="16" t="inlineStr">
         <is>
           <t>T-65.2</t>
         </is>
       </c>
-      <c r="B361" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C361" s="16" t="inlineStr"/>
-      <c r="D361" s="16" t="inlineStr">
+      <c r="B362" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C362" s="16" t="inlineStr"/>
+      <c r="D362" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Revisar las pantallas de los módulos nuevos en ancho de celular</t>
         </is>
       </c>
-      <c r="E361" s="17" t="inlineStr"/>
-      <c r="F361" s="17" t="inlineStr">
+      <c r="E362" s="17" t="inlineStr"/>
+      <c r="F362" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G361" s="17" t="inlineStr">
+      <c r="G362" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H361" s="16" t="inlineStr">
+      <c r="H362" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I361" s="16" t="inlineStr"/>
-    </row>
-    <row r="362">
-      <c r="A362" s="14" t="inlineStr">
+      <c r="I362" s="16" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="14" t="inlineStr">
         <is>
           <t>T-65.3</t>
         </is>
       </c>
-      <c r="B362" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C362" s="14" t="inlineStr"/>
-      <c r="D362" s="14" t="inlineStr">
+      <c r="B363" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C363" s="14" t="inlineStr"/>
+      <c r="D363" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Validar en Chrome y en un segundo navegador</t>
         </is>
       </c>
-      <c r="E362" s="15" t="inlineStr"/>
-      <c r="F362" s="15" t="inlineStr">
+      <c r="E363" s="15" t="inlineStr"/>
+      <c r="F363" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G362" s="15" t="inlineStr">
+      <c r="G363" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H362" s="14" t="inlineStr">
+      <c r="H363" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I362" s="14" t="inlineStr"/>
-    </row>
-    <row r="363">
-      <c r="A363" s="16" t="inlineStr">
+      <c r="I363" s="14" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="16" t="inlineStr">
         <is>
           <t>T-65.4</t>
         </is>
       </c>
-      <c r="B363" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C363" s="16" t="inlineStr"/>
-      <c r="D363" s="16" t="inlineStr">
+      <c r="B364" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C364" s="16" t="inlineStr"/>
+      <c r="D364" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Validar en un celular real</t>
         </is>
       </c>
-      <c r="E363" s="17" t="inlineStr"/>
-      <c r="F363" s="17" t="inlineStr">
+      <c r="E364" s="17" t="inlineStr"/>
+      <c r="F364" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G363" s="17" t="inlineStr">
+      <c r="G364" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H363" s="16" t="inlineStr">
+      <c r="H364" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I363" s="16" t="inlineStr"/>
-    </row>
-    <row r="364" ht="16" customHeight="1">
-      <c r="A364" s="12" t="inlineStr">
+      <c r="I364" s="16" t="inlineStr"/>
+    </row>
+    <row r="365" ht="16" customHeight="1">
+      <c r="A365" s="12" t="inlineStr">
         <is>
           <t>HU-66</t>
         </is>
       </c>
-      <c r="B364" s="12" t="inlineStr">
+      <c r="B365" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C364" s="12" t="inlineStr">
+      <c r="C365" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D364" s="12" t="inlineStr">
+      <c r="D365" s="12" t="inlineStr">
         <is>
           <t>Como equipo quiero dejar el proyecto documentado para poder continuarlo el año próximo.</t>
         </is>
       </c>
-      <c r="E364" s="13" t="inlineStr">
+      <c r="E365" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F364" s="13" t="inlineStr">
+      <c r="F365" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G364" s="13" t="inlineStr">
+      <c r="G365" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H364" s="12" t="inlineStr">
+      <c r="H365" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I364" s="12" t="inlineStr"/>
-    </row>
-    <row r="365">
-      <c r="A365" s="14" t="inlineStr">
+      <c r="I365" s="12" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="14" t="inlineStr">
         <is>
           <t>T-66.1</t>
         </is>
       </c>
-      <c r="B365" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C365" s="14" t="inlineStr"/>
-      <c r="D365" s="14" t="inlineStr">
+      <c r="B366" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C366" s="14" t="inlineStr"/>
+      <c r="D366" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Escribir el README con las instrucciones de instalación</t>
         </is>
       </c>
-      <c r="E365" s="15" t="inlineStr"/>
-      <c r="F365" s="15" t="inlineStr">
+      <c r="E366" s="15" t="inlineStr"/>
+      <c r="F366" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G365" s="15" t="inlineStr">
+      <c r="G366" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H365" s="14" t="inlineStr">
+      <c r="H366" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I365" s="14" t="inlineStr"/>
-    </row>
-    <row r="366">
-      <c r="A366" s="16" t="inlineStr">
+      <c r="I366" s="14" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="16" t="inlineStr">
         <is>
           <t>T-66.2</t>
         </is>
       </c>
-      <c r="B366" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C366" s="16" t="inlineStr"/>
-      <c r="D366" s="16" t="inlineStr">
+      <c r="B367" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C367" s="16" t="inlineStr"/>
+      <c r="D367" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Escribir el manual de usuario básico</t>
         </is>
       </c>
-      <c r="E366" s="17" t="inlineStr"/>
-      <c r="F366" s="17" t="inlineStr">
+      <c r="E367" s="17" t="inlineStr"/>
+      <c r="F367" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G366" s="17" t="inlineStr">
+      <c r="G367" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H366" s="16" t="inlineStr">
+      <c r="H367" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I366" s="16" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" s="14" t="inlineStr">
+      <c r="I367" s="16" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="14" t="inlineStr">
         <is>
           <t>T-66.3</t>
         </is>
       </c>
-      <c r="B367" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C367" s="14" t="inlineStr"/>
-      <c r="D367" s="14" t="inlineStr">
+      <c r="B368" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C368" s="14" t="inlineStr"/>
+      <c r="D368" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Documentar el modelo de datos</t>
         </is>
       </c>
-      <c r="E367" s="15" t="inlineStr"/>
-      <c r="F367" s="15" t="inlineStr">
+      <c r="E368" s="15" t="inlineStr"/>
+      <c r="F368" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G367" s="15" t="inlineStr">
+      <c r="G368" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H367" s="14" t="inlineStr">
+      <c r="H368" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I367" s="14" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" s="16" t="inlineStr">
+      <c r="I368" s="14" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="16" t="inlineStr">
         <is>
           <t>T-66.4</t>
         </is>
       </c>
-      <c r="B368" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C368" s="16" t="inlineStr"/>
-      <c r="D368" s="16" t="inlineStr">
+      <c r="B369" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C369" s="16" t="inlineStr"/>
+      <c r="D369" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Documentar el diseño de los módulos que quedaron sin implementar</t>
         </is>
       </c>
-      <c r="E368" s="17" t="inlineStr"/>
-      <c r="F368" s="17" t="inlineStr">
+      <c r="E369" s="17" t="inlineStr"/>
+      <c r="F369" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G368" s="17" t="inlineStr">
+      <c r="G369" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H368" s="16" t="inlineStr">
+      <c r="H369" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I368" s="16" t="inlineStr"/>
-    </row>
-    <row r="369" ht="16" customHeight="1">
-      <c r="A369" s="12" t="inlineStr">
+      <c r="I369" s="16" t="inlineStr"/>
+    </row>
+    <row r="370" ht="16" customHeight="1">
+      <c r="A370" s="12" t="inlineStr">
         <is>
           <t>HU-67</t>
         </is>
       </c>
-      <c r="B369" s="12" t="inlineStr">
+      <c r="B370" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C369" s="12" t="inlineStr">
+      <c r="C370" s="12" t="inlineStr">
         <is>
           <t>Calidad, UX y Documentación</t>
         </is>
       </c>
-      <c r="D369" s="12" t="inlineStr">
+      <c r="D370" s="12" t="inlineStr">
         <is>
           <t>Como equipo quiero probar el sistema completo para entregar una versión estable.</t>
         </is>
       </c>
-      <c r="E369" s="13" t="inlineStr">
+      <c r="E370" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F369" s="13" t="inlineStr">
+      <c r="F370" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G369" s="13" t="inlineStr">
+      <c r="G370" s="13" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H369" s="12" t="inlineStr">
+      <c r="H370" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I369" s="12" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" s="14" t="inlineStr">
+      <c r="I370" s="12" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="14" t="inlineStr">
         <is>
           <t>T-67.1</t>
         </is>
       </c>
-      <c r="B370" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C370" s="14" t="inlineStr"/>
-      <c r="D370" s="14" t="inlineStr">
+      <c r="B371" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C371" s="14" t="inlineStr"/>
+      <c r="D371" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Ejecutar la batería de pruebas de punta a punta</t>
         </is>
       </c>
-      <c r="E370" s="15" t="inlineStr"/>
-      <c r="F370" s="15" t="inlineStr">
+      <c r="E371" s="15" t="inlineStr"/>
+      <c r="F371" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G370" s="15" t="inlineStr">
+      <c r="G371" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H370" s="14" t="inlineStr">
+      <c r="H371" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I370" s="14" t="inlineStr"/>
-    </row>
-    <row r="371">
-      <c r="A371" s="16" t="inlineStr">
+      <c r="I371" s="14" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="16" t="inlineStr">
         <is>
           <t>T-67.2</t>
         </is>
       </c>
-      <c r="B371" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C371" s="16" t="inlineStr"/>
-      <c r="D371" s="16" t="inlineStr">
+      <c r="B372" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C372" s="16" t="inlineStr"/>
+      <c r="D372" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Corregir los errores detectados</t>
         </is>
       </c>
-      <c r="E371" s="17" t="inlineStr"/>
-      <c r="F371" s="17" t="inlineStr">
+      <c r="E372" s="17" t="inlineStr"/>
+      <c r="F372" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G371" s="17" t="inlineStr">
+      <c r="G372" s="17" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H371" s="16" t="inlineStr">
+      <c r="H372" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I371" s="16" t="inlineStr"/>
-    </row>
-    <row r="372">
-      <c r="A372" s="14" t="inlineStr">
+      <c r="I372" s="16" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="14" t="inlineStr">
         <is>
           <t>T-67.3</t>
         </is>
       </c>
-      <c r="B372" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C372" s="14" t="inlineStr"/>
-      <c r="D372" s="14" t="inlineStr">
+      <c r="B373" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C373" s="14" t="inlineStr"/>
+      <c r="D373" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Unificar la carga del encabezado en un archivo compartido</t>
         </is>
       </c>
-      <c r="E372" s="15" t="inlineStr"/>
-      <c r="F372" s="15" t="inlineStr">
+      <c r="E373" s="15" t="inlineStr"/>
+      <c r="F373" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G372" s="15" t="inlineStr">
+      <c r="G373" s="15" t="inlineStr">
         <is>
           <t>Sprint 13</t>
         </is>
       </c>
-      <c r="H372" s="14" t="inlineStr">
+      <c r="H373" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I372" s="14" t="inlineStr"/>
-    </row>
-    <row r="373" ht="20" customHeight="1">
-      <c r="A373" s="9" t="inlineStr">
+      <c r="I373" s="14" t="inlineStr"/>
+    </row>
+    <row r="374" ht="20" customHeight="1">
+      <c r="A374" s="9" t="inlineStr">
         <is>
           <t>E11</t>
         </is>
       </c>
-      <c r="B373" s="9" t="inlineStr">
+      <c r="B374" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C373" s="9" t="inlineStr">
+      <c r="C374" s="9" t="inlineStr">
         <is>
           <t>Chat y Notificaciones</t>
         </is>
       </c>
-      <c r="D373" s="9" t="inlineStr">
+      <c r="D374" s="9" t="inlineStr">
         <is>
           <t>Mensajería entre empresas (posterior al MVP)</t>
         </is>
       </c>
-      <c r="E373" s="10" t="inlineStr">
+      <c r="E374" s="10" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F373" s="11" t="n"/>
-      <c r="G373" s="11" t="n"/>
-      <c r="H373" s="11" t="n"/>
-      <c r="I373" s="11" t="n"/>
-    </row>
-    <row r="374" ht="16" customHeight="1">
-      <c r="A374" s="12" t="inlineStr">
+      <c r="F374" s="11" t="n"/>
+      <c r="G374" s="11" t="n"/>
+      <c r="H374" s="11" t="n"/>
+      <c r="I374" s="11" t="n"/>
+    </row>
+    <row r="375" ht="16" customHeight="1">
+      <c r="A375" s="12" t="inlineStr">
         <is>
           <t>HU-73</t>
         </is>
       </c>
-      <c r="B374" s="12" t="inlineStr">
+      <c r="B375" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C374" s="12" t="inlineStr">
+      <c r="C375" s="12" t="inlineStr">
         <is>
           <t>Chat y Notificaciones</t>
         </is>
       </c>
-      <c r="D374" s="12" t="inlineStr">
+      <c r="D375" s="12" t="inlineStr">
         <is>
           <t>Como empresa quiero chatear con otra empresa para coordinar una articulación.</t>
         </is>
       </c>
-      <c r="E374" s="13" t="inlineStr">
+      <c r="E375" s="13" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F374" s="13" t="inlineStr">
+      <c r="F375" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G374" s="13" t="inlineStr">
+      <c r="G375" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H374" s="12" t="inlineStr">
+      <c r="H375" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I374" s="12" t="inlineStr"/>
-    </row>
-    <row r="375">
-      <c r="A375" s="14" t="inlineStr">
+      <c r="I375" s="12" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="14" t="inlineStr">
         <is>
           <t>T-73.1</t>
         </is>
       </c>
-      <c r="B375" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C375" s="14" t="inlineStr"/>
-      <c r="D375" s="14" t="inlineStr">
+      <c r="B376" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C376" s="14" t="inlineStr"/>
+      <c r="D376" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar la pantalla de chat</t>
         </is>
       </c>
-      <c r="E375" s="15" t="inlineStr"/>
-      <c r="F375" s="15" t="inlineStr">
+      <c r="E376" s="15" t="inlineStr"/>
+      <c r="F376" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G375" s="15" t="inlineStr">
+      <c r="G376" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H375" s="14" t="inlineStr">
+      <c r="H376" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I375" s="14" t="inlineStr"/>
-    </row>
-    <row r="376">
-      <c r="A376" s="16" t="inlineStr">
+      <c r="I376" s="14" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="16" t="inlineStr">
         <is>
           <t>T-73.2</t>
         </is>
       </c>
-      <c r="B376" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C376" s="16" t="inlineStr"/>
-      <c r="D376" s="16" t="inlineStr">
+      <c r="B377" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C377" s="16" t="inlineStr"/>
+      <c r="D377" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar el envío y la recepción de mensajes</t>
         </is>
       </c>
-      <c r="E376" s="17" t="inlineStr"/>
-      <c r="F376" s="17" t="inlineStr">
+      <c r="E377" s="17" t="inlineStr"/>
+      <c r="F377" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G376" s="17" t="inlineStr">
+      <c r="G377" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H376" s="16" t="inlineStr">
+      <c r="H377" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I376" s="16" t="inlineStr"/>
-    </row>
-    <row r="377">
-      <c r="A377" s="14" t="inlineStr">
+      <c r="I377" s="16" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="14" t="inlineStr">
         <is>
           <t>T-73.3</t>
         </is>
       </c>
-      <c r="B377" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C377" s="14" t="inlineStr"/>
-      <c r="D377" s="14" t="inlineStr">
+      <c r="B378" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C378" s="14" t="inlineStr"/>
+      <c r="D378" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Agregar notificaciones de mensaje nuevo</t>
         </is>
       </c>
-      <c r="E377" s="15" t="inlineStr"/>
-      <c r="F377" s="15" t="inlineStr">
+      <c r="E378" s="15" t="inlineStr"/>
+      <c r="F378" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G377" s="15" t="inlineStr">
+      <c r="G378" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H377" s="14" t="inlineStr">
+      <c r="H378" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I377" s="14" t="inlineStr"/>
-    </row>
-    <row r="378" ht="20" customHeight="1">
-      <c r="A378" s="9" t="inlineStr">
+      <c r="I378" s="14" t="inlineStr"/>
+    </row>
+    <row r="379" ht="20" customHeight="1">
+      <c r="A379" s="9" t="inlineStr">
         <is>
           <t>E12</t>
         </is>
       </c>
-      <c r="B378" s="9" t="inlineStr">
+      <c r="B379" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C378" s="9" t="inlineStr">
+      <c r="C379" s="9" t="inlineStr">
         <is>
           <t>Configuración de Módulos</t>
         </is>
       </c>
-      <c r="D378" s="9" t="inlineStr">
+      <c r="D379" s="9" t="inlineStr">
         <is>
           <t>Cada empresa activa sólo los módulos que usa</t>
         </is>
       </c>
-      <c r="E378" s="10" t="inlineStr">
+      <c r="E379" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F378" s="11" t="n"/>
-      <c r="G378" s="11" t="n"/>
-      <c r="H378" s="11" t="n"/>
-      <c r="I378" s="11" t="n"/>
-    </row>
-    <row r="379" ht="26" customHeight="1">
-      <c r="A379" s="12" t="inlineStr">
+      <c r="F379" s="11" t="n"/>
+      <c r="G379" s="11" t="n"/>
+      <c r="H379" s="11" t="n"/>
+      <c r="I379" s="11" t="n"/>
+    </row>
+    <row r="380" ht="26" customHeight="1">
+      <c r="A380" s="12" t="inlineStr">
         <is>
           <t>HU-34</t>
         </is>
       </c>
-      <c r="B379" s="12" t="inlineStr">
+      <c r="B380" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C379" s="12" t="inlineStr">
+      <c r="C380" s="12" t="inlineStr">
         <is>
           <t>Configuración de Módulos</t>
         </is>
       </c>
-      <c r="D379" s="12" t="inlineStr">
+      <c r="D380" s="12" t="inlineStr">
         <is>
           <t>Como administrador de la empresa quiero activar sólo los módulos que mi empresa usa para no ver funciones que no necesito.</t>
         </is>
       </c>
-      <c r="E379" s="13" t="inlineStr">
+      <c r="E380" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F379" s="13" t="inlineStr">
+      <c r="F380" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G379" s="13" t="inlineStr">
+      <c r="G380" s="13" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H379" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I379" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" s="14" t="inlineStr">
+      <c r="H380" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I380" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="14" t="inlineStr">
         <is>
           <t>T-34.1</t>
         </is>
       </c>
-      <c r="B380" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C380" s="14" t="inlineStr"/>
-      <c r="D380" s="14" t="inlineStr">
+      <c r="B381" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C381" s="14" t="inlineStr"/>
+      <c r="D381" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Crear la tabla de módulos activos por empresa</t>
         </is>
       </c>
-      <c r="E380" s="15" t="inlineStr"/>
-      <c r="F380" s="15" t="inlineStr">
+      <c r="E381" s="15" t="inlineStr"/>
+      <c r="F381" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G380" s="15" t="inlineStr">
+      <c r="G381" s="15" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H380" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I380" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="16" t="inlineStr">
+      <c r="H381" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I381" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="16" t="inlineStr">
         <is>
           <t>T-34.2</t>
         </is>
       </c>
-      <c r="B381" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C381" s="16" t="inlineStr"/>
-      <c r="D381" s="16" t="inlineStr">
+      <c r="B382" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C382" s="16" t="inlineStr"/>
+      <c r="D382" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Definir el conjunto de módulos disponibles</t>
         </is>
       </c>
-      <c r="E381" s="17" t="inlineStr"/>
-      <c r="F381" s="17" t="inlineStr">
+      <c r="E382" s="17" t="inlineStr"/>
+      <c r="F382" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G381" s="17" t="inlineStr">
+      <c r="G382" s="17" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H381" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I381" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="14" t="inlineStr">
+      <c r="H382" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I382" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="14" t="inlineStr">
         <is>
           <t>T-34.3</t>
         </is>
       </c>
-      <c r="B382" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C382" s="14" t="inlineStr"/>
-      <c r="D382" s="14" t="inlineStr">
+      <c r="B383" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C383" s="14" t="inlineStr"/>
+      <c r="D383" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar los endpoints de consulta y actualización</t>
         </is>
       </c>
-      <c r="E382" s="15" t="inlineStr"/>
-      <c r="F382" s="15" t="inlineStr">
+      <c r="E383" s="15" t="inlineStr"/>
+      <c r="F383" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G382" s="15" t="inlineStr">
+      <c r="G383" s="15" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H382" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I382" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="16" t="inlineStr">
+      <c r="H383" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I383" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="16" t="inlineStr">
         <is>
           <t>T-34.4</t>
         </is>
       </c>
-      <c r="B383" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C383" s="16" t="inlineStr"/>
-      <c r="D383" s="16" t="inlineStr">
+      <c r="B384" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C384" s="16" t="inlineStr"/>
+      <c r="D384" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar la pantalla de configuración de módulos</t>
         </is>
       </c>
-      <c r="E383" s="17" t="inlineStr"/>
-      <c r="F383" s="17" t="inlineStr">
+      <c r="E384" s="17" t="inlineStr"/>
+      <c r="F384" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G383" s="17" t="inlineStr">
+      <c r="G384" s="17" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H383" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I383" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="14" t="inlineStr">
+      <c r="H384" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I384" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="14" t="inlineStr">
         <is>
           <t>T-34.5</t>
         </is>
       </c>
-      <c r="B384" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C384" s="14" t="inlineStr"/>
-      <c r="D384" s="14" t="inlineStr">
+      <c r="B385" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C385" s="14" t="inlineStr"/>
+      <c r="D385" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Mostrar en el menú sólo los módulos activos</t>
         </is>
       </c>
-      <c r="E384" s="15" t="inlineStr"/>
-      <c r="F384" s="15" t="inlineStr">
+      <c r="E385" s="15" t="inlineStr"/>
+      <c r="F385" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G384" s="15" t="inlineStr">
+      <c r="G385" s="15" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H384" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I384" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="385" ht="26" customHeight="1">
-      <c r="A385" s="12" t="inlineStr">
+      <c r="H385" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I385" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="26" customHeight="1">
+      <c r="A386" s="12" t="inlineStr">
         <is>
           <t>HU-35</t>
         </is>
       </c>
-      <c r="B385" s="12" t="inlineStr">
+      <c r="B386" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C385" s="12" t="inlineStr">
+      <c r="C386" s="12" t="inlineStr">
         <is>
           <t>Configuración de Módulos</t>
         </is>
       </c>
-      <c r="D385" s="12" t="inlineStr">
+      <c r="D386" s="12" t="inlineStr">
         <is>
           <t>Como sistema quiero rechazar los pedidos a módulos desactivados para que no se pueda entrar por fuera del menú.</t>
         </is>
       </c>
-      <c r="E385" s="13" t="inlineStr">
+      <c r="E386" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F385" s="13" t="inlineStr">
+      <c r="F386" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G385" s="13" t="inlineStr">
+      <c r="G386" s="13" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H385" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I385" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="14" t="inlineStr">
+      <c r="H386" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I386" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="14" t="inlineStr">
         <is>
           <t>T-35.1</t>
         </is>
       </c>
-      <c r="B386" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C386" s="14" t="inlineStr"/>
-      <c r="D386" s="14" t="inlineStr">
+      <c r="B387" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C387" s="14" t="inlineStr"/>
+      <c r="D387" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar el middleware de módulo activo</t>
         </is>
       </c>
-      <c r="E386" s="15" t="inlineStr"/>
-      <c r="F386" s="15" t="inlineStr">
+      <c r="E387" s="15" t="inlineStr"/>
+      <c r="F387" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G386" s="15" t="inlineStr">
+      <c r="G387" s="15" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H386" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I386" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" s="16" t="inlineStr">
+      <c r="H387" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I387" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="16" t="inlineStr">
         <is>
           <t>T-35.2</t>
         </is>
       </c>
-      <c r="B387" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C387" s="16" t="inlineStr"/>
-      <c r="D387" s="16" t="inlineStr">
+      <c r="B388" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C388" s="16" t="inlineStr"/>
+      <c r="D388" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Aplicarlo a las rutas de movimientos y categorías</t>
         </is>
       </c>
-      <c r="E387" s="17" t="inlineStr"/>
-      <c r="F387" s="17" t="inlineStr">
+      <c r="E388" s="17" t="inlineStr"/>
+      <c r="F388" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G387" s="17" t="inlineStr">
+      <c r="G388" s="17" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H387" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I387" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="14" t="inlineStr">
+      <c r="H388" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I388" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="14" t="inlineStr">
         <is>
           <t>T-35.3</t>
         </is>
       </c>
-      <c r="B388" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C388" s="14" t="inlineStr"/>
-      <c r="D388" s="14" t="inlineStr">
+      <c r="B389" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C389" s="14" t="inlineStr"/>
+      <c r="D389" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Mostrar en pantalla un aviso claro cuando el módulo está apagado</t>
         </is>
       </c>
-      <c r="E388" s="15" t="inlineStr"/>
-      <c r="F388" s="15" t="inlineStr">
+      <c r="E389" s="15" t="inlineStr"/>
+      <c r="F389" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G388" s="15" t="inlineStr">
+      <c r="G389" s="15" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H388" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I388" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" s="16" t="inlineStr">
+      <c r="H389" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I389" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="16" t="inlineStr">
         <is>
           <t>T-35.4</t>
         </is>
       </c>
-      <c r="B389" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C389" s="16" t="inlineStr"/>
-      <c r="D389" s="16" t="inlineStr">
+      <c r="B390" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C390" s="16" t="inlineStr"/>
+      <c r="D390" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Distinguir el aviso de módulo apagado del de falta de permiso</t>
         </is>
       </c>
-      <c r="E389" s="17" t="inlineStr"/>
-      <c r="F389" s="17" t="inlineStr">
+      <c r="E390" s="17" t="inlineStr"/>
+      <c r="F390" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G389" s="17" t="inlineStr">
+      <c r="G390" s="17" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H389" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I389" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="14" t="inlineStr">
+      <c r="H390" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I390" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="14" t="inlineStr">
         <is>
           <t>T-35.5</t>
         </is>
       </c>
-      <c r="B390" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C390" s="14" t="inlineStr"/>
-      <c r="D390" s="14" t="inlineStr">
+      <c r="B391" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C391" s="14" t="inlineStr"/>
+      <c r="D391" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Probar el acceso con el módulo apagado</t>
         </is>
       </c>
-      <c r="E390" s="15" t="inlineStr"/>
-      <c r="F390" s="15" t="inlineStr">
+      <c r="E391" s="15" t="inlineStr"/>
+      <c r="F391" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G390" s="15" t="inlineStr">
+      <c r="G391" s="15" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H390" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I390" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="391" ht="26" customHeight="1">
-      <c r="A391" s="12" t="inlineStr">
+      <c r="H391" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I391" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="26" customHeight="1">
+      <c r="A392" s="12" t="inlineStr">
         <is>
           <t>HU-36</t>
         </is>
       </c>
-      <c r="B391" s="12" t="inlineStr">
+      <c r="B392" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C391" s="12" t="inlineStr">
+      <c r="C392" s="12" t="inlineStr">
         <is>
           <t>Configuración de Módulos</t>
         </is>
       </c>
-      <c r="D391" s="12" t="inlineStr">
+      <c r="D392" s="12" t="inlineStr">
         <is>
           <t>Como empresa nueva quiero empezar con una configuración razonable para no tener que definir todo antes de usar el sistema.</t>
         </is>
       </c>
-      <c r="E391" s="13" t="inlineStr">
+      <c r="E392" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F391" s="13" t="inlineStr">
+      <c r="F392" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G391" s="13" t="inlineStr">
+      <c r="G392" s="13" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H391" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I391" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="14" t="inlineStr">
+      <c r="H392" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I392" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="14" t="inlineStr">
         <is>
           <t>T-36.1</t>
         </is>
       </c>
-      <c r="B392" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C392" s="14" t="inlineStr"/>
-      <c r="D392" s="14" t="inlineStr">
+      <c r="B393" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C393" s="14" t="inlineStr"/>
+      <c r="D393" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Definir el conjunto de módulos y categorías iniciales</t>
         </is>
       </c>
-      <c r="E392" s="15" t="inlineStr"/>
-      <c r="F392" s="15" t="inlineStr">
+      <c r="E393" s="15" t="inlineStr"/>
+      <c r="F393" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G392" s="15" t="inlineStr">
+      <c r="G393" s="15" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H392" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I392" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" s="16" t="inlineStr">
+      <c r="H393" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I393" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="16" t="inlineStr">
         <is>
           <t>T-36.2</t>
         </is>
       </c>
-      <c r="B393" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C393" s="16" t="inlineStr"/>
-      <c r="D393" s="16" t="inlineStr">
+      <c r="B394" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C394" s="16" t="inlineStr"/>
+      <c r="D394" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar la carga automática al aprobar la empresa</t>
         </is>
       </c>
-      <c r="E393" s="17" t="inlineStr"/>
-      <c r="F393" s="17" t="inlineStr">
+      <c r="E394" s="17" t="inlineStr"/>
+      <c r="F394" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G393" s="17" t="inlineStr">
+      <c r="G394" s="17" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H393" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I393" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" s="14" t="inlineStr">
+      <c r="H394" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I394" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="14" t="inlineStr">
         <is>
           <t>T-36.3</t>
         </is>
       </c>
-      <c r="B394" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C394" s="14" t="inlineStr"/>
-      <c r="D394" s="14" t="inlineStr">
+      <c r="B395" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C395" s="14" t="inlineStr"/>
+      <c r="D395" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Dejar la configuración escrita en la base, no deducida del catálogo</t>
         </is>
       </c>
-      <c r="E394" s="15" t="inlineStr"/>
-      <c r="F394" s="15" t="inlineStr">
+      <c r="E395" s="15" t="inlineStr"/>
+      <c r="F395" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G394" s="15" t="inlineStr">
+      <c r="G395" s="15" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H394" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I394" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" s="16" t="inlineStr">
+      <c r="H395" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I395" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="16" t="inlineStr">
         <is>
           <t>T-36.4</t>
         </is>
       </c>
-      <c r="B395" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C395" s="16" t="inlineStr"/>
-      <c r="D395" s="16" t="inlineStr">
+      <c r="B396" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C396" s="16" t="inlineStr"/>
+      <c r="D396" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Evitar que una segunda aprobación duplique o pise lo ya configurado</t>
         </is>
       </c>
-      <c r="E395" s="17" t="inlineStr"/>
-      <c r="F395" s="17" t="inlineStr">
+      <c r="E396" s="17" t="inlineStr"/>
+      <c r="F396" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G395" s="17" t="inlineStr">
+      <c r="G396" s="17" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H395" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I395" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="14" t="inlineStr">
+      <c r="H396" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I396" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="14" t="inlineStr">
         <is>
           <t>T-36.5</t>
         </is>
       </c>
-      <c r="B396" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C396" s="14" t="inlineStr"/>
-      <c r="D396" s="14" t="inlineStr">
+      <c r="B397" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C397" s="14" t="inlineStr"/>
+      <c r="D397" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Probar el alta de una empresa nueva de punta a punta</t>
         </is>
       </c>
-      <c r="E396" s="15" t="inlineStr"/>
-      <c r="F396" s="15" t="inlineStr">
+      <c r="E397" s="15" t="inlineStr"/>
+      <c r="F397" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G396" s="15" t="inlineStr">
+      <c r="G397" s="15" t="inlineStr">
         <is>
           <t>Sprint 06</t>
         </is>
       </c>
-      <c r="H396" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I396" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="397" ht="20" customHeight="1">
-      <c r="A397" s="9" t="inlineStr">
+      <c r="H397" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I397" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="20" customHeight="1">
+      <c r="A398" s="9" t="inlineStr">
         <is>
           <t>E13</t>
         </is>
       </c>
-      <c r="B397" s="9" t="inlineStr">
+      <c r="B398" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C397" s="9" t="inlineStr">
+      <c r="C398" s="9" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D397" s="9" t="inlineStr">
+      <c r="D398" s="9" t="inlineStr">
         <is>
           <t>Catálogo de servicios que generan ingreso o egreso</t>
         </is>
       </c>
-      <c r="E397" s="10" t="inlineStr">
+      <c r="E398" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F397" s="11" t="n"/>
-      <c r="G397" s="11" t="n"/>
-      <c r="H397" s="11" t="n"/>
-      <c r="I397" s="11" t="n"/>
-    </row>
-    <row r="398" ht="26" customHeight="1">
-      <c r="A398" s="12" t="inlineStr">
+      <c r="F398" s="11" t="n"/>
+      <c r="G398" s="11" t="n"/>
+      <c r="H398" s="11" t="n"/>
+      <c r="I398" s="11" t="n"/>
+    </row>
+    <row r="399" ht="26" customHeight="1">
+      <c r="A399" s="12" t="inlineStr">
         <is>
           <t>HU-47</t>
         </is>
       </c>
-      <c r="B398" s="12" t="inlineStr">
+      <c r="B399" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C398" s="12" t="inlineStr">
+      <c r="C399" s="12" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D398" s="12" t="inlineStr">
+      <c r="D399" s="12" t="inlineStr">
         <is>
           <t>Como administrador quiero cargar los servicios que presta o contrata mi empresa para registrarlos igual que los productos.</t>
         </is>
       </c>
-      <c r="E398" s="13" t="inlineStr">
+      <c r="E399" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F398" s="13" t="inlineStr">
+      <c r="F399" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G398" s="13" t="inlineStr">
+      <c r="G399" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H398" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I398" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" s="14" t="inlineStr">
+      <c r="H399" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I399" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="14" t="inlineStr">
         <is>
           <t>T-47.1</t>
         </is>
       </c>
-      <c r="B399" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C399" s="14" t="inlineStr"/>
-      <c r="D399" s="14" t="inlineStr">
+      <c r="B400" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C400" s="14" t="inlineStr"/>
+      <c r="D400" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Reutilizar el modelo de productos agregando la distinción de servicio</t>
         </is>
       </c>
-      <c r="E399" s="15" t="inlineStr"/>
-      <c r="F399" s="15" t="inlineStr">
+      <c r="E400" s="15" t="inlineStr"/>
+      <c r="F400" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G399" s="15" t="inlineStr">
+      <c r="G400" s="15" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H399" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I399" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" s="16" t="inlineStr">
+      <c r="H400" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I400" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="16" t="inlineStr">
         <is>
           <t>T-47.2</t>
         </is>
       </c>
-      <c r="B400" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C400" s="16" t="inlineStr"/>
-      <c r="D400" s="16" t="inlineStr">
+      <c r="B401" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C401" s="16" t="inlineStr"/>
+      <c r="D401" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar el alta, la edición y la baja lógica</t>
         </is>
       </c>
-      <c r="E400" s="17" t="inlineStr"/>
-      <c r="F400" s="17" t="inlineStr">
+      <c r="E401" s="17" t="inlineStr"/>
+      <c r="F401" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G400" s="17" t="inlineStr">
+      <c r="G401" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H400" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I400" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" s="14" t="inlineStr">
+      <c r="H401" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I401" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="14" t="inlineStr">
         <is>
           <t>T-47.3</t>
         </is>
       </c>
-      <c r="B401" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C401" s="14" t="inlineStr"/>
-      <c r="D401" s="14" t="inlineStr">
+      <c r="B402" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C402" s="14" t="inlineStr"/>
+      <c r="D402" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar la pantalla de servicios</t>
         </is>
       </c>
-      <c r="E401" s="15" t="inlineStr"/>
-      <c r="F401" s="15" t="inlineStr">
+      <c r="E402" s="15" t="inlineStr"/>
+      <c r="F402" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G401" s="15" t="inlineStr">
+      <c r="G402" s="15" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H401" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I401" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" s="16" t="inlineStr">
+      <c r="H402" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I402" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="16" t="inlineStr">
         <is>
           <t>T-47.4</t>
         </is>
       </c>
-      <c r="B402" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C402" s="16" t="inlineStr"/>
-      <c r="D402" s="16" t="inlineStr">
+      <c r="B403" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C403" s="16" t="inlineStr"/>
+      <c r="D403" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Verificar que los servicios no lleven existencias</t>
         </is>
       </c>
-      <c r="E402" s="17" t="inlineStr"/>
-      <c r="F402" s="17" t="inlineStr">
+      <c r="E403" s="17" t="inlineStr"/>
+      <c r="F403" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G402" s="17" t="inlineStr">
+      <c r="G403" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H402" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I402" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="403" ht="26" customHeight="1">
-      <c r="A403" s="12" t="inlineStr">
+      <c r="H403" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I403" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="26" customHeight="1">
+      <c r="A404" s="12" t="inlineStr">
         <is>
           <t>HU-48</t>
         </is>
       </c>
-      <c r="B403" s="12" t="inlineStr">
+      <c r="B404" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C403" s="12" t="inlineStr">
+      <c r="C404" s="12" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D403" s="12" t="inlineStr">
+      <c r="D404" s="12" t="inlineStr">
         <is>
           <t>Como tesorero quiero vincular un movimiento de dinero con un servicio para saber de dónde viene cada ingreso o egreso.</t>
         </is>
       </c>
-      <c r="E403" s="13" t="inlineStr">
+      <c r="E404" s="13" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="F403" s="13" t="inlineStr">
+      <c r="F404" s="13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G403" s="13" t="inlineStr">
+      <c r="G404" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H403" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I403" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="14" t="inlineStr">
+      <c r="H404" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I404" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="14" t="inlineStr">
         <is>
           <t>T-48.1</t>
         </is>
       </c>
-      <c r="B404" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C404" s="14" t="inlineStr"/>
-      <c r="D404" s="14" t="inlineStr">
+      <c r="B405" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C405" s="14" t="inlineStr"/>
+      <c r="D405" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Vincular el movimiento económico con el servicio</t>
         </is>
       </c>
-      <c r="E404" s="15" t="inlineStr"/>
-      <c r="F404" s="15" t="inlineStr">
+      <c r="E405" s="15" t="inlineStr"/>
+      <c r="F405" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G404" s="15" t="inlineStr">
+      <c r="G405" s="15" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H404" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I404" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="16" t="inlineStr">
+      <c r="H405" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I405" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="16" t="inlineStr">
         <is>
           <t>T-48.2</t>
         </is>
       </c>
-      <c r="B405" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C405" s="16" t="inlineStr"/>
-      <c r="D405" s="16" t="inlineStr">
+      <c r="B406" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C406" s="16" t="inlineStr"/>
+      <c r="D406" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Agregar el servicio al formulario de movimiento</t>
         </is>
       </c>
-      <c r="E405" s="17" t="inlineStr"/>
-      <c r="F405" s="17" t="inlineStr">
+      <c r="E406" s="17" t="inlineStr"/>
+      <c r="F406" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G405" s="17" t="inlineStr">
+      <c r="G406" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H405" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I405" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" s="14" t="inlineStr">
+      <c r="H406" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I406" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="14" t="inlineStr">
         <is>
           <t>T-48.3</t>
         </is>
       </c>
-      <c r="B406" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C406" s="14" t="inlineStr"/>
-      <c r="D406" s="14" t="inlineStr">
+      <c r="B407" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C407" s="14" t="inlineStr"/>
+      <c r="D407" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Agregar el filtro por servicio en el listado</t>
         </is>
       </c>
-      <c r="E406" s="15" t="inlineStr"/>
-      <c r="F406" s="15" t="inlineStr">
+      <c r="E407" s="15" t="inlineStr"/>
+      <c r="F407" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G406" s="15" t="inlineStr">
+      <c r="G407" s="15" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H406" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I406" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="407" ht="16" customHeight="1">
-      <c r="A407" s="12" t="inlineStr">
+      <c r="H407" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I407" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="16" customHeight="1">
+      <c r="A408" s="12" t="inlineStr">
         <is>
           <t>HU-49</t>
         </is>
       </c>
-      <c r="B407" s="12" t="inlineStr">
+      <c r="B408" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C407" s="12" t="inlineStr">
+      <c r="C408" s="12" t="inlineStr">
         <is>
           <t>Servicios</t>
         </is>
       </c>
-      <c r="D407" s="12" t="inlineStr">
+      <c r="D408" s="12" t="inlineStr">
         <is>
           <t>Como empresa quiero ver cuánto me deja cada servicio para saber cuáles conviene sostener.</t>
         </is>
       </c>
-      <c r="E407" s="13" t="inlineStr">
+      <c r="E408" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F407" s="13" t="inlineStr">
+      <c r="F408" s="13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G407" s="13" t="inlineStr">
+      <c r="G408" s="13" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H407" s="12" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I407" s="12" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="14" t="inlineStr">
+      <c r="H408" s="12" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I408" s="12" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="14" t="inlineStr">
         <is>
           <t>T-49.1</t>
         </is>
       </c>
-      <c r="B408" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C408" s="14" t="inlineStr"/>
-      <c r="D408" s="14" t="inlineStr">
+      <c r="B409" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C409" s="14" t="inlineStr"/>
+      <c r="D409" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar la consulta agrupada por servicio</t>
         </is>
       </c>
-      <c r="E408" s="15" t="inlineStr"/>
-      <c r="F408" s="15" t="inlineStr">
+      <c r="E409" s="15" t="inlineStr"/>
+      <c r="F409" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G408" s="15" t="inlineStr">
+      <c r="G409" s="15" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H408" s="14" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I408" s="14" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="16" t="inlineStr">
+      <c r="H409" s="14" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I409" s="14" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="16" t="inlineStr">
         <is>
           <t>T-49.2</t>
         </is>
       </c>
-      <c r="B409" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C409" s="16" t="inlineStr"/>
-      <c r="D409" s="16" t="inlineStr">
+      <c r="B410" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C410" s="16" t="inlineStr"/>
+      <c r="D410" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar la visualización del resumen</t>
         </is>
       </c>
-      <c r="E409" s="17" t="inlineStr"/>
-      <c r="F409" s="17" t="inlineStr">
+      <c r="E410" s="17" t="inlineStr"/>
+      <c r="F410" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G409" s="17" t="inlineStr">
+      <c r="G410" s="17" t="inlineStr">
         <is>
           <t>Sprint 09</t>
         </is>
       </c>
-      <c r="H409" s="16" t="inlineStr">
-        <is>
-          <t>Hecho</t>
-        </is>
-      </c>
-      <c r="I409" s="16" t="inlineStr">
-        <is>
-          <t>Equipo</t>
-        </is>
-      </c>
-    </row>
-    <row r="410" ht="20" customHeight="1">
-      <c r="A410" s="9" t="inlineStr">
+      <c r="H410" s="16" t="inlineStr">
+        <is>
+          <t>Hecho</t>
+        </is>
+      </c>
+      <c r="I410" s="16" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="20" customHeight="1">
+      <c r="A411" s="9" t="inlineStr">
         <is>
           <t>E14</t>
         </is>
       </c>
-      <c r="B410" s="9" t="inlineStr">
+      <c r="B411" s="9" t="inlineStr">
         <is>
           <t>Épica</t>
         </is>
       </c>
-      <c r="C410" s="9" t="inlineStr">
+      <c r="C411" s="9" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D410" s="9" t="inlineStr">
+      <c r="D411" s="9" t="inlineStr">
         <is>
           <t>Vacaciones, licencias y documentación del personal (backlog futuro)</t>
         </is>
       </c>
-      <c r="E410" s="10" t="inlineStr">
+      <c r="E411" s="10" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F410" s="11" t="n"/>
-      <c r="G410" s="11" t="n"/>
-      <c r="H410" s="11" t="n"/>
-      <c r="I410" s="11" t="n"/>
-    </row>
-    <row r="411" ht="16" customHeight="1">
-      <c r="A411" s="12" t="inlineStr">
+      <c r="F411" s="11" t="n"/>
+      <c r="G411" s="11" t="n"/>
+      <c r="H411" s="11" t="n"/>
+      <c r="I411" s="11" t="n"/>
+    </row>
+    <row r="412" ht="16" customHeight="1">
+      <c r="A412" s="12" t="inlineStr">
         <is>
           <t>HU-68</t>
         </is>
       </c>
-      <c r="B411" s="12" t="inlineStr">
+      <c r="B412" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C411" s="12" t="inlineStr">
+      <c r="C412" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D411" s="12" t="inlineStr">
+      <c r="D412" s="12" t="inlineStr">
         <is>
           <t>Como empleado quiero solicitar días de vacaciones para gestionarlos sin papeles.</t>
         </is>
       </c>
-      <c r="E411" s="13" t="inlineStr">
+      <c r="E412" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F411" s="13" t="inlineStr">
+      <c r="F412" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G411" s="13" t="inlineStr">
+      <c r="G412" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H411" s="12" t="inlineStr">
+      <c r="H412" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I411" s="12" t="inlineStr"/>
-    </row>
-    <row r="412">
-      <c r="A412" s="14" t="inlineStr">
+      <c r="I412" s="12" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="14" t="inlineStr">
         <is>
           <t>T-68.1</t>
         </is>
       </c>
-      <c r="B412" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C412" s="14" t="inlineStr"/>
-      <c r="D412" s="14" t="inlineStr">
+      <c r="B413" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C413" s="14" t="inlineStr"/>
+      <c r="D413" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar el modelo de licencias y saldo de días</t>
         </is>
       </c>
-      <c r="E412" s="15" t="inlineStr"/>
-      <c r="F412" s="15" t="inlineStr">
+      <c r="E413" s="15" t="inlineStr"/>
+      <c r="F413" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G412" s="15" t="inlineStr">
+      <c r="G413" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H412" s="14" t="inlineStr">
+      <c r="H413" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I412" s="14" t="inlineStr"/>
-    </row>
-    <row r="413">
-      <c r="A413" s="16" t="inlineStr">
+      <c r="I413" s="14" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="16" t="inlineStr">
         <is>
           <t>T-68.2</t>
         </is>
       </c>
-      <c r="B413" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C413" s="16" t="inlineStr"/>
-      <c r="D413" s="16" t="inlineStr">
+      <c r="B414" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C414" s="16" t="inlineStr"/>
+      <c r="D414" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar el circuito de solicitud y aprobación</t>
         </is>
       </c>
-      <c r="E413" s="17" t="inlineStr"/>
-      <c r="F413" s="17" t="inlineStr">
+      <c r="E414" s="17" t="inlineStr"/>
+      <c r="F414" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G413" s="17" t="inlineStr">
+      <c r="G414" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H413" s="16" t="inlineStr">
+      <c r="H414" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I413" s="16" t="inlineStr"/>
-    </row>
-    <row r="414">
-      <c r="A414" s="14" t="inlineStr">
+      <c r="I414" s="16" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="14" t="inlineStr">
         <is>
           <t>T-68.3</t>
         </is>
       </c>
-      <c r="B414" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C414" s="14" t="inlineStr"/>
-      <c r="D414" s="14" t="inlineStr">
+      <c r="B415" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C415" s="14" t="inlineStr"/>
+      <c r="D415" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar las pantallas de solicitud y de bandeja del responsable</t>
         </is>
       </c>
-      <c r="E414" s="15" t="inlineStr"/>
-      <c r="F414" s="15" t="inlineStr">
+      <c r="E415" s="15" t="inlineStr"/>
+      <c r="F415" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G414" s="15" t="inlineStr">
+      <c r="G415" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H414" s="14" t="inlineStr">
+      <c r="H415" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I414" s="14" t="inlineStr"/>
-    </row>
-    <row r="415">
-      <c r="A415" s="16" t="inlineStr">
+      <c r="I415" s="14" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="16" t="inlineStr">
         <is>
           <t>T-68.4</t>
         </is>
       </c>
-      <c r="B415" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C415" s="16" t="inlineStr"/>
-      <c r="D415" s="16" t="inlineStr">
+      <c r="B416" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C416" s="16" t="inlineStr"/>
+      <c r="D416" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar el cálculo del saldo de días</t>
         </is>
       </c>
-      <c r="E415" s="17" t="inlineStr"/>
-      <c r="F415" s="17" t="inlineStr">
+      <c r="E416" s="17" t="inlineStr"/>
+      <c r="F416" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G415" s="17" t="inlineStr">
+      <c r="G416" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H415" s="16" t="inlineStr">
+      <c r="H416" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I415" s="16" t="inlineStr"/>
-    </row>
-    <row r="416" ht="16" customHeight="1">
-      <c r="A416" s="12" t="inlineStr">
+      <c r="I416" s="16" t="inlineStr"/>
+    </row>
+    <row r="417" ht="16" customHeight="1">
+      <c r="A417" s="12" t="inlineStr">
         <is>
           <t>HU-69</t>
         </is>
       </c>
-      <c r="B416" s="12" t="inlineStr">
+      <c r="B417" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C416" s="12" t="inlineStr">
+      <c r="C417" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D416" s="12" t="inlineStr">
+      <c r="D417" s="12" t="inlineStr">
         <is>
           <t>Como empleado quiero subir mi orden médica para justificar una ausencia.</t>
         </is>
       </c>
-      <c r="E416" s="13" t="inlineStr">
+      <c r="E417" s="13" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F416" s="13" t="inlineStr">
+      <c r="F417" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G416" s="13" t="inlineStr">
+      <c r="G417" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H416" s="12" t="inlineStr">
+      <c r="H417" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I416" s="12" t="inlineStr"/>
-    </row>
-    <row r="417">
-      <c r="A417" s="14" t="inlineStr">
+      <c r="I417" s="12" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="14" t="inlineStr">
         <is>
           <t>T-69.1</t>
         </is>
       </c>
-      <c r="B417" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C417" s="14" t="inlineStr"/>
-      <c r="D417" s="14" t="inlineStr">
+      <c r="B418" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C418" s="14" t="inlineStr"/>
+      <c r="D418" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Definir el almacenamiento local de archivos adjuntos</t>
         </is>
       </c>
-      <c r="E417" s="15" t="inlineStr"/>
-      <c r="F417" s="15" t="inlineStr">
+      <c r="E418" s="15" t="inlineStr"/>
+      <c r="F418" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G417" s="15" t="inlineStr">
+      <c r="G418" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H417" s="14" t="inlineStr">
+      <c r="H418" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I417" s="14" t="inlineStr"/>
-    </row>
-    <row r="418">
-      <c r="A418" s="16" t="inlineStr">
+      <c r="I418" s="14" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="16" t="inlineStr">
         <is>
           <t>T-69.2</t>
         </is>
       </c>
-      <c r="B418" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C418" s="16" t="inlineStr"/>
-      <c r="D418" s="16" t="inlineStr">
+      <c r="B419" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C419" s="16" t="inlineStr"/>
+      <c r="D419" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar la subida con validación de tipo y tamaño</t>
         </is>
       </c>
-      <c r="E418" s="17" t="inlineStr"/>
-      <c r="F418" s="17" t="inlineStr">
+      <c r="E419" s="17" t="inlineStr"/>
+      <c r="F419" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G418" s="17" t="inlineStr">
+      <c r="G419" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H418" s="16" t="inlineStr">
+      <c r="H419" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I418" s="16" t="inlineStr"/>
-    </row>
-    <row r="419">
-      <c r="A419" s="14" t="inlineStr">
+      <c r="I419" s="16" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="14" t="inlineStr">
         <is>
           <t>T-69.3</t>
         </is>
       </c>
-      <c r="B419" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C419" s="14" t="inlineStr"/>
-      <c r="D419" s="14" t="inlineStr">
+      <c r="B420" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C420" s="14" t="inlineStr"/>
+      <c r="D420" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Restringir la visibilidad del archivo</t>
         </is>
       </c>
-      <c r="E419" s="15" t="inlineStr"/>
-      <c r="F419" s="15" t="inlineStr">
+      <c r="E420" s="15" t="inlineStr"/>
+      <c r="F420" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G419" s="15" t="inlineStr">
+      <c r="G420" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H419" s="14" t="inlineStr">
+      <c r="H420" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I419" s="14" t="inlineStr"/>
-    </row>
-    <row r="420">
-      <c r="A420" s="16" t="inlineStr">
+      <c r="I420" s="14" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="16" t="inlineStr">
         <is>
           <t>T-69.4</t>
         </is>
       </c>
-      <c r="B420" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C420" s="16" t="inlineStr"/>
-      <c r="D420" s="16" t="inlineStr">
+      <c r="B421" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C421" s="16" t="inlineStr"/>
+      <c r="D421" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Definir el tratamiento de los datos de salud</t>
         </is>
       </c>
-      <c r="E420" s="17" t="inlineStr"/>
-      <c r="F420" s="17" t="inlineStr">
+      <c r="E421" s="17" t="inlineStr"/>
+      <c r="F421" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G420" s="17" t="inlineStr">
+      <c r="G421" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H420" s="16" t="inlineStr">
+      <c r="H421" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I420" s="16" t="inlineStr"/>
-    </row>
-    <row r="421" ht="16" customHeight="1">
-      <c r="A421" s="12" t="inlineStr">
+      <c r="I421" s="16" t="inlineStr"/>
+    </row>
+    <row r="422" ht="16" customHeight="1">
+      <c r="A422" s="12" t="inlineStr">
         <is>
           <t>HU-70</t>
         </is>
       </c>
-      <c r="B421" s="12" t="inlineStr">
+      <c r="B422" s="12" t="inlineStr">
         <is>
           <t>HU</t>
         </is>
       </c>
-      <c r="C421" s="12" t="inlineStr">
+      <c r="C422" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="D421" s="12" t="inlineStr">
+      <c r="D422" s="12" t="inlineStr">
         <is>
           <t>Como área de personal quiero ver el calendario de ausencias para organizar la cobertura.</t>
         </is>
       </c>
-      <c r="E421" s="13" t="inlineStr">
+      <c r="E422" s="13" t="inlineStr">
         <is>
           <t>Baja</t>
         </is>
       </c>
-      <c r="F421" s="13" t="inlineStr">
+      <c r="F422" s="13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G421" s="13" t="inlineStr">
+      <c r="G422" s="13" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H421" s="12" t="inlineStr">
+      <c r="H422" s="12" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I421" s="12" t="inlineStr"/>
-    </row>
-    <row r="422">
-      <c r="A422" s="14" t="inlineStr">
+      <c r="I422" s="12" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="14" t="inlineStr">
         <is>
           <t>T-70.1</t>
         </is>
       </c>
-      <c r="B422" s="14" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C422" s="14" t="inlineStr"/>
-      <c r="D422" s="14" t="inlineStr">
+      <c r="B423" s="14" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C423" s="14" t="inlineStr"/>
+      <c r="D423" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">    Diseñar el calendario de ausencias</t>
         </is>
       </c>
-      <c r="E422" s="15" t="inlineStr"/>
-      <c r="F422" s="15" t="inlineStr">
+      <c r="E423" s="15" t="inlineStr"/>
+      <c r="F423" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G422" s="15" t="inlineStr">
+      <c r="G423" s="15" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H422" s="14" t="inlineStr">
+      <c r="H423" s="14" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I422" s="14" t="inlineStr"/>
-    </row>
-    <row r="423">
-      <c r="A423" s="16" t="inlineStr">
+      <c r="I423" s="14" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="16" t="inlineStr">
         <is>
           <t>T-70.2</t>
         </is>
       </c>
-      <c r="B423" s="16" t="inlineStr">
-        <is>
-          <t>Tarea</t>
-        </is>
-      </c>
-      <c r="C423" s="16" t="inlineStr"/>
-      <c r="D423" s="16" t="inlineStr">
+      <c r="B424" s="16" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C424" s="16" t="inlineStr"/>
+      <c r="D424" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">    Programar la consulta por período</t>
         </is>
       </c>
-      <c r="E423" s="17" t="inlineStr"/>
-      <c r="F423" s="17" t="inlineStr">
+      <c r="E424" s="17" t="inlineStr"/>
+      <c r="F424" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G423" s="17" t="inlineStr">
+      <c r="G424" s="17" t="inlineStr">
         <is>
           <t>Sin asignar</t>
         </is>
       </c>
-      <c r="H423" s="16" t="inlineStr">
+      <c r="H424" s="16" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="I423" s="16" t="inlineStr"/>
+      <c r="I424" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I423"/>
+  <autoFilter ref="A4:I424"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H423">
+  <conditionalFormatting sqref="H5:H424">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Hecho"</formula>
     </cfRule>
@@ -23272,13 +23358,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="H5:H423" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H424" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,En curso,En revisión,Hecho,Bloqueado"</formula1>
     </dataValidation>
-    <dataValidation sqref="E5:E423" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E424" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I423" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:I424" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Aguilera Maximiliano,Hoyos Franco,Delipetro Ezequiel,Achille Nahuel,Equipo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23593,7 +23679,7 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Cerrado</t>
         </is>
       </c>
     </row>
@@ -23630,7 +23716,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Cerrado</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23753,7 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Cerrado</t>
         </is>
       </c>
     </row>
@@ -23704,7 +23790,7 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>Planificado</t>
+          <t>En curso</t>
         </is>
       </c>
     </row>
@@ -23741,7 +23827,7 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>Planificado</t>
+          <t>En curso</t>
         </is>
       </c>
     </row>
@@ -23839,11 +23925,11 @@
         <v>7</v>
       </c>
       <c r="E17" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 13'!A6:A36,2)="T-")*1)</f>
+        <f>SUMPRODUCT((LEFT('Sprint 13'!A6:A37,2)="T-")*1)</f>
         <v/>
       </c>
       <c r="F17" s="15">
-        <f>SUMPRODUCT((LEFT('Sprint 13'!A6:A36,2)="T-")*('Sprint 13'!E6:E36="Hecho"))</f>
+        <f>SUMPRODUCT((LEFT('Sprint 13'!A6:A37,2)="T-")*('Sprint 13'!E6:E37="Hecho"))</f>
         <v/>
       </c>
       <c r="G17" s="18">
@@ -28041,7 +28127,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Período: 14/09 al 20/09    |    Estado: En curso</t>
+          <t>Período: 14/09 al 20/09    |    Estado: Cerrado</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
